--- a/public/excel-files/atlas.xlsx
+++ b/public/excel-files/atlas.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1919" uniqueCount="1048">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1991" uniqueCount="1086">
   <si>
     <t>ID</t>
   </si>
@@ -46,6 +46,9 @@
     <t>platforms</t>
   </si>
   <si>
+    <t>AML.T0108</t>
+  </si>
+  <si>
     <t>AML.T0100</t>
   </si>
   <si>
@@ -217,6 +220,9 @@
     <t>AML.T0059</t>
   </si>
   <si>
+    <t>AML.T0105</t>
+  </si>
+  <si>
     <t>AML.T0021</t>
   </si>
   <si>
@@ -235,6 +241,12 @@
     <t>AML.T0049</t>
   </si>
   <si>
+    <t>AML.T0106</t>
+  </si>
+  <si>
+    <t>AML.T0107</t>
+  </si>
+  <si>
     <t>AML.T0048</t>
   </si>
   <si>
@@ -313,6 +325,9 @@
     <t>AML.T0067</t>
   </si>
   <si>
+    <t>AML.T0011.003</t>
+  </si>
+  <si>
     <t>AML.T0011.001</t>
   </si>
   <si>
@@ -364,6 +379,9 @@
     <t>AML.T0020</t>
   </si>
   <si>
+    <t>AML.T0011.002</t>
+  </si>
+  <si>
     <t>AML.T0000.001</t>
   </si>
   <si>
@@ -376,6 +394,9 @@
     <t>AML.T0060</t>
   </si>
   <si>
+    <t>AML.T0104</t>
+  </si>
+  <si>
     <t>AML.T0019</t>
   </si>
   <si>
@@ -490,6 +511,9 @@
     <t>AML.T0043.000</t>
   </si>
   <si>
+    <t>attack-pattern--cf34558d-6970-51aa-a43e-d345b9cf7d38</t>
+  </si>
+  <si>
     <t>attack-pattern--bd74bd28-20ce-5f69-972e-0afe627b7147</t>
   </si>
   <si>
@@ -661,6 +685,9 @@
     <t>attack-pattern--6cc31098-f336-5fd8-932e-0289ff502d16</t>
   </si>
   <si>
+    <t>attack-pattern--8a98b993-8854-5fdd-ae81-4256db9e7a2d</t>
+  </si>
+  <si>
     <t>attack-pattern--d3d7763a-58e1-5e38-84fd-3abea967cb08</t>
   </si>
   <si>
@@ -679,6 +706,12 @@
     <t>attack-pattern--ebeed0c7-c5de-5049-8f27-efcae5f88b00</t>
   </si>
   <si>
+    <t>attack-pattern--61bd1eb1-b526-59aa-9b1c-86a7dc5fa0d8</t>
+  </si>
+  <si>
+    <t>attack-pattern--1f612544-c939-5d60-ad34-2d0644622e1f</t>
+  </si>
+  <si>
     <t>attack-pattern--2093defe-1976-5bca-9c88-f63072c90073</t>
   </si>
   <si>
@@ -757,6 +790,9 @@
     <t>attack-pattern--ab0f8614-31f1-5014-a3e5-4520341c4933</t>
   </si>
   <si>
+    <t>attack-pattern--386bf4df-e7c7-54da-a297-fec4ffd5e1a8</t>
+  </si>
+  <si>
     <t>attack-pattern--08fd47ac-8b5f-5c0b-8b1d-8e915351cdc2</t>
   </si>
   <si>
@@ -808,6 +844,9 @@
     <t>attack-pattern--4f25f684-63f5-5dfa-a286-20dfbd6db4c1</t>
   </si>
   <si>
+    <t>attack-pattern--5010d920-1568-56ee-ae3e-18fcf145fa40</t>
+  </si>
+  <si>
     <t>attack-pattern--02ea7626-0eec-5a4b-98ff-b3f21733b783</t>
   </si>
   <si>
@@ -820,6 +859,9 @@
     <t>attack-pattern--7ef953bd-97c4-5fac-af50-8619601046e2</t>
   </si>
   <si>
+    <t>attack-pattern--04842d98-bb69-586e-9765-6ff1f56ef722</t>
+  </si>
+  <si>
     <t>attack-pattern--c38896b2-974c-5ed5-adeb-c2477b311353</t>
   </si>
   <si>
@@ -934,6 +976,9 @@
     <t>attack-pattern--5f8f898d-1e29-52a7-bf95-2d420313aee8</t>
   </si>
   <si>
+    <t>AI Agent</t>
+  </si>
+  <si>
     <t>AI Agent Clickbait</t>
   </si>
   <si>
@@ -1105,6 +1150,9 @@
     <t>Erode Dataset Integrity</t>
   </si>
   <si>
+    <t>Escape to Host</t>
+  </si>
+  <si>
     <t>Establish Accounts</t>
   </si>
   <si>
@@ -1123,6 +1171,12 @@
     <t>Exploit Public-Facing Application</t>
   </si>
   <si>
+    <t>Exploitation for Credential Access</t>
+  </si>
+  <si>
+    <t>Exploitation for Defense Evasion</t>
+  </si>
+  <si>
     <t>External Harms</t>
   </si>
   <si>
@@ -1201,6 +1255,9 @@
     <t>LLM Trusted Output Components Manipulation</t>
   </si>
   <si>
+    <t>Malicious Link</t>
+  </si>
+  <si>
     <t>Malicious Package</t>
   </si>
   <si>
@@ -1252,6 +1309,9 @@
     <t>Poison Training Data</t>
   </si>
   <si>
+    <t>Poisoned AI Agent Tool</t>
+  </si>
+  <si>
     <t>Pre-Print Repositories</t>
   </si>
   <si>
@@ -1264,6 +1324,9 @@
     <t>Publish Hallucinated Entities</t>
   </si>
   <si>
+    <t>Publish Poisoned AI Agent Tool</t>
+  </si>
+  <si>
     <t>Publish Poisoned Datasets</t>
   </si>
   <si>
@@ -1376,6 +1439,10 @@
   </si>
   <si>
     <t>White-Box Optimization</t>
+  </si>
+  <si>
+    <t>Adversaries may abuse AI agents present on the victim's system for command and control. AI agents are often granted access to tools that can execute shell commands, reach out to the internet, and interact with other services in the victim's environment, making them capable C2 agents.
+The adversary may modify the behavior of an AI agent for C2 via [LLM Prompt Injection](/techniques/AML.T0051) and rely on the agent's ability to invoke tools to retrieve and execute the adversary's commands. They may maintain persistent control of an agent via [Modify AI Agent Configuration](/techniques/AML.T0081) or [AI Agent Context Poisoning](/techniques/AML.T0080). They may instruct the agent to not report their actions to the user in an attempt to remain covert.</t>
   </si>
   <si>
     <t>Adversaries may craft deceptive web content designed to bait Computer-Using AI agents or AI web browsers into taking unintended actions, such as clicking buttons, copying code, or navigating to specific web pages. These attacks exploit the agent's interpretation of UI content, visual cues, or prompt-like language embedded in the site. When successful, they can lead the agent to inadvertently copy and execute malicious code on the user's operating system.</t>
@@ -1674,6 +1741,10 @@
     <t>Adversaries may poison or manipulate portions of a dataset to reduce its usefulness, reduce trust, and cause users to waste resources correcting errors.</t>
   </si>
   <si>
+    <t>Adversaries may break out of a container or virtualized environment to gain access to the underlying host. This can allow an adversary access to other containerized or virtualized resources from the host level or to the host itself. In principle, containerized / virtualized resources should provide a clear separation of application functionality and be isolated from the host environment.
+There are many ways an adversary may escape from a container or sandbox environment via AI Systems. For example, modifying an AI Agent's configuration to disable safety features or user confirmations could allow the adversary to invoke tools to be run on host environments rather than in the sandbox.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Adversaries may create accounts with various services for use in targeting, to gain access to resources needed in [AI Attack Staging](/tactics/AML.TA0001), or for victim impersonation.
 </t>
   </si>
@@ -1698,6 +1769,12 @@
   <si>
     <t xml:space="preserve">Adversaries may attempt to take advantage of a weakness in an Internet-facing computer or program using software, data, or commands in order to cause unintended or unanticipated behavior. The weakness in the system can be a bug, a glitch, or a design vulnerability. These applications are often websites, but can include databases (like SQL), standard services (like SMB or SSH), network device administration and management protocols (like SNMP and Smart Install), and any other applications with Internet accessible open sockets, such as web servers and related services.
 </t>
+  </si>
+  <si>
+    <t>Adversaries may exploit software vulnerabilities in an attempt to collect credentials. Exploitation of a software vulnerability occurs when an adversary takes advantage of a programming error in a program, service, or within the operating system software or kernel itself to execute adversary-controlled code.</t>
+  </si>
+  <si>
+    <t>Adversaries may exploit a system or application vulnerability to bypass security features. Exploitation of a vulnerability occurs when an adversary takes advantage of a programming error in a program, service, or within the operating system software or kernel itself to execute adversary-controlled code. Vulnerabilities may exist in defensive security software that can be used to disable or circumvent them.</t>
   </si>
   <si>
     <t xml:space="preserve">Adversaries may abuse their access to a victim system and use its resources or capabilities to further their goals by causing harms external to that system.
@@ -1845,6 +1922,10 @@
 The LLM may be instructed to tailor its language to appear more trustworthy to the user or attempt to manipulate the user to take certain actions. Other response components that could be manipulated include links, recommended follow-up actions, retrieved document metadata, and [Citations](/techniques/AML.T0067.000).</t>
   </si>
   <si>
+    <t>An adversary may rely upon a user clicking a malicious link in order to gain execution. Users may be subjected to social engineering to get them to click on a link that will lead to code execution. This user action will typically be observed as follow-on behavior from Spearphishing Link. Clicking on a link may also lead to other execution techniques such as exploitation of a browser or application vulnerability via Exploitation for Client Execution. Links may also lead users to download files that require execution via Malicious File.
+There are many ways an adversary can leverage malicious links to gain access to a victim system via an AI system. For example, an AI Agent that is configured to not validate website origin headers will accept connections from any website, allowing adversaries the ability to get around previously inaccessible network.</t>
+  </si>
+  <si>
     <t>Adversaries may develop malicious software packages that when imported by a user have a deleterious effect.
 Malicious packages may behave as expected to the user. They may be introduced via [AI Supply Chain Compromise](/techniques/AML.T0010). They may not present as obviously malicious to the user and may appear to be useful for an AI-related task.</t>
   </si>
@@ -1886,7 +1967,8 @@
   </si>
   <si>
     <t>Adversaries may modify the configuration files for AI agents on a system. This allows malicious changes to persist beyond the life of a single agent and affects any agents that share the configuration.
-Configuration changes may include modifications to the system prompt, tampering with or replacing knowledge sources, modification to settings of connected tools, and more. Through those changes, an attacker could redirect outputs or tools to malicious services, embed covert instructions that exfiltrate data, or weaken security controls that normally restrict agent behavior.</t>
+Configuration changes may include modifications to the system prompt, tampering with or replacing knowledge sources, modification to settings of connected tools, and more. Through those changes, an attacker could redirect outputs or tools to malicious services, embed covert instructions that exfiltrate data, or weaken security controls that normally restrict agent behavior.
+Adversaries may modify or disable a configuration setting related to security controls, such as those that would prevent the AI Agent from taking actions that may be harmful to the user's system without human-in-the-loop oversight. Disabling AI agent security features may allow adversaries to achieve their malicious goals and maintain long-term corruption of the AI agent.</t>
   </si>
   <si>
     <t>Adversaries may directly modify an AI model's architecture to re-define it's behavior. This can include adding or removing layers as well as adding pre or post-processing operations.
@@ -1928,6 +2010,10 @@
 Poisoned data can be introduced via [AI Supply Chain Compromise](/techniques/AML.T0010) or the data may be poisoned after the adversary gains [Initial Access](/tactics/AML.TA0004) to the system.</t>
   </si>
   <si>
+    <t>A victim may invoke a poisoned tool when interacting with their AI agent. A poisoned tool may execute an [LLM Prompt Injection](/techniques/AML.T0051) or perform [AI Agent Tool Invocation](/techniques/AML.T0053).
+Poisoned AI agent tools may be introduced into the victim's environment via [AI Software](/techniques/AML.T0010.001), or the user may configure their agent to connect to remote tools.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pre-Print repositories, such as arXiv, contain the latest academic research papers that haven't been peer reviewed.
 They may contain research notes, or technical reports that aren't typically published in journals or conference proceedings.
 Pre-print repositories also serve as a central location to share papers that have been accepted to journals.
@@ -1946,6 +2032,11 @@
   </si>
   <si>
     <t>Adversaries may create an entity they control, such as a software package, website, or email address to a source hallucinated by an LLM. The hallucinations may take the form of package names commands, URLs, company names, or email addresses that point the victim to the entity controlled by the adversary. When the victim interacts with the adversary-controlled entity, the attack can proceed.</t>
+  </si>
+  <si>
+    <t>Adversaries may create and publish poisoned AI agent tools. Poisoned tools may contain an [LLM Prompt Injection](/techniques/AML.T0051), which can lead to a variety of impacts.
+Tools may be published to open source version control repositories (e.g. GitHub, GitLab), to package registries (e.g. npm), or to repositories specifically designed for sharing tools (e.g. OpenClaw Hub). These registries may be largely unregulated and may contain many poisoned tools [\[1\]][1].
+[1]: https://opensourcemalware.com/blog/clawdbot-skills-ganked-your-crypto</t>
   </si>
   <si>
     <t xml:space="preserve">Adversaries may [Poison Training Data](/techniques/AML.T0020) and publish it to a public location.
@@ -2137,6 +2228,9 @@
 </t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0108</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0100</t>
   </si>
   <si>
@@ -2308,6 +2402,9 @@
     <t>https://atlas.mitre.org/techniques/AML.T0059</t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0105</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0021</t>
   </si>
   <si>
@@ -2326,6 +2423,12 @@
     <t>https://atlas.mitre.org/techniques/AML.T0049</t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0106</t>
+  </si>
+  <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0107</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0048</t>
   </si>
   <si>
@@ -2404,6 +2507,9 @@
     <t>https://atlas.mitre.org/techniques/AML.T0067</t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0011.003</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0011.001</t>
   </si>
   <si>
@@ -2455,6 +2561,9 @@
     <t>https://atlas.mitre.org/techniques/AML.T0020</t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0011.002</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0000.001</t>
   </si>
   <si>
@@ -2467,6 +2576,9 @@
     <t>https://atlas.mitre.org/techniques/AML.T0060</t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0104</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0019</t>
   </si>
   <si>
@@ -2581,6 +2693,9 @@
     <t>https://atlas.mitre.org/techniques/AML.T0043.000</t>
   </si>
   <si>
+    <t>30 January 2026</t>
+  </si>
+  <si>
     <t>25 November 2025</t>
   </si>
   <si>
@@ -2644,6 +2759,9 @@
     <t>05 November 2025</t>
   </si>
   <si>
+    <t>05 February 2026</t>
+  </si>
+  <si>
     <t>13 October 2025</t>
   </si>
   <si>
@@ -2680,6 +2798,9 @@
     <t>29 April 2024</t>
   </si>
   <si>
+    <t>Command and Control</t>
+  </si>
+  <si>
     <t>Execution</t>
   </si>
   <si>
@@ -2704,9 +2825,6 @@
     <t>AI Model Access</t>
   </si>
   <si>
-    <t>Command and Control</t>
-  </si>
-  <si>
     <t>Initial Access</t>
   </si>
   <si>
@@ -2722,6 +2840,9 @@
     <t>AI Attack Staging</t>
   </si>
   <si>
+    <t>Privilege Escalation</t>
+  </si>
+  <si>
     <t>Defense Evasion, Impact, Initial Access</t>
   </si>
   <si>
@@ -2734,6 +2855,9 @@
     <t>AI Attack Staging, Persistence</t>
   </si>
   <si>
+    <t>Defense Evasion, Persistence</t>
+  </si>
+  <si>
     <t>Initial Access, Lateral Movement</t>
   </si>
   <si>
@@ -2846,9 +2970,6 @@
   </si>
   <si>
     <t>x-mitre-tactic--39099d7c-9fb7-5836-8e8a-9f6b594bf01b</t>
-  </si>
-  <si>
-    <t>Privilege Escalation</t>
   </si>
   <si>
     <t>The adversary is leveraging their knowledge of and access to the target system to tailor the attack.
@@ -3563,16 +3684,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -3615,21 +3728,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
       <right/>
       <top/>
       <bottom/>
@@ -3644,27 +3742,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3965,35 +4075,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I149"/>
+  <dimension ref="A1:I156"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -4002,28 +4112,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C2" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="D2" t="s">
-        <v>453</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>601</v>
+        <v>474</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>629</v>
       </c>
       <c r="F2" t="s">
-        <v>749</v>
+        <v>784</v>
       </c>
       <c r="G2" t="s">
-        <v>749</v>
+        <v>806</v>
       </c>
       <c r="H2" t="s">
-        <v>782</v>
+        <v>819</v>
       </c>
       <c r="I2" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -4031,28 +4141,28 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C3" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="D3" t="s">
-        <v>454</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>602</v>
+        <v>475</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>630</v>
       </c>
       <c r="F3" t="s">
-        <v>750</v>
+        <v>785</v>
       </c>
       <c r="G3" t="s">
-        <v>770</v>
+        <v>785</v>
       </c>
       <c r="H3" t="s">
-        <v>783</v>
+        <v>820</v>
       </c>
       <c r="I3" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -4060,28 +4170,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="D4" t="s">
-        <v>455</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>603</v>
+        <v>476</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>631</v>
       </c>
       <c r="F4" t="s">
-        <v>749</v>
+        <v>786</v>
       </c>
       <c r="G4" t="s">
-        <v>771</v>
+        <v>807</v>
       </c>
       <c r="H4" t="s">
-        <v>784</v>
+        <v>821</v>
       </c>
       <c r="I4" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -4089,28 +4199,28 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C5" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="D5" t="s">
-        <v>456</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>604</v>
+        <v>477</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>632</v>
       </c>
       <c r="F5" t="s">
-        <v>749</v>
+        <v>785</v>
       </c>
       <c r="G5" t="s">
-        <v>749</v>
+        <v>808</v>
       </c>
       <c r="H5" t="s">
-        <v>783</v>
+        <v>822</v>
       </c>
       <c r="I5" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -4118,28 +4228,28 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="D6" t="s">
-        <v>457</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>605</v>
+        <v>478</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>633</v>
       </c>
       <c r="F6" t="s">
-        <v>751</v>
+        <v>785</v>
       </c>
       <c r="G6" t="s">
-        <v>760</v>
+        <v>785</v>
       </c>
       <c r="H6" t="s">
-        <v>785</v>
+        <v>821</v>
       </c>
       <c r="I6" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -4147,28 +4257,28 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C7" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="D7" t="s">
-        <v>458</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>606</v>
+        <v>479</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>634</v>
       </c>
       <c r="F7" t="s">
-        <v>750</v>
+        <v>787</v>
       </c>
       <c r="G7" t="s">
-        <v>750</v>
+        <v>796</v>
       </c>
       <c r="H7" t="s">
-        <v>786</v>
+        <v>823</v>
       </c>
       <c r="I7" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -4176,28 +4286,28 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C8" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="D8" t="s">
-        <v>459</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>607</v>
+        <v>480</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>635</v>
       </c>
       <c r="F8" t="s">
-        <v>752</v>
+        <v>786</v>
       </c>
       <c r="G8" t="s">
-        <v>763</v>
+        <v>786</v>
       </c>
       <c r="H8" t="s">
-        <v>786</v>
+        <v>824</v>
       </c>
       <c r="I8" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -4205,28 +4315,28 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="C9" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="D9" t="s">
-        <v>460</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>608</v>
+        <v>481</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>636</v>
       </c>
       <c r="F9" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G9" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
       <c r="H9" t="s">
-        <v>787</v>
+        <v>824</v>
       </c>
       <c r="I9" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -4234,28 +4344,28 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C10" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="D10" t="s">
-        <v>461</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>609</v>
+        <v>482</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>637</v>
       </c>
       <c r="F10" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G10" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
       <c r="H10" t="s">
-        <v>788</v>
+        <v>825</v>
       </c>
       <c r="I10" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -4263,28 +4373,28 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C11" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="D11" t="s">
-        <v>462</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>610</v>
+        <v>483</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>638</v>
       </c>
       <c r="F11" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G11" t="s">
-        <v>755</v>
+        <v>799</v>
       </c>
       <c r="H11" t="s">
-        <v>789</v>
+        <v>826</v>
       </c>
       <c r="I11" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -4292,28 +4402,28 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C12" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="D12" t="s">
-        <v>463</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>611</v>
+        <v>484</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>639</v>
       </c>
       <c r="F12" t="s">
-        <v>753</v>
+        <v>788</v>
       </c>
       <c r="G12" t="s">
-        <v>772</v>
+        <v>791</v>
       </c>
       <c r="H12" t="s">
-        <v>790</v>
+        <v>827</v>
       </c>
       <c r="I12" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -4321,28 +4431,28 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C13" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="D13" t="s">
-        <v>464</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>612</v>
+        <v>485</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>640</v>
       </c>
       <c r="F13" t="s">
-        <v>752</v>
+        <v>789</v>
       </c>
       <c r="G13" t="s">
-        <v>773</v>
+        <v>809</v>
       </c>
       <c r="H13" t="s">
-        <v>791</v>
+        <v>819</v>
       </c>
       <c r="I13" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -4350,28 +4460,28 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C14" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="D14" t="s">
-        <v>465</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>613</v>
+        <v>486</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>641</v>
       </c>
       <c r="F14" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G14" t="s">
-        <v>763</v>
+        <v>810</v>
       </c>
       <c r="H14" t="s">
-        <v>791</v>
+        <v>828</v>
       </c>
       <c r="I14" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -4379,28 +4489,28 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C15" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="D15" t="s">
-        <v>466</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>614</v>
+        <v>487</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>642</v>
       </c>
       <c r="F15" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G15" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
       <c r="H15" t="s">
-        <v>789</v>
+        <v>828</v>
       </c>
       <c r="I15" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -4408,28 +4518,28 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C16" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="D16" t="s">
-        <v>467</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>615</v>
+        <v>488</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>643</v>
       </c>
       <c r="F16" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G16" t="s">
-        <v>755</v>
+        <v>799</v>
       </c>
       <c r="H16" t="s">
-        <v>787</v>
+        <v>827</v>
       </c>
       <c r="I16" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -4437,28 +4547,28 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C17" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="D17" t="s">
-        <v>468</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>616</v>
+        <v>489</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>644</v>
       </c>
       <c r="F17" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G17" t="s">
-        <v>763</v>
+        <v>791</v>
       </c>
       <c r="H17" t="s">
-        <v>787</v>
+        <v>825</v>
       </c>
       <c r="I17" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -4466,28 +4576,28 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C18" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="D18" t="s">
-        <v>469</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>617</v>
+        <v>490</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>645</v>
       </c>
       <c r="F18" t="s">
-        <v>750</v>
+        <v>788</v>
       </c>
       <c r="G18" t="s">
-        <v>750</v>
+        <v>799</v>
       </c>
       <c r="H18" t="s">
-        <v>792</v>
+        <v>825</v>
       </c>
       <c r="I18" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -4495,28 +4605,28 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C19" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="D19" t="s">
-        <v>470</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>618</v>
+        <v>491</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>646</v>
       </c>
       <c r="F19" t="s">
-        <v>752</v>
+        <v>786</v>
       </c>
       <c r="G19" t="s">
-        <v>760</v>
+        <v>786</v>
       </c>
       <c r="H19" t="s">
-        <v>793</v>
+        <v>829</v>
       </c>
       <c r="I19" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -4524,28 +4634,28 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C20" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="D20" t="s">
-        <v>471</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>619</v>
+        <v>492</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>647</v>
       </c>
       <c r="F20" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G20" t="s">
-        <v>763</v>
+        <v>796</v>
       </c>
       <c r="H20" t="s">
-        <v>787</v>
+        <v>830</v>
       </c>
       <c r="I20" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -4553,28 +4663,28 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C21" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="D21" t="s">
-        <v>472</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>620</v>
+        <v>493</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>648</v>
       </c>
       <c r="F21" t="s">
-        <v>751</v>
+        <v>788</v>
       </c>
       <c r="G21" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
       <c r="H21" t="s">
-        <v>787</v>
+        <v>825</v>
       </c>
       <c r="I21" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -4582,28 +4692,28 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C22" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="D22" t="s">
-        <v>473</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>621</v>
+        <v>494</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>649</v>
       </c>
       <c r="F22" t="s">
-        <v>754</v>
+        <v>787</v>
       </c>
       <c r="G22" t="s">
-        <v>772</v>
+        <v>799</v>
       </c>
       <c r="H22" t="s">
-        <v>794</v>
+        <v>825</v>
       </c>
       <c r="I22" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -4611,28 +4721,28 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C23" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="D23" t="s">
-        <v>474</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>622</v>
+        <v>495</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>650</v>
       </c>
       <c r="F23" t="s">
-        <v>752</v>
+        <v>790</v>
       </c>
       <c r="G23" t="s">
-        <v>752</v>
+        <v>809</v>
       </c>
       <c r="H23" t="s">
-        <v>795</v>
+        <v>831</v>
       </c>
       <c r="I23" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -4640,28 +4750,28 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C24" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="D24" t="s">
-        <v>475</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>623</v>
+        <v>496</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>651</v>
       </c>
       <c r="F24" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G24" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
       <c r="H24" t="s">
-        <v>795</v>
+        <v>832</v>
       </c>
       <c r="I24" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -4669,28 +4779,28 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C25" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="D25" t="s">
-        <v>476</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>624</v>
+        <v>497</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>652</v>
       </c>
       <c r="F25" t="s">
-        <v>755</v>
+        <v>788</v>
       </c>
       <c r="G25" t="s">
-        <v>755</v>
+        <v>811</v>
       </c>
       <c r="H25" t="s">
-        <v>794</v>
+        <v>832</v>
       </c>
       <c r="I25" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -4698,28 +4808,28 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C26" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="D26" t="s">
-        <v>477</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>625</v>
+        <v>498</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="F26" t="s">
-        <v>756</v>
+        <v>791</v>
       </c>
       <c r="G26" t="s">
-        <v>753</v>
+        <v>791</v>
       </c>
       <c r="H26" t="s">
-        <v>792</v>
+        <v>831</v>
       </c>
       <c r="I26" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -4727,28 +4837,28 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C27" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="D27" t="s">
-        <v>478</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>626</v>
+        <v>499</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>654</v>
       </c>
       <c r="F27" t="s">
-        <v>757</v>
+        <v>792</v>
       </c>
       <c r="G27" t="s">
-        <v>775</v>
+        <v>789</v>
       </c>
       <c r="H27" t="s">
-        <v>782</v>
+        <v>829</v>
       </c>
       <c r="I27" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -4756,28 +4866,28 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C28" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="D28" t="s">
-        <v>479</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>627</v>
+        <v>500</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>655</v>
       </c>
       <c r="F28" t="s">
-        <v>752</v>
+        <v>793</v>
       </c>
       <c r="G28" t="s">
-        <v>752</v>
+        <v>812</v>
       </c>
       <c r="H28" t="s">
-        <v>787</v>
+        <v>820</v>
       </c>
       <c r="I28" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -4785,28 +4895,28 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C29" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="D29" t="s">
-        <v>480</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>628</v>
+        <v>501</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>656</v>
       </c>
       <c r="F29" t="s">
-        <v>758</v>
+        <v>788</v>
       </c>
       <c r="G29" t="s">
-        <v>758</v>
+        <v>788</v>
       </c>
       <c r="H29" t="s">
-        <v>794</v>
+        <v>825</v>
       </c>
       <c r="I29" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -4814,28 +4924,28 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C30" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="D30" t="s">
-        <v>481</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>629</v>
+        <v>502</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>657</v>
       </c>
       <c r="F30" t="s">
-        <v>756</v>
+        <v>794</v>
       </c>
       <c r="G30" t="s">
-        <v>756</v>
+        <v>794</v>
       </c>
       <c r="H30" t="s">
-        <v>794</v>
+        <v>831</v>
       </c>
       <c r="I30" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -4843,28 +4953,28 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="C31" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="D31" t="s">
-        <v>482</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>630</v>
+        <v>503</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>658</v>
       </c>
       <c r="F31" t="s">
-        <v>752</v>
+        <v>792</v>
       </c>
       <c r="G31" t="s">
-        <v>763</v>
+        <v>792</v>
       </c>
       <c r="H31" t="s">
-        <v>788</v>
+        <v>831</v>
       </c>
       <c r="I31" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -4872,28 +4982,28 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C32" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="D32" t="s">
-        <v>483</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>631</v>
+        <v>504</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>659</v>
       </c>
       <c r="F32" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G32" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
       <c r="H32" t="s">
-        <v>795</v>
+        <v>826</v>
       </c>
       <c r="I32" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -4901,28 +5011,28 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C33" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="D33" t="s">
-        <v>484</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>632</v>
+        <v>505</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>660</v>
       </c>
       <c r="F33" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G33" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
       <c r="H33" t="s">
-        <v>795</v>
+        <v>832</v>
       </c>
       <c r="I33" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -4930,28 +5040,28 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C34" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D34" t="s">
-        <v>485</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>633</v>
+        <v>506</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>661</v>
       </c>
       <c r="F34" t="s">
-        <v>750</v>
+        <v>788</v>
       </c>
       <c r="G34" t="s">
-        <v>770</v>
+        <v>799</v>
       </c>
       <c r="H34" t="s">
-        <v>784</v>
+        <v>832</v>
       </c>
       <c r="I34" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -4959,28 +5069,28 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C35" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="D35" t="s">
-        <v>486</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>634</v>
+        <v>507</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>662</v>
       </c>
       <c r="F35" t="s">
-        <v>752</v>
+        <v>786</v>
       </c>
       <c r="G35" t="s">
-        <v>763</v>
+        <v>807</v>
       </c>
       <c r="H35" t="s">
-        <v>791</v>
+        <v>822</v>
       </c>
       <c r="I35" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -4988,28 +5098,28 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C36" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="D36" t="s">
-        <v>487</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>635</v>
+        <v>508</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>663</v>
       </c>
       <c r="F36" t="s">
-        <v>749</v>
+        <v>788</v>
       </c>
       <c r="G36" t="s">
-        <v>749</v>
+        <v>799</v>
       </c>
       <c r="H36" t="s">
-        <v>788</v>
+        <v>828</v>
       </c>
       <c r="I36" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -5017,28 +5127,28 @@
         <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C37" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="D37" t="s">
-        <v>488</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>636</v>
+        <v>509</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>664</v>
       </c>
       <c r="F37" t="s">
-        <v>750</v>
+        <v>785</v>
       </c>
       <c r="G37" t="s">
-        <v>760</v>
+        <v>785</v>
       </c>
       <c r="H37" t="s">
-        <v>786</v>
+        <v>826</v>
       </c>
       <c r="I37" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -5046,28 +5156,28 @@
         <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="C38" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="D38" t="s">
-        <v>489</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>637</v>
+        <v>510</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>665</v>
       </c>
       <c r="F38" t="s">
-        <v>759</v>
+        <v>786</v>
       </c>
       <c r="G38" t="s">
-        <v>776</v>
+        <v>796</v>
       </c>
       <c r="H38" t="s">
-        <v>786</v>
+        <v>824</v>
       </c>
       <c r="I38" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -5075,28 +5185,28 @@
         <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="C39" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="D39" t="s">
-        <v>490</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>638</v>
+        <v>511</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>666</v>
       </c>
       <c r="F39" t="s">
-        <v>752</v>
+        <v>795</v>
       </c>
       <c r="G39" t="s">
-        <v>776</v>
+        <v>813</v>
       </c>
       <c r="H39" t="s">
-        <v>786</v>
+        <v>824</v>
       </c>
       <c r="I39" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -5104,28 +5214,28 @@
         <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C40" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="D40" t="s">
-        <v>491</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>639</v>
+        <v>512</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>667</v>
       </c>
       <c r="F40" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G40" t="s">
-        <v>752</v>
+        <v>813</v>
       </c>
       <c r="H40" t="s">
-        <v>787</v>
+        <v>824</v>
       </c>
       <c r="I40" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -5133,28 +5243,28 @@
         <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C41" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="D41" t="s">
-        <v>492</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>640</v>
+        <v>513</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>668</v>
       </c>
       <c r="F41" t="s">
-        <v>760</v>
+        <v>788</v>
       </c>
       <c r="G41" t="s">
-        <v>769</v>
+        <v>788</v>
       </c>
       <c r="H41" t="s">
-        <v>794</v>
+        <v>825</v>
       </c>
       <c r="I41" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -5162,28 +5272,28 @@
         <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C42" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="D42" t="s">
-        <v>493</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>641</v>
+        <v>514</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>669</v>
       </c>
       <c r="F42" t="s">
-        <v>752</v>
+        <v>796</v>
       </c>
       <c r="G42" t="s">
-        <v>763</v>
+        <v>805</v>
       </c>
       <c r="H42" t="s">
-        <v>788</v>
+        <v>831</v>
       </c>
       <c r="I42" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -5191,28 +5301,28 @@
         <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="C43" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="D43" t="s">
-        <v>494</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>642</v>
+        <v>515</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>670</v>
       </c>
       <c r="F43" t="s">
-        <v>761</v>
+        <v>788</v>
       </c>
       <c r="G43" t="s">
-        <v>761</v>
+        <v>799</v>
       </c>
       <c r="H43" t="s">
-        <v>782</v>
+        <v>826</v>
       </c>
       <c r="I43" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -5220,28 +5330,28 @@
         <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C44" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="D44" t="s">
-        <v>495</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>643</v>
+        <v>516</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>671</v>
       </c>
       <c r="F44" t="s">
-        <v>751</v>
+        <v>797</v>
       </c>
       <c r="G44" t="s">
-        <v>763</v>
+        <v>797</v>
       </c>
       <c r="H44" t="s">
-        <v>787</v>
+        <v>820</v>
       </c>
       <c r="I44" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -5249,28 +5359,28 @@
         <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="C45" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="D45" t="s">
-        <v>496</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>644</v>
+        <v>517</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>672</v>
       </c>
       <c r="F45" t="s">
-        <v>751</v>
+        <v>787</v>
       </c>
       <c r="G45" t="s">
-        <v>751</v>
+        <v>799</v>
       </c>
       <c r="H45" t="s">
-        <v>782</v>
+        <v>825</v>
       </c>
       <c r="I45" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -5278,28 +5388,28 @@
         <v>53</v>
       </c>
       <c r="B46" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C46" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="D46" t="s">
-        <v>497</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>645</v>
+        <v>518</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>673</v>
       </c>
       <c r="F46" t="s">
-        <v>750</v>
+        <v>787</v>
       </c>
       <c r="G46" t="s">
-        <v>750</v>
+        <v>787</v>
       </c>
       <c r="H46" t="s">
-        <v>792</v>
+        <v>820</v>
       </c>
       <c r="I46" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -5307,28 +5417,28 @@
         <v>54</v>
       </c>
       <c r="B47" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="C47" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="D47" t="s">
-        <v>498</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>646</v>
+        <v>519</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>674</v>
       </c>
       <c r="F47" t="s">
-        <v>752</v>
+        <v>786</v>
       </c>
       <c r="G47" t="s">
-        <v>763</v>
+        <v>786</v>
       </c>
       <c r="H47" t="s">
-        <v>792</v>
+        <v>829</v>
       </c>
       <c r="I47" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -5336,28 +5446,28 @@
         <v>55</v>
       </c>
       <c r="B48" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C48" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="D48" t="s">
-        <v>499</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>647</v>
+        <v>520</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>675</v>
       </c>
       <c r="F48" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G48" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
       <c r="H48" t="s">
-        <v>792</v>
+        <v>829</v>
       </c>
       <c r="I48" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -5365,28 +5475,28 @@
         <v>56</v>
       </c>
       <c r="B49" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C49" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="D49" t="s">
-        <v>500</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>648</v>
+        <v>521</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>676</v>
       </c>
       <c r="F49" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G49" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
       <c r="H49" t="s">
-        <v>792</v>
+        <v>829</v>
       </c>
       <c r="I49" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5394,28 +5504,28 @@
         <v>57</v>
       </c>
       <c r="B50" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C50" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="D50" t="s">
-        <v>501</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>649</v>
+        <v>522</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>677</v>
       </c>
       <c r="F50" t="s">
-        <v>755</v>
+        <v>788</v>
       </c>
       <c r="G50" t="s">
-        <v>755</v>
+        <v>799</v>
       </c>
       <c r="H50" t="s">
-        <v>792</v>
+        <v>829</v>
       </c>
       <c r="I50" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -5423,28 +5533,28 @@
         <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C51" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="D51" t="s">
-        <v>502</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>650</v>
+        <v>523</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>678</v>
       </c>
       <c r="F51" t="s">
-        <v>755</v>
+        <v>791</v>
       </c>
       <c r="G51" t="s">
-        <v>765</v>
+        <v>791</v>
       </c>
       <c r="H51" t="s">
-        <v>792</v>
+        <v>829</v>
       </c>
       <c r="I51" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -5452,28 +5562,28 @@
         <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C52" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="D52" t="s">
-        <v>503</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>651</v>
+        <v>524</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>679</v>
       </c>
       <c r="F52" t="s">
-        <v>755</v>
+        <v>791</v>
       </c>
       <c r="G52" t="s">
-        <v>755</v>
+        <v>801</v>
       </c>
       <c r="H52" t="s">
-        <v>792</v>
+        <v>829</v>
       </c>
       <c r="I52" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -5481,28 +5591,28 @@
         <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="C53" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="D53" t="s">
-        <v>504</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>652</v>
+        <v>525</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>680</v>
       </c>
       <c r="F53" t="s">
-        <v>755</v>
+        <v>791</v>
       </c>
       <c r="G53" t="s">
-        <v>755</v>
+        <v>791</v>
       </c>
       <c r="H53" t="s">
-        <v>792</v>
+        <v>829</v>
       </c>
       <c r="I53" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -5510,28 +5620,28 @@
         <v>61</v>
       </c>
       <c r="B54" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C54" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="D54" t="s">
-        <v>505</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>653</v>
+        <v>526</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>681</v>
       </c>
       <c r="F54" t="s">
-        <v>762</v>
+        <v>791</v>
       </c>
       <c r="G54" t="s">
-        <v>777</v>
+        <v>791</v>
       </c>
       <c r="H54" t="s">
-        <v>791</v>
+        <v>829</v>
       </c>
       <c r="I54" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -5539,28 +5649,28 @@
         <v>62</v>
       </c>
       <c r="B55" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C55" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="D55" t="s">
-        <v>506</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>654</v>
+        <v>527</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>682</v>
       </c>
       <c r="F55" t="s">
-        <v>763</v>
+        <v>798</v>
       </c>
       <c r="G55" t="s">
-        <v>763</v>
+        <v>814</v>
       </c>
       <c r="H55" t="s">
-        <v>794</v>
+        <v>828</v>
       </c>
       <c r="I55" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -5568,28 +5678,28 @@
         <v>63</v>
       </c>
       <c r="B56" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="C56" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="D56" t="s">
-        <v>507</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>655</v>
+        <v>528</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>683</v>
       </c>
       <c r="F56" t="s">
-        <v>750</v>
+        <v>799</v>
       </c>
       <c r="G56" t="s">
-        <v>750</v>
+        <v>799</v>
       </c>
       <c r="H56" t="s">
-        <v>792</v>
+        <v>831</v>
       </c>
       <c r="I56" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -5597,28 +5707,28 @@
         <v>64</v>
       </c>
       <c r="B57" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C57" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="D57" t="s">
-        <v>508</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>656</v>
+        <v>529</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>684</v>
       </c>
       <c r="F57" t="s">
-        <v>752</v>
+        <v>786</v>
       </c>
       <c r="G57" t="s">
-        <v>763</v>
+        <v>786</v>
       </c>
       <c r="H57" t="s">
-        <v>788</v>
+        <v>829</v>
       </c>
       <c r="I57" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -5626,28 +5736,28 @@
         <v>65</v>
       </c>
       <c r="B58" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="C58" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="D58" t="s">
-        <v>509</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>657</v>
+        <v>530</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>685</v>
       </c>
       <c r="F58" t="s">
-        <v>755</v>
+        <v>788</v>
       </c>
       <c r="G58" t="s">
-        <v>755</v>
+        <v>799</v>
       </c>
       <c r="H58" t="s">
-        <v>788</v>
+        <v>826</v>
       </c>
       <c r="I58" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -5655,28 +5765,28 @@
         <v>66</v>
       </c>
       <c r="B59" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="C59" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="D59" t="s">
-        <v>510</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>658</v>
+        <v>531</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>686</v>
       </c>
       <c r="F59" t="s">
-        <v>759</v>
+        <v>791</v>
       </c>
       <c r="G59" t="s">
-        <v>776</v>
+        <v>791</v>
       </c>
       <c r="H59" t="s">
-        <v>787</v>
+        <v>826</v>
       </c>
       <c r="I59" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -5684,28 +5794,28 @@
         <v>67</v>
       </c>
       <c r="B60" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C60" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="D60" t="s">
-        <v>511</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>659</v>
+        <v>532</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>687</v>
       </c>
       <c r="F60" t="s">
-        <v>752</v>
+        <v>784</v>
       </c>
       <c r="G60" t="s">
-        <v>760</v>
+        <v>784</v>
       </c>
       <c r="H60" t="s">
-        <v>796</v>
+        <v>833</v>
       </c>
       <c r="I60" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -5713,28 +5823,28 @@
         <v>68</v>
       </c>
       <c r="B61" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C61" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="D61" t="s">
-        <v>512</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>660</v>
+        <v>533</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>688</v>
       </c>
       <c r="F61" t="s">
-        <v>750</v>
+        <v>795</v>
       </c>
       <c r="G61" t="s">
-        <v>750</v>
+        <v>813</v>
       </c>
       <c r="H61" t="s">
-        <v>797</v>
+        <v>825</v>
       </c>
       <c r="I61" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -5742,28 +5852,28 @@
         <v>69</v>
       </c>
       <c r="B62" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="C62" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="D62" t="s">
-        <v>513</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>661</v>
+        <v>534</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>689</v>
       </c>
       <c r="F62" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G62" t="s">
-        <v>763</v>
+        <v>796</v>
       </c>
       <c r="H62" t="s">
-        <v>797</v>
+        <v>834</v>
       </c>
       <c r="I62" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -5771,28 +5881,28 @@
         <v>70</v>
       </c>
       <c r="B63" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="C63" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="D63" t="s">
-        <v>514</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>662</v>
+        <v>535</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>690</v>
       </c>
       <c r="F63" t="s">
-        <v>752</v>
+        <v>786</v>
       </c>
       <c r="G63" t="s">
-        <v>763</v>
+        <v>786</v>
       </c>
       <c r="H63" t="s">
-        <v>797</v>
+        <v>835</v>
       </c>
       <c r="I63" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -5800,28 +5910,28 @@
         <v>71</v>
       </c>
       <c r="B64" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C64" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="D64" t="s">
-        <v>515</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>663</v>
+        <v>536</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>691</v>
       </c>
       <c r="F64" t="s">
-        <v>757</v>
+        <v>788</v>
       </c>
       <c r="G64" t="s">
-        <v>757</v>
+        <v>799</v>
       </c>
       <c r="H64" t="s">
-        <v>791</v>
+        <v>835</v>
       </c>
       <c r="I64" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -5829,28 +5939,28 @@
         <v>72</v>
       </c>
       <c r="B65" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="C65" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="D65" t="s">
-        <v>516</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>664</v>
+        <v>537</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>692</v>
       </c>
       <c r="F65" t="s">
-        <v>764</v>
+        <v>788</v>
       </c>
       <c r="G65" t="s">
-        <v>751</v>
+        <v>799</v>
       </c>
       <c r="H65" t="s">
-        <v>788</v>
+        <v>835</v>
       </c>
       <c r="I65" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -5858,28 +5968,28 @@
         <v>73</v>
       </c>
       <c r="B66" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C66" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="D66" t="s">
-        <v>517</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>665</v>
+        <v>538</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>693</v>
       </c>
       <c r="F66" t="s">
-        <v>752</v>
+        <v>793</v>
       </c>
       <c r="G66" t="s">
-        <v>772</v>
+        <v>793</v>
       </c>
       <c r="H66" t="s">
-        <v>797</v>
+        <v>828</v>
       </c>
       <c r="I66" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -5887,28 +5997,28 @@
         <v>74</v>
       </c>
       <c r="B67" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C67" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="D67" t="s">
-        <v>518</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>666</v>
+        <v>539</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>694</v>
       </c>
       <c r="F67" t="s">
-        <v>751</v>
+        <v>784</v>
       </c>
       <c r="G67" t="s">
-        <v>755</v>
+        <v>806</v>
       </c>
       <c r="H67" t="s">
-        <v>797</v>
+        <v>822</v>
       </c>
       <c r="I67" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -5916,28 +6026,28 @@
         <v>75</v>
       </c>
       <c r="B68" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="C68" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="D68" t="s">
-        <v>519</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>667</v>
+        <v>540</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>695</v>
       </c>
       <c r="F68" t="s">
-        <v>755</v>
+        <v>784</v>
       </c>
       <c r="G68" t="s">
-        <v>753</v>
+        <v>806</v>
       </c>
       <c r="H68" t="s">
-        <v>794</v>
+        <v>831</v>
       </c>
       <c r="I68" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -5945,28 +6055,28 @@
         <v>76</v>
       </c>
       <c r="B69" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C69" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="D69" t="s">
-        <v>520</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>668</v>
+        <v>541</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>696</v>
       </c>
       <c r="F69" t="s">
-        <v>751</v>
+        <v>800</v>
       </c>
       <c r="G69" t="s">
-        <v>751</v>
+        <v>787</v>
       </c>
       <c r="H69" t="s">
-        <v>788</v>
+        <v>826</v>
       </c>
       <c r="I69" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -5974,28 +6084,28 @@
         <v>77</v>
       </c>
       <c r="B70" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C70" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="D70" t="s">
-        <v>521</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>669</v>
+        <v>542</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>697</v>
       </c>
       <c r="F70" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G70" t="s">
-        <v>763</v>
+        <v>809</v>
       </c>
       <c r="H70" t="s">
-        <v>789</v>
+        <v>835</v>
       </c>
       <c r="I70" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -6003,28 +6113,28 @@
         <v>78</v>
       </c>
       <c r="B71" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="C71" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="D71" t="s">
-        <v>522</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>670</v>
+        <v>543</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>698</v>
       </c>
       <c r="F71" t="s">
-        <v>755</v>
+        <v>787</v>
       </c>
       <c r="G71" t="s">
-        <v>755</v>
+        <v>791</v>
       </c>
       <c r="H71" t="s">
-        <v>793</v>
+        <v>835</v>
       </c>
       <c r="I71" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -6032,28 +6142,28 @@
         <v>79</v>
       </c>
       <c r="B72" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C72" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="D72" t="s">
-        <v>523</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>671</v>
+        <v>544</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>699</v>
       </c>
       <c r="F72" t="s">
-        <v>765</v>
+        <v>791</v>
       </c>
       <c r="G72" t="s">
-        <v>767</v>
+        <v>789</v>
       </c>
       <c r="H72" t="s">
-        <v>793</v>
+        <v>831</v>
       </c>
       <c r="I72" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -6061,28 +6171,28 @@
         <v>80</v>
       </c>
       <c r="B73" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C73" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="D73" t="s">
-        <v>524</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>672</v>
+        <v>545</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>700</v>
       </c>
       <c r="F73" t="s">
-        <v>765</v>
+        <v>787</v>
       </c>
       <c r="G73" t="s">
-        <v>760</v>
+        <v>787</v>
       </c>
       <c r="H73" t="s">
-        <v>795</v>
+        <v>826</v>
       </c>
       <c r="I73" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -6090,28 +6200,28 @@
         <v>81</v>
       </c>
       <c r="B74" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="C74" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="D74" t="s">
-        <v>525</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>673</v>
+        <v>546</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>701</v>
       </c>
       <c r="F74" t="s">
-        <v>749</v>
+        <v>788</v>
       </c>
       <c r="G74" t="s">
-        <v>772</v>
+        <v>799</v>
       </c>
       <c r="H74" t="s">
-        <v>795</v>
+        <v>827</v>
       </c>
       <c r="I74" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -6119,28 +6229,28 @@
         <v>82</v>
       </c>
       <c r="B75" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C75" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="D75" t="s">
-        <v>526</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>674</v>
+        <v>547</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>702</v>
       </c>
       <c r="F75" t="s">
-        <v>755</v>
+        <v>791</v>
       </c>
       <c r="G75" t="s">
-        <v>772</v>
+        <v>791</v>
       </c>
       <c r="H75" t="s">
-        <v>792</v>
+        <v>830</v>
       </c>
       <c r="I75" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -6148,28 +6258,28 @@
         <v>83</v>
       </c>
       <c r="B76" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C76" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="D76" t="s">
-        <v>527</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>675</v>
+        <v>548</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>703</v>
       </c>
       <c r="F76" t="s">
-        <v>752</v>
+        <v>801</v>
       </c>
       <c r="G76" t="s">
-        <v>755</v>
+        <v>803</v>
       </c>
       <c r="H76" t="s">
-        <v>791</v>
+        <v>830</v>
       </c>
       <c r="I76" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -6177,28 +6287,28 @@
         <v>84</v>
       </c>
       <c r="B77" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C77" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="D77" t="s">
-        <v>528</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>676</v>
+        <v>549</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>704</v>
       </c>
       <c r="F77" t="s">
-        <v>756</v>
+        <v>801</v>
       </c>
       <c r="G77" t="s">
-        <v>756</v>
+        <v>796</v>
       </c>
       <c r="H77" t="s">
-        <v>794</v>
+        <v>832</v>
       </c>
       <c r="I77" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -6206,28 +6316,28 @@
         <v>85</v>
       </c>
       <c r="B78" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C78" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="D78" t="s">
-        <v>529</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>677</v>
+        <v>550</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>705</v>
       </c>
       <c r="F78" t="s">
-        <v>751</v>
+        <v>785</v>
       </c>
       <c r="G78" t="s">
-        <v>751</v>
+        <v>809</v>
       </c>
       <c r="H78" t="s">
-        <v>782</v>
+        <v>832</v>
       </c>
       <c r="I78" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -6235,28 +6345,28 @@
         <v>86</v>
       </c>
       <c r="B79" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C79" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="D79" t="s">
-        <v>530</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>678</v>
+        <v>551</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>706</v>
       </c>
       <c r="F79" t="s">
-        <v>752</v>
+        <v>791</v>
       </c>
       <c r="G79" t="s">
-        <v>778</v>
+        <v>809</v>
       </c>
       <c r="H79" t="s">
-        <v>797</v>
+        <v>829</v>
       </c>
       <c r="I79" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -6264,28 +6374,28 @@
         <v>87</v>
       </c>
       <c r="B80" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="C80" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="D80" t="s">
-        <v>531</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>679</v>
+        <v>552</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>707</v>
       </c>
       <c r="F80" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G80" t="s">
-        <v>752</v>
+        <v>791</v>
       </c>
       <c r="H80" t="s">
-        <v>795</v>
+        <v>828</v>
       </c>
       <c r="I80" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -6293,28 +6403,28 @@
         <v>88</v>
       </c>
       <c r="B81" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C81" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="D81" t="s">
-        <v>532</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>680</v>
+        <v>553</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>708</v>
       </c>
       <c r="F81" t="s">
-        <v>752</v>
+        <v>792</v>
       </c>
       <c r="G81" t="s">
-        <v>763</v>
+        <v>792</v>
       </c>
       <c r="H81" t="s">
-        <v>797</v>
+        <v>831</v>
       </c>
       <c r="I81" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -6322,28 +6432,28 @@
         <v>89</v>
       </c>
       <c r="B82" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C82" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="D82" t="s">
-        <v>533</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>681</v>
+        <v>554</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>709</v>
       </c>
       <c r="F82" t="s">
-        <v>752</v>
+        <v>787</v>
       </c>
       <c r="G82" t="s">
-        <v>763</v>
+        <v>787</v>
       </c>
       <c r="H82" t="s">
-        <v>793</v>
+        <v>820</v>
       </c>
       <c r="I82" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -6351,28 +6461,28 @@
         <v>90</v>
       </c>
       <c r="B83" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="C83" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="D83" t="s">
-        <v>534</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>682</v>
+        <v>555</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>710</v>
       </c>
       <c r="F83" t="s">
-        <v>751</v>
+        <v>788</v>
       </c>
       <c r="G83" t="s">
-        <v>751</v>
+        <v>815</v>
       </c>
       <c r="H83" t="s">
-        <v>797</v>
+        <v>835</v>
       </c>
       <c r="I83" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -6380,28 +6490,28 @@
         <v>91</v>
       </c>
       <c r="B84" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="C84" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="D84" t="s">
-        <v>535</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>683</v>
+        <v>556</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>711</v>
       </c>
       <c r="F84" t="s">
-        <v>751</v>
+        <v>788</v>
       </c>
       <c r="G84" t="s">
-        <v>751</v>
+        <v>788</v>
       </c>
       <c r="H84" t="s">
-        <v>798</v>
+        <v>832</v>
       </c>
       <c r="I84" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -6409,28 +6519,28 @@
         <v>92</v>
       </c>
       <c r="B85" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C85" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="D85" t="s">
-        <v>536</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>684</v>
+        <v>557</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>712</v>
       </c>
       <c r="F85" t="s">
-        <v>755</v>
+        <v>788</v>
       </c>
       <c r="G85" t="s">
-        <v>755</v>
+        <v>799</v>
       </c>
       <c r="H85" t="s">
-        <v>787</v>
+        <v>835</v>
       </c>
       <c r="I85" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -6438,28 +6548,28 @@
         <v>93</v>
       </c>
       <c r="B86" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C86" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="D86" t="s">
-        <v>537</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>685</v>
+        <v>558</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>713</v>
       </c>
       <c r="F86" t="s">
-        <v>751</v>
+        <v>788</v>
       </c>
       <c r="G86" t="s">
-        <v>769</v>
+        <v>799</v>
       </c>
       <c r="H86" t="s">
-        <v>782</v>
+        <v>830</v>
       </c>
       <c r="I86" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -6467,28 +6577,28 @@
         <v>94</v>
       </c>
       <c r="B87" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="C87" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="D87" t="s">
-        <v>538</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>686</v>
+        <v>559</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>714</v>
       </c>
       <c r="F87" t="s">
-        <v>755</v>
+        <v>787</v>
       </c>
       <c r="G87" t="s">
-        <v>761</v>
+        <v>787</v>
       </c>
       <c r="H87" t="s">
-        <v>794</v>
+        <v>835</v>
       </c>
       <c r="I87" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -6496,28 +6606,28 @@
         <v>95</v>
       </c>
       <c r="B88" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C88" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="D88" t="s">
-        <v>539</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>687</v>
+        <v>560</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>715</v>
       </c>
       <c r="F88" t="s">
-        <v>755</v>
+        <v>787</v>
       </c>
       <c r="G88" t="s">
-        <v>755</v>
+        <v>787</v>
       </c>
       <c r="H88" t="s">
-        <v>783</v>
+        <v>836</v>
       </c>
       <c r="I88" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -6525,28 +6635,28 @@
         <v>96</v>
       </c>
       <c r="B89" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="C89" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="D89" t="s">
-        <v>540</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>688</v>
+        <v>561</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>716</v>
       </c>
       <c r="F89" t="s">
-        <v>766</v>
+        <v>791</v>
       </c>
       <c r="G89" t="s">
-        <v>766</v>
+        <v>791</v>
       </c>
       <c r="H89" t="s">
-        <v>797</v>
+        <v>825</v>
       </c>
       <c r="I89" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -6554,28 +6664,28 @@
         <v>97</v>
       </c>
       <c r="B90" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C90" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="D90" t="s">
-        <v>541</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>689</v>
+        <v>562</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>717</v>
       </c>
       <c r="F90" t="s">
-        <v>755</v>
+        <v>787</v>
       </c>
       <c r="G90" t="s">
-        <v>755</v>
+        <v>805</v>
       </c>
       <c r="H90" t="s">
-        <v>794</v>
+        <v>820</v>
       </c>
       <c r="I90" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -6583,28 +6693,28 @@
         <v>98</v>
       </c>
       <c r="B91" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="C91" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="D91" t="s">
-        <v>542</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>690</v>
+        <v>563</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>718</v>
       </c>
       <c r="F91" t="s">
-        <v>755</v>
+        <v>791</v>
       </c>
       <c r="G91" t="s">
-        <v>755</v>
+        <v>797</v>
       </c>
       <c r="H91" t="s">
-        <v>788</v>
+        <v>831</v>
       </c>
       <c r="I91" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -6612,28 +6722,28 @@
         <v>99</v>
       </c>
       <c r="B92" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="C92" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="D92" t="s">
-        <v>543</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>691</v>
+        <v>564</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>719</v>
       </c>
       <c r="F92" t="s">
-        <v>752</v>
+        <v>791</v>
       </c>
       <c r="G92" t="s">
-        <v>756</v>
+        <v>791</v>
       </c>
       <c r="H92" t="s">
-        <v>799</v>
+        <v>821</v>
       </c>
       <c r="I92" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -6641,28 +6751,28 @@
         <v>100</v>
       </c>
       <c r="B93" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="C93" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="D93" t="s">
-        <v>544</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>692</v>
+        <v>565</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>720</v>
       </c>
       <c r="F93" t="s">
-        <v>767</v>
+        <v>802</v>
       </c>
       <c r="G93" t="s">
-        <v>760</v>
+        <v>802</v>
       </c>
       <c r="H93" t="s">
-        <v>794</v>
+        <v>835</v>
       </c>
       <c r="I93" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -6670,28 +6780,28 @@
         <v>101</v>
       </c>
       <c r="B94" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="C94" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="D94" t="s">
-        <v>545</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>693</v>
+        <v>566</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>721</v>
       </c>
       <c r="F94" t="s">
-        <v>752</v>
+        <v>791</v>
       </c>
       <c r="G94" t="s">
-        <v>752</v>
+        <v>791</v>
       </c>
       <c r="H94" t="s">
-        <v>795</v>
+        <v>831</v>
       </c>
       <c r="I94" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -6699,28 +6809,28 @@
         <v>102</v>
       </c>
       <c r="B95" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="C95" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="D95" t="s">
-        <v>546</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>694</v>
+        <v>567</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>722</v>
       </c>
       <c r="F95" t="s">
-        <v>756</v>
+        <v>784</v>
       </c>
       <c r="G95" t="s">
-        <v>756</v>
+        <v>806</v>
       </c>
       <c r="H95" t="s">
-        <v>794</v>
+        <v>825</v>
       </c>
       <c r="I95" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -6728,28 +6838,28 @@
         <v>103</v>
       </c>
       <c r="B96" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C96" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="D96" t="s">
-        <v>547</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>695</v>
+        <v>568</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>723</v>
       </c>
       <c r="F96" t="s">
-        <v>750</v>
+        <v>791</v>
       </c>
       <c r="G96" t="s">
-        <v>750</v>
+        <v>791</v>
       </c>
       <c r="H96" t="s">
-        <v>783</v>
+        <v>826</v>
       </c>
       <c r="I96" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -6757,28 +6867,28 @@
         <v>104</v>
       </c>
       <c r="B97" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C97" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="D97" t="s">
-        <v>548</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>696</v>
+        <v>569</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>724</v>
       </c>
       <c r="F97" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G97" t="s">
-        <v>763</v>
+        <v>792</v>
       </c>
       <c r="H97" t="s">
-        <v>791</v>
+        <v>837</v>
       </c>
       <c r="I97" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -6786,28 +6896,28 @@
         <v>105</v>
       </c>
       <c r="B98" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="C98" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="D98" t="s">
-        <v>549</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>697</v>
+        <v>570</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>725</v>
       </c>
       <c r="F98" t="s">
-        <v>752</v>
+        <v>803</v>
       </c>
       <c r="G98" t="s">
-        <v>757</v>
+        <v>796</v>
       </c>
       <c r="H98" t="s">
-        <v>787</v>
+        <v>831</v>
       </c>
       <c r="I98" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -6815,28 +6925,28 @@
         <v>106</v>
       </c>
       <c r="B99" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="C99" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="D99" t="s">
-        <v>550</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>698</v>
+        <v>571</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>726</v>
       </c>
       <c r="F99" t="s">
-        <v>750</v>
+        <v>788</v>
       </c>
       <c r="G99" t="s">
-        <v>750</v>
+        <v>788</v>
       </c>
       <c r="H99" t="s">
-        <v>783</v>
+        <v>832</v>
       </c>
       <c r="I99" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -6844,28 +6954,28 @@
         <v>107</v>
       </c>
       <c r="B100" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C100" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="D100" t="s">
-        <v>551</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>699</v>
+        <v>572</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>727</v>
       </c>
       <c r="F100" t="s">
-        <v>752</v>
+        <v>792</v>
       </c>
       <c r="G100" t="s">
-        <v>758</v>
+        <v>792</v>
       </c>
       <c r="H100" t="s">
-        <v>799</v>
+        <v>831</v>
       </c>
       <c r="I100" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -6873,28 +6983,28 @@
         <v>108</v>
       </c>
       <c r="B101" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C101" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="D101" t="s">
-        <v>552</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>700</v>
+        <v>573</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>728</v>
       </c>
       <c r="F101" t="s">
-        <v>767</v>
+        <v>786</v>
       </c>
       <c r="G101" t="s">
-        <v>760</v>
+        <v>786</v>
       </c>
       <c r="H101" t="s">
-        <v>784</v>
+        <v>821</v>
       </c>
       <c r="I101" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -6902,28 +7012,28 @@
         <v>109</v>
       </c>
       <c r="B102" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C102" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="D102" t="s">
-        <v>553</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>701</v>
+        <v>574</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>729</v>
       </c>
       <c r="F102" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G102" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
       <c r="H102" t="s">
-        <v>787</v>
+        <v>828</v>
       </c>
       <c r="I102" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -6931,28 +7041,28 @@
         <v>110</v>
       </c>
       <c r="B103" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="C103" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="D103" t="s">
-        <v>554</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>702</v>
+        <v>575</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>730</v>
       </c>
       <c r="F103" t="s">
-        <v>751</v>
+        <v>788</v>
       </c>
       <c r="G103" t="s">
-        <v>779</v>
+        <v>793</v>
       </c>
       <c r="H103" t="s">
-        <v>800</v>
+        <v>825</v>
       </c>
       <c r="I103" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -6960,28 +7070,28 @@
         <v>111</v>
       </c>
       <c r="B104" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="C104" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="D104" t="s">
-        <v>555</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>703</v>
+        <v>576</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>731</v>
       </c>
       <c r="F104" t="s">
-        <v>755</v>
+        <v>786</v>
       </c>
       <c r="G104" t="s">
-        <v>755</v>
+        <v>806</v>
       </c>
       <c r="H104" t="s">
-        <v>792</v>
+        <v>838</v>
       </c>
       <c r="I104" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -6989,28 +7099,28 @@
         <v>112</v>
       </c>
       <c r="B105" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="C105" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="D105" t="s">
-        <v>556</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>704</v>
+        <v>577</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>732</v>
       </c>
       <c r="F105" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G105" t="s">
-        <v>752</v>
+        <v>794</v>
       </c>
       <c r="H105" t="s">
-        <v>789</v>
+        <v>837</v>
       </c>
       <c r="I105" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -7018,28 +7128,28 @@
         <v>113</v>
       </c>
       <c r="B106" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="C106" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="D106" t="s">
-        <v>557</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>705</v>
+        <v>578</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>733</v>
       </c>
       <c r="F106" t="s">
-        <v>752</v>
+        <v>803</v>
       </c>
       <c r="G106" t="s">
-        <v>772</v>
+        <v>796</v>
       </c>
       <c r="H106" t="s">
-        <v>799</v>
+        <v>822</v>
       </c>
       <c r="I106" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -7047,28 +7157,28 @@
         <v>114</v>
       </c>
       <c r="B107" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="C107" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="D107" t="s">
-        <v>558</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>706</v>
+        <v>579</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>734</v>
       </c>
       <c r="F107" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G107" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
       <c r="H107" t="s">
-        <v>801</v>
+        <v>825</v>
       </c>
       <c r="I107" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -7076,28 +7186,28 @@
         <v>115</v>
       </c>
       <c r="B108" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="C108" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="D108" t="s">
-        <v>559</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>707</v>
+        <v>580</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>735</v>
       </c>
       <c r="F108" t="s">
-        <v>752</v>
+        <v>787</v>
       </c>
       <c r="G108" t="s">
-        <v>752</v>
+        <v>816</v>
       </c>
       <c r="H108" t="s">
-        <v>793</v>
+        <v>839</v>
       </c>
       <c r="I108" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -7105,28 +7215,28 @@
         <v>116</v>
       </c>
       <c r="B109" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="C109" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="D109" t="s">
-        <v>560</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>708</v>
+        <v>581</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>736</v>
       </c>
       <c r="F109" t="s">
-        <v>767</v>
+        <v>791</v>
       </c>
       <c r="G109" t="s">
-        <v>760</v>
+        <v>791</v>
       </c>
       <c r="H109" t="s">
-        <v>792</v>
+        <v>829</v>
       </c>
       <c r="I109" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -7134,28 +7244,28 @@
         <v>117</v>
       </c>
       <c r="B110" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C110" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="D110" t="s">
-        <v>561</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>709</v>
+        <v>582</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>737</v>
       </c>
       <c r="F110" t="s">
-        <v>768</v>
+        <v>788</v>
       </c>
       <c r="G110" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="H110" t="s">
-        <v>802</v>
+        <v>827</v>
       </c>
       <c r="I110" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -7163,28 +7273,28 @@
         <v>118</v>
       </c>
       <c r="B111" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C111" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="D111" t="s">
-        <v>562</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>710</v>
+        <v>583</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>738</v>
       </c>
       <c r="F111" t="s">
-        <v>755</v>
+        <v>788</v>
       </c>
       <c r="G111" t="s">
-        <v>765</v>
+        <v>809</v>
       </c>
       <c r="H111" t="s">
-        <v>787</v>
+        <v>837</v>
       </c>
       <c r="I111" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -7192,28 +7302,28 @@
         <v>119</v>
       </c>
       <c r="B112" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C112" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="D112" t="s">
-        <v>563</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>711</v>
+        <v>584</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>739</v>
       </c>
       <c r="F112" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G112" t="s">
-        <v>752</v>
+        <v>799</v>
       </c>
       <c r="H112" t="s">
-        <v>787</v>
+        <v>840</v>
       </c>
       <c r="I112" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -7221,28 +7331,28 @@
         <v>120</v>
       </c>
       <c r="B113" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C113" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="D113" t="s">
-        <v>564</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>712</v>
+        <v>585</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>740</v>
       </c>
       <c r="F113" t="s">
-        <v>755</v>
+        <v>784</v>
       </c>
       <c r="G113" t="s">
-        <v>755</v>
+        <v>806</v>
       </c>
       <c r="H113" t="s">
-        <v>787</v>
+        <v>825</v>
       </c>
       <c r="I113" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -7250,28 +7360,28 @@
         <v>121</v>
       </c>
       <c r="B114" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C114" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="D114" t="s">
-        <v>565</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>713</v>
+        <v>586</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>741</v>
       </c>
       <c r="F114" t="s">
-        <v>750</v>
+        <v>788</v>
       </c>
       <c r="G114" t="s">
-        <v>750</v>
+        <v>788</v>
       </c>
       <c r="H114" t="s">
-        <v>784</v>
+        <v>830</v>
       </c>
       <c r="I114" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -7279,28 +7389,28 @@
         <v>122</v>
       </c>
       <c r="B115" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="C115" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="D115" t="s">
-        <v>566</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>714</v>
+        <v>587</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>742</v>
       </c>
       <c r="F115" t="s">
-        <v>750</v>
+        <v>803</v>
       </c>
       <c r="G115" t="s">
-        <v>750</v>
+        <v>796</v>
       </c>
       <c r="H115" t="s">
-        <v>786</v>
+        <v>829</v>
       </c>
       <c r="I115" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -7308,28 +7418,28 @@
         <v>123</v>
       </c>
       <c r="B116" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C116" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="D116" t="s">
-        <v>567</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>715</v>
+        <v>588</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>743</v>
       </c>
       <c r="F116" t="s">
-        <v>755</v>
+        <v>804</v>
       </c>
       <c r="G116" t="s">
-        <v>755</v>
+        <v>817</v>
       </c>
       <c r="H116" t="s">
-        <v>783</v>
+        <v>841</v>
       </c>
       <c r="I116" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -7337,28 +7447,28 @@
         <v>124</v>
       </c>
       <c r="B117" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="C117" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="D117" t="s">
-        <v>568</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>716</v>
+        <v>589</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>744</v>
       </c>
       <c r="F117" t="s">
-        <v>751</v>
+        <v>791</v>
       </c>
       <c r="G117" t="s">
-        <v>751</v>
+        <v>801</v>
       </c>
       <c r="H117" t="s">
-        <v>788</v>
+        <v>825</v>
       </c>
       <c r="I117" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -7366,28 +7476,28 @@
         <v>125</v>
       </c>
       <c r="B118" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="C118" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="D118" t="s">
-        <v>569</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>717</v>
+        <v>590</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>745</v>
       </c>
       <c r="F118" t="s">
-        <v>755</v>
+        <v>784</v>
       </c>
       <c r="G118" t="s">
-        <v>755</v>
+        <v>806</v>
       </c>
       <c r="H118" t="s">
-        <v>787</v>
+        <v>825</v>
       </c>
       <c r="I118" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -7395,28 +7505,28 @@
         <v>126</v>
       </c>
       <c r="B119" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="C119" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="D119" t="s">
-        <v>570</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>718</v>
+        <v>591</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>746</v>
       </c>
       <c r="F119" t="s">
-        <v>758</v>
+        <v>788</v>
       </c>
       <c r="G119" t="s">
-        <v>756</v>
+        <v>788</v>
       </c>
       <c r="H119" t="s">
-        <v>790</v>
+        <v>825</v>
       </c>
       <c r="I119" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -7424,28 +7534,28 @@
         <v>127</v>
       </c>
       <c r="B120" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="C120" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="D120" t="s">
-        <v>571</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>719</v>
+        <v>592</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>747</v>
       </c>
       <c r="F120" t="s">
-        <v>752</v>
+        <v>791</v>
       </c>
       <c r="G120" t="s">
-        <v>770</v>
+        <v>791</v>
       </c>
       <c r="H120" t="s">
-        <v>793</v>
+        <v>825</v>
       </c>
       <c r="I120" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -7453,28 +7563,28 @@
         <v>128</v>
       </c>
       <c r="B121" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="C121" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="D121" t="s">
-        <v>572</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>720</v>
+        <v>593</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>748</v>
       </c>
       <c r="F121" t="s">
-        <v>752</v>
+        <v>786</v>
       </c>
       <c r="G121" t="s">
-        <v>777</v>
+        <v>786</v>
       </c>
       <c r="H121" t="s">
-        <v>793</v>
+        <v>822</v>
       </c>
       <c r="I121" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -7482,28 +7592,28 @@
         <v>129</v>
       </c>
       <c r="B122" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="C122" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="D122" t="s">
-        <v>573</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>721</v>
+        <v>594</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>749</v>
       </c>
       <c r="F122" t="s">
-        <v>752</v>
+        <v>786</v>
       </c>
       <c r="G122" t="s">
-        <v>763</v>
+        <v>786</v>
       </c>
       <c r="H122" t="s">
-        <v>793</v>
+        <v>824</v>
       </c>
       <c r="I122" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -7511,28 +7621,28 @@
         <v>130</v>
       </c>
       <c r="B123" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="C123" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="D123" t="s">
-        <v>574</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>722</v>
+        <v>595</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>750</v>
       </c>
       <c r="F123" t="s">
-        <v>769</v>
+        <v>791</v>
       </c>
       <c r="G123" t="s">
-        <v>778</v>
+        <v>791</v>
       </c>
       <c r="H123" t="s">
-        <v>793</v>
+        <v>821</v>
       </c>
       <c r="I123" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -7540,28 +7650,28 @@
         <v>131</v>
       </c>
       <c r="B124" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="C124" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="D124" t="s">
-        <v>575</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>723</v>
+        <v>596</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>751</v>
       </c>
       <c r="F124" t="s">
-        <v>752</v>
+        <v>787</v>
       </c>
       <c r="G124" t="s">
-        <v>763</v>
+        <v>787</v>
       </c>
       <c r="H124" t="s">
-        <v>793</v>
+        <v>826</v>
       </c>
       <c r="I124" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -7569,28 +7679,28 @@
         <v>132</v>
       </c>
       <c r="B125" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="C125" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="D125" t="s">
-        <v>576</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>724</v>
+        <v>597</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>752</v>
       </c>
       <c r="F125" t="s">
-        <v>766</v>
+        <v>791</v>
       </c>
       <c r="G125" t="s">
-        <v>766</v>
+        <v>791</v>
       </c>
       <c r="H125" t="s">
-        <v>797</v>
+        <v>825</v>
       </c>
       <c r="I125" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -7598,28 +7708,28 @@
         <v>133</v>
       </c>
       <c r="B126" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="C126" t="s">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="D126" t="s">
-        <v>577</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>725</v>
+        <v>598</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>753</v>
       </c>
       <c r="F126" t="s">
-        <v>751</v>
+        <v>794</v>
       </c>
       <c r="G126" t="s">
-        <v>751</v>
+        <v>792</v>
       </c>
       <c r="H126" t="s">
-        <v>788</v>
+        <v>819</v>
       </c>
       <c r="I126" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -7627,28 +7737,28 @@
         <v>134</v>
       </c>
       <c r="B127" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="C127" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="D127" t="s">
-        <v>578</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>726</v>
+        <v>599</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>754</v>
       </c>
       <c r="F127" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G127" t="s">
-        <v>763</v>
+        <v>807</v>
       </c>
       <c r="H127" t="s">
-        <v>787</v>
+        <v>830</v>
       </c>
       <c r="I127" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -7656,28 +7766,28 @@
         <v>135</v>
       </c>
       <c r="B128" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="C128" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="D128" t="s">
-        <v>579</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>727</v>
+        <v>600</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>755</v>
       </c>
       <c r="F128" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G128" t="s">
-        <v>780</v>
+        <v>814</v>
       </c>
       <c r="H128" t="s">
-        <v>788</v>
+        <v>830</v>
       </c>
       <c r="I128" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -7685,28 +7795,28 @@
         <v>136</v>
       </c>
       <c r="B129" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="C129" t="s">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="D129" t="s">
-        <v>580</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>728</v>
+        <v>601</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>756</v>
       </c>
       <c r="F129" t="s">
-        <v>751</v>
+        <v>788</v>
       </c>
       <c r="G129" t="s">
-        <v>751</v>
+        <v>799</v>
       </c>
       <c r="H129" t="s">
-        <v>800</v>
+        <v>830</v>
       </c>
       <c r="I129" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -7714,28 +7824,28 @@
         <v>137</v>
       </c>
       <c r="B130" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="C130" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="D130" t="s">
-        <v>581</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>729</v>
+        <v>602</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>757</v>
       </c>
       <c r="F130" t="s">
-        <v>755</v>
+        <v>805</v>
       </c>
       <c r="G130" t="s">
-        <v>755</v>
+        <v>815</v>
       </c>
       <c r="H130" t="s">
-        <v>792</v>
+        <v>830</v>
       </c>
       <c r="I130" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -7743,28 +7853,28 @@
         <v>138</v>
       </c>
       <c r="B131" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="C131" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="D131" t="s">
-        <v>582</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>730</v>
+        <v>603</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>758</v>
       </c>
       <c r="F131" t="s">
-        <v>762</v>
+        <v>788</v>
       </c>
       <c r="G131" t="s">
-        <v>777</v>
+        <v>799</v>
       </c>
       <c r="H131" t="s">
-        <v>787</v>
+        <v>830</v>
       </c>
       <c r="I131" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -7772,28 +7882,28 @@
         <v>139</v>
       </c>
       <c r="B132" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="C132" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="D132" t="s">
-        <v>583</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>731</v>
+        <v>604</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>759</v>
       </c>
       <c r="F132" t="s">
-        <v>755</v>
+        <v>802</v>
       </c>
       <c r="G132" t="s">
-        <v>755</v>
+        <v>802</v>
       </c>
       <c r="H132" t="s">
-        <v>792</v>
+        <v>835</v>
       </c>
       <c r="I132" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -7801,28 +7911,28 @@
         <v>140</v>
       </c>
       <c r="B133" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="C133" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="D133" t="s">
-        <v>584</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>732</v>
+        <v>605</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>760</v>
       </c>
       <c r="F133" t="s">
-        <v>755</v>
+        <v>787</v>
       </c>
       <c r="G133" t="s">
-        <v>755</v>
+        <v>787</v>
       </c>
       <c r="H133" t="s">
-        <v>792</v>
+        <v>826</v>
       </c>
       <c r="I133" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -7830,28 +7940,28 @@
         <v>141</v>
       </c>
       <c r="B134" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="C134" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="D134" t="s">
-        <v>585</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>733</v>
+        <v>606</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>761</v>
       </c>
       <c r="F134" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G134" t="s">
-        <v>770</v>
+        <v>799</v>
       </c>
       <c r="H134" t="s">
-        <v>793</v>
+        <v>825</v>
       </c>
       <c r="I134" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -7859,28 +7969,28 @@
         <v>142</v>
       </c>
       <c r="B135" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="C135" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="D135" t="s">
-        <v>586</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>734</v>
+        <v>607</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>762</v>
       </c>
       <c r="F135" t="s">
-        <v>750</v>
+        <v>788</v>
       </c>
       <c r="G135" t="s">
-        <v>750</v>
+        <v>817</v>
       </c>
       <c r="H135" t="s">
-        <v>783</v>
+        <v>826</v>
       </c>
       <c r="I135" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -7888,28 +7998,28 @@
         <v>143</v>
       </c>
       <c r="B136" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="C136" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="D136" t="s">
-        <v>587</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>735</v>
+        <v>608</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>763</v>
       </c>
       <c r="F136" t="s">
-        <v>750</v>
+        <v>787</v>
       </c>
       <c r="G136" t="s">
-        <v>750</v>
+        <v>787</v>
       </c>
       <c r="H136" t="s">
-        <v>792</v>
+        <v>839</v>
       </c>
       <c r="I136" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -7917,28 +8027,28 @@
         <v>144</v>
       </c>
       <c r="B137" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="C137" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="D137" t="s">
-        <v>588</v>
-      </c>
-      <c r="E137" s="2" t="s">
-        <v>736</v>
+        <v>609</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>764</v>
       </c>
       <c r="F137" t="s">
-        <v>752</v>
+        <v>791</v>
       </c>
       <c r="G137" t="s">
-        <v>763</v>
+        <v>791</v>
       </c>
       <c r="H137" t="s">
-        <v>795</v>
+        <v>829</v>
       </c>
       <c r="I137" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -7946,28 +8056,28 @@
         <v>145</v>
       </c>
       <c r="B138" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="C138" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="D138" t="s">
-        <v>589</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>737</v>
+        <v>610</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>765</v>
       </c>
       <c r="F138" t="s">
-        <v>752</v>
+        <v>798</v>
       </c>
       <c r="G138" t="s">
-        <v>752</v>
+        <v>814</v>
       </c>
       <c r="H138" t="s">
-        <v>795</v>
+        <v>825</v>
       </c>
       <c r="I138" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -7975,28 +8085,28 @@
         <v>146</v>
       </c>
       <c r="B139" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="C139" t="s">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="D139" t="s">
-        <v>590</v>
-      </c>
-      <c r="E139" s="2" t="s">
-        <v>738</v>
+        <v>611</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>766</v>
       </c>
       <c r="F139" t="s">
-        <v>760</v>
+        <v>791</v>
       </c>
       <c r="G139" t="s">
-        <v>769</v>
+        <v>791</v>
       </c>
       <c r="H139" t="s">
-        <v>794</v>
+        <v>829</v>
       </c>
       <c r="I139" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -8004,28 +8114,28 @@
         <v>147</v>
       </c>
       <c r="B140" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="C140" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="D140" t="s">
-        <v>591</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>739</v>
+        <v>612</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>767</v>
       </c>
       <c r="F140" t="s">
-        <v>752</v>
+        <v>791</v>
       </c>
       <c r="G140" t="s">
-        <v>763</v>
+        <v>791</v>
       </c>
       <c r="H140" t="s">
-        <v>782</v>
+        <v>829</v>
       </c>
       <c r="I140" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -8033,28 +8143,28 @@
         <v>148</v>
       </c>
       <c r="B141" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C141" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="D141" t="s">
-        <v>592</v>
-      </c>
-      <c r="E141" s="2" t="s">
-        <v>740</v>
+        <v>613</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>768</v>
       </c>
       <c r="F141" t="s">
-        <v>751</v>
+        <v>788</v>
       </c>
       <c r="G141" t="s">
-        <v>781</v>
+        <v>807</v>
       </c>
       <c r="H141" t="s">
-        <v>784</v>
+        <v>830</v>
       </c>
       <c r="I141" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -8062,28 +8172,28 @@
         <v>149</v>
       </c>
       <c r="B142" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="C142" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="D142" t="s">
-        <v>593</v>
-      </c>
-      <c r="E142" s="2" t="s">
-        <v>741</v>
+        <v>614</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>769</v>
       </c>
       <c r="F142" t="s">
-        <v>767</v>
+        <v>786</v>
       </c>
       <c r="G142" t="s">
-        <v>760</v>
+        <v>786</v>
       </c>
       <c r="H142" t="s">
-        <v>803</v>
+        <v>821</v>
       </c>
       <c r="I142" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -8091,28 +8201,28 @@
         <v>150</v>
       </c>
       <c r="B143" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="C143" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="D143" t="s">
-        <v>594</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>742</v>
+        <v>615</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>770</v>
       </c>
       <c r="F143" t="s">
-        <v>752</v>
+        <v>786</v>
       </c>
       <c r="G143" t="s">
-        <v>752</v>
+        <v>786</v>
       </c>
       <c r="H143" t="s">
-        <v>795</v>
+        <v>829</v>
       </c>
       <c r="I143" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -8120,28 +8230,28 @@
         <v>151</v>
       </c>
       <c r="B144" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="C144" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="D144" t="s">
-        <v>595</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>743</v>
+        <v>616</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>771</v>
       </c>
       <c r="F144" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G144" t="s">
-        <v>776</v>
+        <v>799</v>
       </c>
       <c r="H144" t="s">
-        <v>782</v>
+        <v>832</v>
       </c>
       <c r="I144" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -8149,28 +8259,28 @@
         <v>152</v>
       </c>
       <c r="B145" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="C145" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="D145" t="s">
-        <v>596</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>744</v>
+        <v>617</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>772</v>
       </c>
       <c r="F145" t="s">
-        <v>751</v>
+        <v>788</v>
       </c>
       <c r="G145" t="s">
-        <v>751</v>
+        <v>788</v>
       </c>
       <c r="H145" t="s">
-        <v>788</v>
+        <v>832</v>
       </c>
       <c r="I145" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -8178,28 +8288,28 @@
         <v>153</v>
       </c>
       <c r="B146" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="C146" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="D146" t="s">
-        <v>597</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>745</v>
+        <v>618</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>773</v>
       </c>
       <c r="F146" t="s">
-        <v>759</v>
+        <v>796</v>
       </c>
       <c r="G146" t="s">
-        <v>753</v>
+        <v>805</v>
       </c>
       <c r="H146" t="s">
-        <v>804</v>
+        <v>831</v>
       </c>
       <c r="I146" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -8207,28 +8317,28 @@
         <v>154</v>
       </c>
       <c r="B147" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="C147" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="D147" t="s">
-        <v>598</v>
-      </c>
-      <c r="E147" s="2" t="s">
-        <v>746</v>
+        <v>619</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>774</v>
       </c>
       <c r="F147" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G147" t="s">
-        <v>752</v>
+        <v>799</v>
       </c>
       <c r="H147" t="s">
-        <v>795</v>
+        <v>820</v>
       </c>
       <c r="I147" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -8236,28 +8346,28 @@
         <v>155</v>
       </c>
       <c r="B148" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="C148" t="s">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="D148" t="s">
-        <v>599</v>
-      </c>
-      <c r="E148" s="2" t="s">
-        <v>747</v>
+        <v>620</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>775</v>
       </c>
       <c r="F148" t="s">
-        <v>749</v>
+        <v>787</v>
       </c>
       <c r="G148" t="s">
-        <v>772</v>
+        <v>818</v>
       </c>
       <c r="H148" t="s">
-        <v>794</v>
+        <v>822</v>
       </c>
       <c r="I148" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -8265,28 +8375,231 @@
         <v>156</v>
       </c>
       <c r="B149" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="C149" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="D149" t="s">
-        <v>600</v>
-      </c>
-      <c r="E149" s="2" t="s">
-        <v>748</v>
+        <v>621</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>776</v>
       </c>
       <c r="F149" t="s">
-        <v>752</v>
+        <v>803</v>
       </c>
       <c r="G149" t="s">
-        <v>774</v>
+        <v>796</v>
       </c>
       <c r="H149" t="s">
+        <v>842</v>
+      </c>
+      <c r="I149" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
+      <c r="A150" t="s">
+        <v>157</v>
+      </c>
+      <c r="B150" t="s">
+        <v>312</v>
+      </c>
+      <c r="C150" t="s">
+        <v>467</v>
+      </c>
+      <c r="D150" t="s">
+        <v>622</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="F150" t="s">
+        <v>788</v>
+      </c>
+      <c r="G150" t="s">
+        <v>788</v>
+      </c>
+      <c r="H150" t="s">
+        <v>832</v>
+      </c>
+      <c r="I150" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
+      <c r="A151" t="s">
+        <v>158</v>
+      </c>
+      <c r="B151" t="s">
+        <v>313</v>
+      </c>
+      <c r="C151" t="s">
+        <v>468</v>
+      </c>
+      <c r="D151" t="s">
+        <v>623</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="F151" t="s">
+        <v>788</v>
+      </c>
+      <c r="G151" t="s">
+        <v>813</v>
+      </c>
+      <c r="H151" t="s">
+        <v>820</v>
+      </c>
+      <c r="I151" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9">
+      <c r="A152" t="s">
+        <v>159</v>
+      </c>
+      <c r="B152" t="s">
+        <v>314</v>
+      </c>
+      <c r="C152" t="s">
+        <v>469</v>
+      </c>
+      <c r="D152" t="s">
+        <v>624</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="F152" t="s">
+        <v>787</v>
+      </c>
+      <c r="G152" t="s">
+        <v>787</v>
+      </c>
+      <c r="H152" t="s">
+        <v>826</v>
+      </c>
+      <c r="I152" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9">
+      <c r="A153" t="s">
+        <v>160</v>
+      </c>
+      <c r="B153" t="s">
+        <v>315</v>
+      </c>
+      <c r="C153" t="s">
+        <v>470</v>
+      </c>
+      <c r="D153" t="s">
+        <v>625</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="F153" t="s">
         <v>795</v>
       </c>
-      <c r="I149" t="s">
-        <v>805</v>
+      <c r="G153" t="s">
+        <v>789</v>
+      </c>
+      <c r="H153" t="s">
+        <v>843</v>
+      </c>
+      <c r="I153" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9">
+      <c r="A154" t="s">
+        <v>161</v>
+      </c>
+      <c r="B154" t="s">
+        <v>316</v>
+      </c>
+      <c r="C154" t="s">
+        <v>471</v>
+      </c>
+      <c r="D154" t="s">
+        <v>626</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="F154" t="s">
+        <v>788</v>
+      </c>
+      <c r="G154" t="s">
+        <v>788</v>
+      </c>
+      <c r="H154" t="s">
+        <v>832</v>
+      </c>
+      <c r="I154" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
+      <c r="A155" t="s">
+        <v>162</v>
+      </c>
+      <c r="B155" t="s">
+        <v>317</v>
+      </c>
+      <c r="C155" t="s">
+        <v>472</v>
+      </c>
+      <c r="D155" t="s">
+        <v>627</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="F155" t="s">
+        <v>785</v>
+      </c>
+      <c r="G155" t="s">
+        <v>809</v>
+      </c>
+      <c r="H155" t="s">
+        <v>831</v>
+      </c>
+      <c r="I155" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9">
+      <c r="A156" t="s">
+        <v>163</v>
+      </c>
+      <c r="B156" t="s">
+        <v>318</v>
+      </c>
+      <c r="C156" t="s">
+        <v>473</v>
+      </c>
+      <c r="D156" t="s">
+        <v>628</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="F156" t="s">
+        <v>788</v>
+      </c>
+      <c r="G156" t="s">
+        <v>811</v>
+      </c>
+      <c r="H156" t="s">
+        <v>832</v>
+      </c>
+      <c r="I156" t="s">
+        <v>844</v>
       </c>
     </row>
   </sheetData>
@@ -8439,6 +8752,13 @@
     <hyperlink ref="E147" r:id="rId146"/>
     <hyperlink ref="E148" r:id="rId147"/>
     <hyperlink ref="E149" r:id="rId148"/>
+    <hyperlink ref="E150" r:id="rId149"/>
+    <hyperlink ref="E151" r:id="rId150"/>
+    <hyperlink ref="E152" r:id="rId151"/>
+    <hyperlink ref="E153" r:id="rId152"/>
+    <hyperlink ref="E154" r:id="rId153"/>
+    <hyperlink ref="E155" r:id="rId154"/>
+    <hyperlink ref="E156" r:id="rId155"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8450,394 +8770,394 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>806</v>
+        <v>845</v>
       </c>
       <c r="B2" t="s">
-        <v>822</v>
+        <v>861</v>
       </c>
       <c r="C2" t="s">
-        <v>795</v>
+        <v>832</v>
       </c>
       <c r="D2" t="s">
-        <v>839</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>855</v>
+        <v>877</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>893</v>
       </c>
       <c r="F2" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G2" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
+        <v>846</v>
+      </c>
+      <c r="B3" t="s">
+        <v>862</v>
+      </c>
+      <c r="C3" t="s">
+        <v>827</v>
+      </c>
+      <c r="D3" t="s">
+        <v>878</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="F3" t="s">
+        <v>788</v>
+      </c>
+      <c r="G3" t="s">
         <v>807</v>
-      </c>
-      <c r="B3" t="s">
-        <v>823</v>
-      </c>
-      <c r="C3" t="s">
-        <v>789</v>
-      </c>
-      <c r="D3" t="s">
-        <v>840</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="F3" t="s">
-        <v>752</v>
-      </c>
-      <c r="G3" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>808</v>
+        <v>847</v>
       </c>
       <c r="B4" t="s">
+        <v>863</v>
+      </c>
+      <c r="C4" t="s">
         <v>824</v>
       </c>
-      <c r="C4" t="s">
-        <v>786</v>
-      </c>
       <c r="D4" t="s">
-        <v>841</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>857</v>
+        <v>879</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>895</v>
       </c>
       <c r="F4" t="s">
-        <v>759</v>
+        <v>795</v>
       </c>
       <c r="G4" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>809</v>
+        <v>848</v>
       </c>
       <c r="B5" t="s">
-        <v>825</v>
+        <v>864</v>
       </c>
       <c r="C5" t="s">
-        <v>790</v>
+        <v>819</v>
       </c>
       <c r="D5" t="s">
-        <v>842</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>858</v>
+        <v>880</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>896</v>
       </c>
       <c r="F5" t="s">
-        <v>758</v>
+        <v>794</v>
       </c>
       <c r="G5" t="s">
-        <v>758</v>
+        <v>794</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>810</v>
+        <v>849</v>
       </c>
       <c r="B6" t="s">
-        <v>826</v>
+        <v>865</v>
       </c>
       <c r="C6" t="s">
-        <v>784</v>
+        <v>822</v>
       </c>
       <c r="D6" t="s">
-        <v>843</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>859</v>
+        <v>881</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>897</v>
       </c>
       <c r="F6" t="s">
-        <v>751</v>
+        <v>787</v>
       </c>
       <c r="G6" t="s">
-        <v>751</v>
+        <v>787</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>811</v>
+        <v>850</v>
       </c>
       <c r="B7" t="s">
-        <v>827</v>
+        <v>866</v>
       </c>
       <c r="C7" t="s">
-        <v>794</v>
+        <v>831</v>
       </c>
       <c r="D7" t="s">
-        <v>844</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>860</v>
+        <v>882</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>898</v>
       </c>
       <c r="F7" t="s">
-        <v>759</v>
+        <v>795</v>
       </c>
       <c r="G7" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>812</v>
+        <v>851</v>
       </c>
       <c r="B8" t="s">
-        <v>828</v>
+        <v>867</v>
       </c>
       <c r="C8" t="s">
-        <v>792</v>
+        <v>829</v>
       </c>
       <c r="D8" t="s">
-        <v>845</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>861</v>
+        <v>883</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>899</v>
       </c>
       <c r="F8" t="s">
-        <v>759</v>
+        <v>795</v>
       </c>
       <c r="G8" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>813</v>
+        <v>852</v>
       </c>
       <c r="B9" t="s">
-        <v>829</v>
+        <v>868</v>
       </c>
       <c r="C9" t="s">
-        <v>782</v>
+        <v>820</v>
       </c>
       <c r="D9" t="s">
-        <v>846</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>862</v>
+        <v>884</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>900</v>
       </c>
       <c r="F9" t="s">
-        <v>759</v>
+        <v>795</v>
       </c>
       <c r="G9" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>814</v>
+        <v>853</v>
       </c>
       <c r="B10" t="s">
-        <v>830</v>
+        <v>869</v>
       </c>
       <c r="C10" t="s">
-        <v>797</v>
+        <v>835</v>
       </c>
       <c r="D10" t="s">
-        <v>847</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>863</v>
+        <v>885</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>901</v>
       </c>
       <c r="F10" t="s">
-        <v>759</v>
+        <v>795</v>
       </c>
       <c r="G10" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>815</v>
+        <v>854</v>
       </c>
       <c r="B11" t="s">
-        <v>831</v>
+        <v>870</v>
       </c>
       <c r="C11" t="s">
-        <v>788</v>
+        <v>826</v>
       </c>
       <c r="D11" t="s">
-        <v>848</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>864</v>
+        <v>886</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>902</v>
       </c>
       <c r="F11" t="s">
-        <v>759</v>
+        <v>795</v>
       </c>
       <c r="G11" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>816</v>
+        <v>855</v>
       </c>
       <c r="B12" t="s">
-        <v>832</v>
+        <v>871</v>
       </c>
       <c r="C12" t="s">
-        <v>791</v>
+        <v>828</v>
       </c>
       <c r="D12" t="s">
-        <v>849</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>865</v>
+        <v>887</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>903</v>
       </c>
       <c r="F12" t="s">
-        <v>759</v>
+        <v>795</v>
       </c>
       <c r="G12" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>817</v>
+        <v>856</v>
       </c>
       <c r="B13" t="s">
-        <v>833</v>
+        <v>872</v>
       </c>
       <c r="C13" t="s">
+        <v>842</v>
+      </c>
+      <c r="D13" t="s">
+        <v>888</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="F13" t="s">
         <v>803</v>
       </c>
-      <c r="D13" t="s">
-        <v>850</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>866</v>
-      </c>
-      <c r="F13" t="s">
-        <v>767</v>
-      </c>
       <c r="G13" t="s">
-        <v>769</v>
+        <v>805</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>818</v>
+        <v>857</v>
       </c>
       <c r="B14" t="s">
-        <v>834</v>
+        <v>873</v>
       </c>
       <c r="C14" t="s">
-        <v>783</v>
+        <v>821</v>
       </c>
       <c r="D14" t="s">
-        <v>851</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>867</v>
+        <v>889</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>905</v>
       </c>
       <c r="F14" t="s">
-        <v>759</v>
+        <v>795</v>
       </c>
       <c r="G14" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>819</v>
+        <v>858</v>
       </c>
       <c r="B15" t="s">
-        <v>835</v>
+        <v>874</v>
       </c>
       <c r="C15" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="D15" t="s">
-        <v>852</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>868</v>
+        <v>890</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>906</v>
       </c>
       <c r="F15" t="s">
-        <v>751</v>
+        <v>787</v>
       </c>
       <c r="G15" t="s">
-        <v>751</v>
+        <v>787</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>820</v>
+        <v>859</v>
       </c>
       <c r="B16" t="s">
-        <v>836</v>
+        <v>875</v>
       </c>
       <c r="C16" t="s">
-        <v>793</v>
+        <v>830</v>
       </c>
       <c r="D16" t="s">
-        <v>853</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>869</v>
+        <v>891</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>907</v>
       </c>
       <c r="F16" t="s">
-        <v>759</v>
+        <v>795</v>
       </c>
       <c r="G16" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>821</v>
+        <v>860</v>
       </c>
       <c r="B17" t="s">
-        <v>837</v>
+        <v>876</v>
       </c>
       <c r="C17" t="s">
-        <v>787</v>
+        <v>825</v>
       </c>
       <c r="D17" t="s">
-        <v>854</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>870</v>
+        <v>892</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>908</v>
       </c>
       <c r="F17" t="s">
-        <v>759</v>
+        <v>795</v>
       </c>
       <c r="G17" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
     </row>
   </sheetData>
@@ -8869,834 +9189,834 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>871</v>
+      <c r="H1" t="s">
+        <v>909</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>872</v>
+        <v>910</v>
       </c>
       <c r="B2" t="s">
-        <v>907</v>
+        <v>945</v>
       </c>
       <c r="C2" t="s">
-        <v>942</v>
+        <v>980</v>
       </c>
       <c r="D2" t="s">
-        <v>977</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>1012</v>
+        <v>1015</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>1050</v>
       </c>
       <c r="F2" t="s">
-        <v>768</v>
+        <v>804</v>
       </c>
       <c r="G2" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>873</v>
+        <v>911</v>
       </c>
       <c r="B3" t="s">
-        <v>908</v>
+        <v>946</v>
       </c>
       <c r="C3" t="s">
-        <v>943</v>
+        <v>981</v>
       </c>
       <c r="D3" t="s">
-        <v>978</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>1013</v>
+        <v>1016</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>1051</v>
       </c>
       <c r="F3" t="s">
-        <v>755</v>
+        <v>791</v>
       </c>
       <c r="G3" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>874</v>
+        <v>912</v>
       </c>
       <c r="B4" t="s">
-        <v>909</v>
+        <v>947</v>
       </c>
       <c r="C4" t="s">
-        <v>944</v>
+        <v>982</v>
       </c>
       <c r="D4" t="s">
-        <v>979</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>1014</v>
+        <v>1017</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>1052</v>
       </c>
       <c r="F4" t="s">
-        <v>1047</v>
+        <v>1085</v>
       </c>
       <c r="G4" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>875</v>
+        <v>913</v>
       </c>
       <c r="B5" t="s">
-        <v>910</v>
+        <v>948</v>
       </c>
       <c r="C5" t="s">
-        <v>945</v>
+        <v>983</v>
       </c>
       <c r="D5" t="s">
-        <v>980</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>1015</v>
+        <v>1018</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>1053</v>
       </c>
       <c r="F5" t="s">
-        <v>755</v>
+        <v>791</v>
       </c>
       <c r="G5" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>876</v>
+        <v>914</v>
       </c>
       <c r="B6" t="s">
-        <v>911</v>
+        <v>949</v>
       </c>
       <c r="C6" t="s">
-        <v>946</v>
+        <v>984</v>
       </c>
       <c r="D6" t="s">
-        <v>981</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>1016</v>
+        <v>1019</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>1054</v>
       </c>
       <c r="F6" t="s">
-        <v>1047</v>
+        <v>1085</v>
       </c>
       <c r="G6" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>877</v>
+        <v>915</v>
       </c>
       <c r="B7" t="s">
-        <v>912</v>
+        <v>950</v>
       </c>
       <c r="C7" t="s">
-        <v>947</v>
+        <v>985</v>
       </c>
       <c r="D7" t="s">
-        <v>982</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>1017</v>
+        <v>1020</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>1055</v>
       </c>
       <c r="F7" t="s">
-        <v>1047</v>
+        <v>1085</v>
       </c>
       <c r="G7" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>878</v>
+        <v>916</v>
       </c>
       <c r="B8" t="s">
-        <v>913</v>
+        <v>951</v>
       </c>
       <c r="C8" t="s">
-        <v>948</v>
+        <v>986</v>
       </c>
       <c r="D8" t="s">
-        <v>983</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>1018</v>
+        <v>1021</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>1056</v>
       </c>
       <c r="F8" t="s">
-        <v>1047</v>
+        <v>1085</v>
       </c>
       <c r="G8" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>879</v>
+        <v>917</v>
       </c>
       <c r="B9" t="s">
-        <v>914</v>
+        <v>952</v>
       </c>
       <c r="C9" t="s">
-        <v>949</v>
+        <v>987</v>
       </c>
       <c r="D9" t="s">
-        <v>984</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>1019</v>
+        <v>1022</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>1057</v>
       </c>
       <c r="F9" t="s">
-        <v>774</v>
+        <v>811</v>
       </c>
       <c r="G9" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>880</v>
+        <v>918</v>
       </c>
       <c r="B10" t="s">
-        <v>915</v>
+        <v>953</v>
       </c>
       <c r="C10" t="s">
-        <v>950</v>
+        <v>988</v>
       </c>
       <c r="D10" t="s">
-        <v>985</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>1020</v>
+        <v>1023</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>1058</v>
       </c>
       <c r="F10" t="s">
-        <v>749</v>
+        <v>785</v>
       </c>
       <c r="G10" t="s">
-        <v>749</v>
+        <v>785</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>881</v>
+        <v>919</v>
       </c>
       <c r="B11" t="s">
-        <v>916</v>
+        <v>954</v>
       </c>
       <c r="C11" t="s">
-        <v>951</v>
+        <v>989</v>
       </c>
       <c r="D11" t="s">
-        <v>986</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>1021</v>
+        <v>1024</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>1059</v>
       </c>
       <c r="F11" t="s">
-        <v>1047</v>
+        <v>1085</v>
       </c>
       <c r="G11" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>882</v>
+        <v>920</v>
       </c>
       <c r="B12" t="s">
-        <v>917</v>
+        <v>955</v>
       </c>
       <c r="C12" t="s">
-        <v>952</v>
+        <v>990</v>
       </c>
       <c r="D12" t="s">
-        <v>987</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>1022</v>
+        <v>1025</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>1060</v>
       </c>
       <c r="F12" t="s">
-        <v>755</v>
+        <v>791</v>
       </c>
       <c r="G12" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>883</v>
+        <v>921</v>
       </c>
       <c r="B13" t="s">
-        <v>918</v>
+        <v>956</v>
       </c>
       <c r="C13" t="s">
-        <v>953</v>
+        <v>991</v>
       </c>
       <c r="D13" t="s">
-        <v>988</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>1023</v>
+        <v>1026</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>1061</v>
       </c>
       <c r="F13" t="s">
-        <v>755</v>
+        <v>791</v>
       </c>
       <c r="G13" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>884</v>
+        <v>922</v>
       </c>
       <c r="B14" t="s">
-        <v>919</v>
+        <v>957</v>
       </c>
       <c r="C14" t="s">
-        <v>954</v>
+        <v>992</v>
       </c>
       <c r="D14" t="s">
-        <v>989</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>1024</v>
+        <v>1027</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>1062</v>
       </c>
       <c r="F14" t="s">
-        <v>755</v>
+        <v>791</v>
       </c>
       <c r="G14" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>885</v>
+        <v>923</v>
       </c>
       <c r="B15" t="s">
-        <v>920</v>
+        <v>958</v>
       </c>
       <c r="C15" t="s">
-        <v>955</v>
+        <v>993</v>
       </c>
       <c r="D15" t="s">
-        <v>990</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>1025</v>
+        <v>1028</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>1063</v>
       </c>
       <c r="F15" t="s">
-        <v>768</v>
+        <v>804</v>
       </c>
       <c r="G15" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>886</v>
+        <v>924</v>
       </c>
       <c r="B16" t="s">
-        <v>921</v>
+        <v>959</v>
       </c>
       <c r="C16" t="s">
-        <v>956</v>
+        <v>994</v>
       </c>
       <c r="D16" t="s">
-        <v>991</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>1026</v>
+        <v>1029</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>1064</v>
       </c>
       <c r="F16" t="s">
-        <v>1047</v>
+        <v>1085</v>
       </c>
       <c r="G16" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>887</v>
+        <v>925</v>
       </c>
       <c r="B17" t="s">
-        <v>922</v>
+        <v>960</v>
       </c>
       <c r="C17" t="s">
-        <v>957</v>
+        <v>995</v>
       </c>
       <c r="D17" t="s">
-        <v>992</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>1027</v>
+        <v>1030</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>1065</v>
       </c>
       <c r="F17" t="s">
-        <v>749</v>
+        <v>785</v>
       </c>
       <c r="G17" t="s">
-        <v>780</v>
+        <v>817</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>888</v>
+        <v>926</v>
       </c>
       <c r="B18" t="s">
-        <v>923</v>
+        <v>961</v>
       </c>
       <c r="C18" t="s">
-        <v>958</v>
+        <v>996</v>
       </c>
       <c r="D18" t="s">
-        <v>993</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>1028</v>
+        <v>1031</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>1066</v>
       </c>
       <c r="F18" t="s">
-        <v>1047</v>
+        <v>1085</v>
       </c>
       <c r="G18" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>889</v>
+        <v>927</v>
       </c>
       <c r="B19" t="s">
-        <v>924</v>
+        <v>962</v>
       </c>
       <c r="C19" t="s">
-        <v>959</v>
+        <v>997</v>
       </c>
       <c r="D19" t="s">
-        <v>994</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>1029</v>
+        <v>1032</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>1067</v>
       </c>
       <c r="F19" t="s">
-        <v>1047</v>
+        <v>1085</v>
       </c>
       <c r="G19" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>890</v>
+        <v>928</v>
       </c>
       <c r="B20" t="s">
-        <v>925</v>
+        <v>963</v>
       </c>
       <c r="C20" t="s">
-        <v>960</v>
+        <v>998</v>
       </c>
       <c r="D20" t="s">
-        <v>995</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>1030</v>
+        <v>1033</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>1068</v>
       </c>
       <c r="F20" t="s">
-        <v>755</v>
+        <v>791</v>
       </c>
       <c r="G20" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>891</v>
+        <v>929</v>
       </c>
       <c r="B21" t="s">
-        <v>926</v>
+        <v>964</v>
       </c>
       <c r="C21" t="s">
-        <v>961</v>
+        <v>999</v>
       </c>
       <c r="D21" t="s">
-        <v>996</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>1031</v>
+        <v>1034</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>1069</v>
       </c>
       <c r="F21" t="s">
-        <v>768</v>
+        <v>804</v>
       </c>
       <c r="G21" t="s">
-        <v>779</v>
+        <v>816</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>892</v>
+        <v>930</v>
       </c>
       <c r="B22" t="s">
-        <v>927</v>
+        <v>965</v>
       </c>
       <c r="C22" t="s">
-        <v>962</v>
+        <v>1000</v>
       </c>
       <c r="D22" t="s">
-        <v>997</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>1032</v>
+        <v>1035</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>1070</v>
       </c>
       <c r="F22" t="s">
-        <v>1047</v>
+        <v>1085</v>
       </c>
       <c r="G22" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>893</v>
+        <v>931</v>
       </c>
       <c r="B23" t="s">
-        <v>928</v>
+        <v>966</v>
       </c>
       <c r="C23" t="s">
-        <v>963</v>
+        <v>1001</v>
       </c>
       <c r="D23" t="s">
-        <v>998</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>1033</v>
+        <v>1036</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>1071</v>
       </c>
       <c r="F23" t="s">
-        <v>1047</v>
+        <v>1085</v>
       </c>
       <c r="G23" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>894</v>
+        <v>932</v>
       </c>
       <c r="B24" t="s">
-        <v>929</v>
+        <v>967</v>
       </c>
       <c r="C24" t="s">
-        <v>964</v>
+        <v>1002</v>
       </c>
       <c r="D24" t="s">
-        <v>999</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>1034</v>
+        <v>1037</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>1072</v>
       </c>
       <c r="F24" t="s">
-        <v>768</v>
+        <v>804</v>
       </c>
       <c r="G24" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>895</v>
+        <v>933</v>
       </c>
       <c r="B25" t="s">
-        <v>930</v>
+        <v>968</v>
       </c>
       <c r="C25" t="s">
-        <v>965</v>
+        <v>1003</v>
       </c>
       <c r="D25" t="s">
-        <v>1000</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>1035</v>
+        <v>1038</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>1073</v>
       </c>
       <c r="F25" t="s">
-        <v>768</v>
+        <v>804</v>
       </c>
       <c r="G25" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>896</v>
+        <v>934</v>
       </c>
       <c r="B26" t="s">
-        <v>931</v>
+        <v>969</v>
       </c>
       <c r="C26" t="s">
-        <v>966</v>
+        <v>1004</v>
       </c>
       <c r="D26" t="s">
-        <v>1001</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>1036</v>
+        <v>1039</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>1074</v>
       </c>
       <c r="F26" t="s">
-        <v>1047</v>
+        <v>1085</v>
       </c>
       <c r="G26" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>897</v>
+        <v>935</v>
       </c>
       <c r="B27" t="s">
-        <v>932</v>
+        <v>970</v>
       </c>
       <c r="C27" t="s">
-        <v>967</v>
+        <v>1005</v>
       </c>
       <c r="D27" t="s">
-        <v>1002</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>1037</v>
+        <v>1040</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>1075</v>
       </c>
       <c r="F27" t="s">
-        <v>1047</v>
+        <v>1085</v>
       </c>
       <c r="G27" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>898</v>
+        <v>936</v>
       </c>
       <c r="B28" t="s">
-        <v>933</v>
+        <v>971</v>
       </c>
       <c r="C28" t="s">
-        <v>968</v>
+        <v>1006</v>
       </c>
       <c r="D28" t="s">
-        <v>1003</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>1038</v>
+        <v>1041</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>1076</v>
       </c>
       <c r="F28" t="s">
-        <v>1047</v>
+        <v>1085</v>
       </c>
       <c r="G28" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>899</v>
+        <v>937</v>
       </c>
       <c r="B29" t="s">
-        <v>934</v>
+        <v>972</v>
       </c>
       <c r="C29" t="s">
-        <v>969</v>
+        <v>1007</v>
       </c>
       <c r="D29" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>1039</v>
+        <v>1042</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>1077</v>
       </c>
       <c r="F29" t="s">
-        <v>749</v>
+        <v>785</v>
       </c>
       <c r="G29" t="s">
-        <v>780</v>
+        <v>817</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>900</v>
+        <v>938</v>
       </c>
       <c r="B30" t="s">
-        <v>935</v>
+        <v>973</v>
       </c>
       <c r="C30" t="s">
-        <v>970</v>
+        <v>1008</v>
       </c>
       <c r="D30" t="s">
-        <v>1005</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>1040</v>
+        <v>1043</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>1078</v>
       </c>
       <c r="F30" t="s">
-        <v>768</v>
+        <v>804</v>
       </c>
       <c r="G30" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>901</v>
+        <v>939</v>
       </c>
       <c r="B31" t="s">
-        <v>936</v>
+        <v>974</v>
       </c>
       <c r="C31" t="s">
-        <v>971</v>
+        <v>1009</v>
       </c>
       <c r="D31" t="s">
-        <v>1006</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>1041</v>
+        <v>1044</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>1079</v>
       </c>
       <c r="F31" t="s">
-        <v>1047</v>
+        <v>1085</v>
       </c>
       <c r="G31" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>902</v>
+        <v>940</v>
       </c>
       <c r="B32" t="s">
-        <v>937</v>
+        <v>975</v>
       </c>
       <c r="C32" t="s">
-        <v>972</v>
+        <v>1010</v>
       </c>
       <c r="D32" t="s">
-        <v>1007</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>1042</v>
+        <v>1045</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>1080</v>
       </c>
       <c r="F32" t="s">
-        <v>1047</v>
+        <v>1085</v>
       </c>
       <c r="G32" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>903</v>
+        <v>941</v>
       </c>
       <c r="B33" t="s">
-        <v>938</v>
+        <v>976</v>
       </c>
       <c r="C33" t="s">
-        <v>973</v>
+        <v>1011</v>
       </c>
       <c r="D33" t="s">
-        <v>1008</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>1043</v>
+        <v>1046</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>1081</v>
       </c>
       <c r="F33" t="s">
-        <v>1047</v>
+        <v>1085</v>
       </c>
       <c r="G33" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>904</v>
+        <v>942</v>
       </c>
       <c r="B34" t="s">
-        <v>939</v>
+        <v>977</v>
       </c>
       <c r="C34" t="s">
-        <v>974</v>
+        <v>1012</v>
       </c>
       <c r="D34" t="s">
-        <v>1009</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>1044</v>
+        <v>1047</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>1082</v>
       </c>
       <c r="F34" t="s">
-        <v>1047</v>
+        <v>1085</v>
       </c>
       <c r="G34" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>905</v>
+        <v>943</v>
       </c>
       <c r="B35" t="s">
-        <v>940</v>
+        <v>978</v>
       </c>
       <c r="C35" t="s">
-        <v>975</v>
+        <v>1013</v>
       </c>
       <c r="D35" t="s">
-        <v>1010</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>1045</v>
+        <v>1048</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>1083</v>
       </c>
       <c r="F35" t="s">
-        <v>1047</v>
+        <v>1085</v>
       </c>
       <c r="G35" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>906</v>
+        <v>944</v>
       </c>
       <c r="B36" t="s">
-        <v>941</v>
+        <v>979</v>
       </c>
       <c r="C36" t="s">
-        <v>976</v>
+        <v>1014</v>
       </c>
       <c r="D36" t="s">
-        <v>1011</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>1046</v>
+        <v>1049</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>1084</v>
       </c>
       <c r="F36" t="s">
-        <v>1047</v>
+        <v>1085</v>
       </c>
       <c r="G36" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
     </row>
   </sheetData>
@@ -9743,651 +10063,681 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB16"/>
+  <dimension ref="A1:AB18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" style="4" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" style="4" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" style="3" customWidth="1"/>
     <col min="7" max="7" width="20.7109375" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" style="4" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" style="3" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" style="4" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" style="3" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" style="3" customWidth="1"/>
     <col min="12" max="12" width="20.7109375" customWidth="1"/>
-    <col min="13" max="13" width="20.7109375" style="3" customWidth="1"/>
-    <col min="14" max="14" width="20.7109375" style="4" customWidth="1"/>
+    <col min="13" max="13" width="20.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="20.7109375" style="3" customWidth="1"/>
     <col min="15" max="15" width="20.7109375" customWidth="1"/>
-    <col min="16" max="16" width="20.7109375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="20.7109375" style="4" customWidth="1"/>
-    <col min="18" max="18" width="20.7109375" style="3" customWidth="1"/>
-    <col min="19" max="19" width="20.7109375" style="4" customWidth="1"/>
-    <col min="20" max="20" width="20.7109375" style="3" customWidth="1"/>
-    <col min="21" max="21" width="20.7109375" style="4" customWidth="1"/>
-    <col min="22" max="22" width="20.7109375" style="3" customWidth="1"/>
-    <col min="23" max="23" width="20.7109375" style="4" customWidth="1"/>
+    <col min="16" max="16" width="20.7109375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="20.7109375" style="3" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" style="2" customWidth="1"/>
+    <col min="19" max="19" width="20.7109375" style="3" customWidth="1"/>
+    <col min="20" max="20" width="20.7109375" style="2" customWidth="1"/>
+    <col min="21" max="21" width="20.7109375" style="3" customWidth="1"/>
+    <col min="22" max="22" width="20.7109375" style="2" customWidth="1"/>
+    <col min="23" max="23" width="20.7109375" style="3" customWidth="1"/>
     <col min="24" max="24" width="20.7109375" customWidth="1"/>
-    <col min="25" max="25" width="20.7109375" style="3" customWidth="1"/>
-    <col min="26" max="26" width="20.7109375" style="4" customWidth="1"/>
-    <col min="27" max="27" width="20.7109375" style="3" customWidth="1"/>
-    <col min="28" max="28" width="20.7109375" style="4" customWidth="1"/>
+    <col min="25" max="25" width="20.7109375" style="2" customWidth="1"/>
+    <col min="26" max="26" width="20.7109375" style="3" customWidth="1"/>
+    <col min="27" max="27" width="20.7109375" style="2" customWidth="1"/>
+    <col min="28" max="28" width="20.7109375" style="3" customWidth="1"/>
     <col min="29" max="29" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
-      <c r="A1" s="5" t="s">
-        <v>793</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5" t="s">
-        <v>787</v>
-      </c>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5" t="s">
-        <v>791</v>
-      </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="1" t="s">
-        <v>789</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>782</v>
-      </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5" t="s">
-        <v>783</v>
-      </c>
-      <c r="K1" s="5"/>
-      <c r="L1" s="1" t="s">
-        <v>838</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>794</v>
-      </c>
-      <c r="N1" s="5"/>
-      <c r="O1" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>792</v>
-      </c>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5" t="s">
-        <v>803</v>
-      </c>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5" t="s">
-        <v>786</v>
-      </c>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5" t="s">
-        <v>795</v>
-      </c>
-      <c r="W1" s="5"/>
-      <c r="X1" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="Y1" s="5" t="s">
-        <v>797</v>
-      </c>
-      <c r="Z1" s="5"/>
-      <c r="AA1" s="5" t="s">
-        <v>788</v>
-      </c>
-      <c r="AB1" s="5"/>
+      <c r="A1" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4" t="s">
+        <v>825</v>
+      </c>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4" t="s">
+        <v>828</v>
+      </c>
+      <c r="F1" s="4"/>
+      <c r="G1" t="s">
+        <v>827</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="K1" s="4"/>
+      <c r="L1" t="s">
+        <v>833</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>831</v>
+      </c>
+      <c r="N1" s="4"/>
+      <c r="O1" t="s">
+        <v>822</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4" t="s">
+        <v>824</v>
+      </c>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="W1" s="4"/>
+      <c r="X1" t="s">
+        <v>819</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4" t="s">
+        <v>826</v>
+      </c>
+      <c r="AB1" s="4"/>
     </row>
     <row r="2" spans="1:28">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="G2" t="s">
+        <v>329</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="L2" t="s">
+        <v>324</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="O2" t="s">
         <v>322</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="P2" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="X2" t="s">
         <v>319</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="G2" t="s">
-        <v>314</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="K2" s="4" t="s">
+      <c r="Y2" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28">
+      <c r="A3" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="G3" t="s">
+        <v>333</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="J3" s="5"/>
+      <c r="K3" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="L3" t="s">
+        <v>377</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="O3" t="s">
+        <v>352</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="V3" s="5"/>
+      <c r="W3" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="X3" t="s">
+        <v>330</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28">
+      <c r="A4" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="G4" t="s">
+        <v>391</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="L4" t="s">
+        <v>405</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="O4" t="s">
+        <v>384</v>
+      </c>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="T4" s="5"/>
+      <c r="U4" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="V4" s="5"/>
+      <c r="W4" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="X4" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28">
+      <c r="A5" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="G5" t="s">
+        <v>427</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="L5" t="s">
+        <v>470</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="O5" t="s">
+        <v>423</v>
+      </c>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="V5" s="5"/>
+      <c r="W5" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="Y5" s="5"/>
+      <c r="Z5" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28">
+      <c r="A6" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="O6" t="s">
+        <v>438</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="V6" s="5"/>
+      <c r="W6" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="Y6" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="AA6" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="AB6" s="3" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28">
+      <c r="A7" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="L2" t="s">
-        <v>309</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="O2" t="s">
-        <v>307</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="R2" s="3" t="s">
+      <c r="J7" s="5"/>
+      <c r="K7" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="M7" s="5"/>
+      <c r="N7" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="O7" t="s">
+        <v>465</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="V7" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="W7" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28">
+      <c r="A8" s="5"/>
+      <c r="B8" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="E8" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="M8" s="5"/>
+      <c r="N8" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="V8" s="5"/>
+      <c r="W8" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="AA8" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="AB8" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28">
+      <c r="A9" s="5"/>
+      <c r="B9" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="V9" s="5"/>
+      <c r="W9" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="Y9" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="AA9" s="5"/>
+      <c r="AB9" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28">
+      <c r="A10" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="AA10" s="5"/>
+      <c r="AB10" s="3" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28">
+      <c r="A11" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="AA11" s="5"/>
+      <c r="AB11" s="3" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28">
+      <c r="C12" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="P12" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="V12" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="AA12" s="5"/>
+      <c r="AB12" s="3" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28">
+      <c r="C13" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="V13" s="5"/>
+      <c r="W13" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="AA13" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28">
+      <c r="C14" s="5"/>
+      <c r="D14" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28">
+      <c r="C15" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="P15" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="T2" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="V2" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="X2" t="s">
-        <v>315</v>
-      </c>
-      <c r="Y2" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28">
-      <c r="A3" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="G3" t="s">
-        <v>318</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="J3" s="6"/>
-      <c r="K3" s="4" t="s">
-        <v>438</v>
-      </c>
-      <c r="L3" t="s">
-        <v>387</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="N3" s="4" t="s">
+    </row>
+    <row r="16" spans="1:28">
+      <c r="C16" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="O3" t="s">
-        <v>337</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="T3" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="V3" s="6"/>
-      <c r="W3" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="X3" t="s">
-        <v>422</v>
-      </c>
-      <c r="Y3" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="Z3" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="AA3" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28">
-      <c r="A4" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="G4" t="s">
-        <v>373</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="L4" t="s">
-        <v>449</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="O4" t="s">
-        <v>404</v>
-      </c>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="T4" s="6"/>
-      <c r="U4" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="V4" s="6"/>
-      <c r="W4" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="AA4" s="3" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28">
-      <c r="A5" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="G5" t="s">
-        <v>408</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="O5" t="s">
-        <v>417</v>
-      </c>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="V5" s="6"/>
-      <c r="W5" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="AA5" s="3" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28">
-      <c r="A6" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>403</v>
-      </c>
-      <c r="M6" s="6"/>
-      <c r="N6" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="O6" t="s">
-        <v>444</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="V6" s="6"/>
-      <c r="W6" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="Y6" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="AA6" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="AB6" s="4" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28">
-      <c r="A7" s="6" t="s">
-        <v>425</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="J7" s="6"/>
-      <c r="K7" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="M7" s="6"/>
-      <c r="N7" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="V7" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="W7" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="Y7" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="AA7" s="3" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28">
-      <c r="A8" s="6"/>
-      <c r="B8" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="V8" s="6"/>
-      <c r="W8" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="Y8" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="AA8" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="AB8" s="4" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28">
-      <c r="A9" s="6"/>
-      <c r="B9" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>405</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="Q9" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="V9" s="6"/>
-      <c r="W9" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="Y9" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="Z9" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="AA9" s="6"/>
-      <c r="AB9" s="4" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28">
-      <c r="A10" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="P10" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="Q10" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="AA10" s="6"/>
-      <c r="AB10" s="4" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28">
-      <c r="A11" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="V11" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="AA11" s="6"/>
-      <c r="AB11" s="4" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28">
-      <c r="C12" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="N12" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="Q12" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="V12" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="W12" s="4" t="s">
-        <v>403</v>
-      </c>
-      <c r="AA12" s="6"/>
-      <c r="AB12" s="4" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28">
-      <c r="C13" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="V13" s="6"/>
-      <c r="W13" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="AA13" s="3" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28">
-      <c r="C14" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28">
-      <c r="C15" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28">
-      <c r="C16" s="3" t="s">
-        <v>434</v>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" s="2" t="s">
+        <v>455</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="31">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="C9:C10"/>
+    <mergeCell ref="C13:C14"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E2:E5"/>
     <mergeCell ref="E1:F1"/>
@@ -10396,7 +10746,7 @@
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J1:K1"/>
-    <mergeCell ref="M5:M7"/>
+    <mergeCell ref="M6:M8"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="P3:P5"/>
     <mergeCell ref="P10:P11"/>

--- a/public/excel-files/atlas.xlsx
+++ b/public/excel-files/atlas.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2113" uniqueCount="1147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2145" uniqueCount="1164">
   <si>
     <t>ID</t>
   </si>
@@ -52,6 +52,9 @@
     <t>AML.T0100</t>
   </si>
   <si>
+    <t>AML.T0002.002</t>
+  </si>
+  <si>
     <t>AML.T0080</t>
   </si>
   <si>
@@ -148,6 +151,9 @@
     <t>AML.T0075</t>
   </si>
   <si>
+    <t>AML.T0095.000</t>
+  </si>
+  <si>
     <t>AML.T0050</t>
   </si>
   <si>
@@ -190,6 +196,9 @@
     <t>AML.T0002.000</t>
   </si>
   <si>
+    <t>AML.T0052.001</t>
+  </si>
+  <si>
     <t>AML.T0094</t>
   </si>
   <si>
@@ -553,6 +562,9 @@
     <t>attack-pattern--bd74bd28-20ce-5f69-972e-0afe627b7147</t>
   </si>
   <si>
+    <t>attack-pattern--8eb979a1-1e5a-5955-8a7d-df82ecb14088</t>
+  </si>
+  <si>
     <t>attack-pattern--785ca1b4-7d17-51f1-a605-46a9f21fb9b0</t>
   </si>
   <si>
@@ -649,6 +661,9 @@
     <t>attack-pattern--59fc3797-1686-503b-9212-26e1eecb5a69</t>
   </si>
   <si>
+    <t>attack-pattern--47789eb8-2a21-5a8b-a380-57e17bde15e2</t>
+  </si>
+  <si>
     <t>attack-pattern--07421f1a-a5ae-5936-9713-c77e4758177c</t>
   </si>
   <si>
@@ -691,6 +706,9 @@
     <t>attack-pattern--bbffbb39-c270-5822-8786-7bbab1a43dc3</t>
   </si>
   <si>
+    <t>attack-pattern--d017d9b8-ad90-5b6a-804f-229b342b05a3</t>
+  </si>
+  <si>
     <t>attack-pattern--ced5d1be-a572-58e3-bb3f-9f8c22de02b5</t>
   </si>
   <si>
@@ -1054,6 +1072,9 @@
     <t>AI Agent Clickbait</t>
   </si>
   <si>
+    <t>AI Agent Configuration</t>
+  </si>
+  <si>
     <t>AI Agent Context Poisoning</t>
   </si>
   <si>
@@ -1150,6 +1171,9 @@
     <t>Cloud Service Discovery</t>
   </si>
   <si>
+    <t>Code Repositories</t>
+  </si>
+  <si>
     <t>Command and Scripting Interpreter</t>
   </si>
   <si>
@@ -1190,6 +1214,9 @@
   </si>
   <si>
     <t>Datasets</t>
+  </si>
+  <si>
+    <t>Deepfake-Assisted Phishing</t>
   </si>
   <si>
     <t>Delay Execution of LLM Instructions</t>
@@ -1554,6 +1581,15 @@
   </si>
   <si>
     <t>Adversaries may craft deceptive web content designed to bait Computer-Using AI agents or AI web browsers into taking unintended actions, such as clicking buttons, copying code, or navigating to specific web pages. These attacks exploit the agent's interpretation of UI content, visual cues, or prompt-like language embedded in the site. When successful, they can lead the agent to inadvertently copy and execute malicious code on the user's operating system.</t>
+  </si>
+  <si>
+    <t>Adversaries may acquire publicly accessible AI agent configuration files to understand agent capabilities, gain unauthorized access to tools and data sources, or identify credentials for further attacks. Configuration files define what tools an agent can use, credentials for external services, system prompts, and behavioral settings, making valuable resources for adversaries targeting AI agent deployments.
+Once configuration files are acquired, adversaries may perform [Discover AI Agent Configuration](/techniques/AML.T0084) to gain additional insights they can use in their operation or [Credentials from AI Agent Configuration](/techniques/AML.T0083) to harvest secrets.
+AI agent configuration files come in multiple forms depending on the platform and agent framework. Agent configuration files adversaries may target include:
+- System prompts: Files containing agent instructions, behavioral guidelines, and internal logic.
+- Tool configuration: Files defining tools the agent can utilize, including Model Context Protocol (MCP) configs (e.g., `mcp.json`, `claude_desktop_config.json`), IDE-specific configs (e.g., `.claude/settings.json`, `.vscode/tasks.json`), and framework-specific settings that define external tool and data source integrations.
+- Skills and workflows: Files defining agent capabilities, behaviors, or workflows. Often a combination of instructions, scripts, and resources.
+- Environment and deployment configs: Files that control agent deployment and runtime behavior, often environment variables or framework-specific configs.</t>
   </si>
   <si>
     <t>Adversaries may attempt to manipulate the context used by an AI agent's large language model (LLM) to influence the responses it generates or actions it takes. This allows an adversary to persistently change the behavior of the target agent and further their goals.
@@ -1733,6 +1769,10 @@
 [1]: https://www.sysdig.com/blog/llmjacking-stolen-cloud-credentials-used-in-new-ai-attack</t>
   </si>
   <si>
+    <t>Adversaries may search public code repositories for information about a victim or victim system that can be used during targeting. Victims may store code or artifacts related to their AI systems in repositories on various third-party websites such as GitHub, GitLab, SourceForge, and BitBucket. Adversaries may search code repositories of common AI tools, frameworks, models, or agentic systems that are used--but not owned--by the victim.
+Public code repositories can often be a source of various information about victims, such as commonly used AI frameworks, libraries, models, datasets, agents, and agent tools, as well as the names of employees. Adversaries may also identify more sensitive data, including accidentally leaked credentials or API keys (ex: [Credentials from AI Agent Configuration](/techniques/AML.T0083)). Information from these sources may reveal opportunities for other forms of [Reconnaissance](/tactics/AML.TA0002) (ex: [Gather RAG-Indexed Targets](/techniques/AML.T0064)), establishing operational resources (ex: [Acquire Public AI Artifacts](/techniques/AML.T0002)), [Discovery](/tactics/AML.TA0008) (ex: [Discover AI Agent Configuration](/techniques/AML.T0084)) and/or [Initial Access](/tactics/AML.TA0004) (ex: [Valid Accounts](/techniques/AML.T0012) or [Phishing](/techniques/AML.T0052)).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Adversaries may abuse command and script interpreters to execute commands, scripts, or binaries. These interfaces and languages provide ways of interacting with computer systems and are a common feature across many different platforms. Most systems come with some built-in command-line interface and scripting capabilities, for example, macOS and Linux distributions include some flavor of Unix Shell while Windows installations include the Windows Command Shell and PowerShell.
 There are also cross-platform interpreters such as Python, as well as those commonly associated with client applications such as JavaScript and Visual Basic.
 Adversaries may abuse these technologies in various ways as a means of executing arbitrary commands. Commands and scripts can be embedded in Initial Access payloads delivered to victims as lure documents or as secondary payloads downloaded from an existing C2. Adversaries may also execute commands through interactive terminals/shells, as well as utilize various Remote Services in order to achieve remote Execution.
@@ -1815,6 +1855,29 @@
 Some datasets require the adversary to [Establish Accounts](/techniques/AML.T0021) for access.
 Acquired datasets help the adversary advance their operations, stage attacks,  and tailor attacks to the victim organization.
 </t>
+  </si>
+  <si>
+    <t>Adversaries may use deepfakes (AI-generated synthetic images, audio, or video) in phishing campaigns to impersonate trusted individuals, executives, or organizations. These attacks exploit human trust by presenting fraudulent voice or video communications as legitimate, enabling adversaries to manipulate targets into disclosing credentials, transferring funds, or granting access to systems.
+Voice deepfakes (AI-cloned voices) are used in vishing [\[1\]][vishing] (voice phishing) attacks over telephone or VoIP. Adversaries can clone a target's voice using a few seconds [\[2\]][valle] of publicly available audio from speeches, earnings calls, podcasts, or social media [\[3\]][voice]. These cloned voices are then used in pre-recorded voicemail messages or live phone calls. Video deepfakes can impersonate a trusted individual's face and voice. Adversaries use publicly available video from company meetings, earnings calls, or social media to create convincing AI-generated video of target individuals. They are used in live video conference calls or recorded video messages. AI-generated content has advanced to the point that it is often difficult to identify as synthetic [\[4\]][fbi].
+Adversaries may first perform [Obtain Capabilities](/techniques/AML.T0016): [Generative AI](/techniques/AML.T0016.002) followed by [Generate Deepfakes](/techniques/AML.T0088) in preparation for their [Phishing](/techniques/AML.T0052) campaign. Deepfake phishing campaigns often utilize other communication channels (such as email, SMS, or instant messaging) for layered social engineering attacks [\[5\]][aiid839].
+These attacks span a wide range of victims and attack types, demonstrating the breadth of deepfake-enabled fraud. Adversaries have conducted extensive deepfake-assisted phishing campaigns against the individuals, including targeted scams [\[6\]][aiid564] [\[7\]][oecd1] [\[8\]][aiid1280] [\[9\]][aiid1285], as well as large-scale credential harvesting campaigns targeting billions of users [\[10\]][aiid839] [\[11\]][aiid941]. Adversaries have used deepfakes to impersonate executives [\[12\]][aiid1100], causing business entities to suffer significant financial losses from [\[13\]][aiid634] [\[14\]][aiid147]. There are also reports of government officials being targeted in widespread campaigns [\[4\]][fbi] [\[15\]][aiid927].
+The attacks span communication channels including voice deepfakes for vishing [\[16\]][aiid567] and video deepfakes in conference calls [\[13\]][aiid634], as well as multi-channel campaigns combining phone, email, and messaging platforms [\[10\]][aiid839].
+[valle]: https://www.microsoft.com/en-us/research/project/vall-e-x/ "VALL-E Family: Neural codec language models for speech synthesis"
+[vishing]: https://www.social-engineer.org/framework/attack-vectors/vishing/ "Vishing - Social-Engineer Framework"
+[voice]: https://cloud.google.com/blog/topics/threat-intelligence/ai-powered-voice-spoofing-vishing-attacks "AI-powered voice spoofing: Understanding and defending against vishing attacks"
+[fbi]: https://www.ic3.gov/PSA/2025/PSA250515/ "FBI Public Service Advisory: Scammers are deepfaking voices of senior US government officials"
+[oecd1]: https://oecd.ai/en/incidents/2026-04-06-ca7a "AI-Generated Voice Used in Scam Targeting Drica Moraes' Contacts"
+[oecd2]: https://oecd.ai/en/incidents/2026-03-02-3408 "AI Deepfake Voice Scams Target 1 in 4 Americans"
+[aiid634]: https://incidentdatabase.ai/cite/634/ "Alleged Deepfake CFO Scam Reportedly Costs Multinational Engineering Firm Arup $25 Million"
+[aiid147]: https://incidentdatabase.ai/cite/147/ "Reported AI-Cloned Voice Used to Deceive Hong Kong Bank Manager in Purported $35 Million Fraud Scheme"
+[aiid1100]: https://incidentdatabase.ai/cite/1100/ "AI Incident Database - LastPass CEO Voice Deepfake Attempt"
+[aiid927]: https://incidentdatabase.ai/cite/927/ "Italian Defense Minister Voice Clone"
+[aiid564]: https://incidentdatabase.ai/cite/564/ "Voice deepfake targets bank in failed transfer scam"
+[aiid567]: https://incidentdatabase.ai/cite/567/ "Deepfake Voice Exploit Compromises Retool's Cloud Services"
+[aiid1280]: https://incidentdatabase.ai/cite/1280/ "Reported Use of AI Voice and Identity Manipulation in the 'Phantom Hacker' Fraud Scheme"
+[aiid1285]: https://incidentdatabase.ai/cite/1285/ "Purportedly AI-Generated Jason Momoa Deepfake Used in Romance Scam"
+[aiid839]: https://incidentdatabase.ai/cite/839/ "Purportedly AI-Driven Phishing Scam Uses Spoofed Google Call to Attempt Gmail Breach"
+[aiid941]: https://incidentdatabase.ai/cite/941/ "AI-Driven Phishing Scam Uses Deepfake Robocalls to Target Gmail Users"</t>
   </si>
   <si>
     <t>Adversaries may include instructions to be followed by the AI system in response to a future event, such as a specific keyword or the next interaction, in order to evade detection or bypass controls placed on the AI system.
@@ -2043,10 +2106,33 @@
 </t>
   </si>
   <si>
-    <t>An adversary may target the inputs or the architecture of an LLM, placing it in a state where it will freely respond to user input, bypassing any controls, restrictions, or guardrails placed on the LLM. Once successfully jailbroken, the LLM can be used in unintended ways by the adversary.
-Jailbreaks are classified as either white-box or black-box depending on the level of model access they require. In white-box jailbreaks, the attacker directly exploits the model. Gradient and logit-based attacks use internal signals to select prompts that make harmful answers more likely while fine-tuning-based methods weaken safety through retraining ([Jailbreak Attacks and Defenses: A Survey]; [JailbreakZoo]). Additionally, many large language models encode refusal in a single linear signal in their internal layers; removing or suppressing this signal via an activation edit largely disables refusal while leaving normal skills mostly intact ([Refusal Direction]).
-Black-box jailbreaks, on the other hand, do not require direct model access, relying instead on clever prompting and context tricks. Examples include wrapping a harmful question inside a story, role-play, or code snippet so the model "fills in" the dangerous part as part of the scenario ([Jailbreak Attacks and Defenses: A Survey]) or hiding intent through ciphers, rare languages, and other encodings so the text looks harmless to filters but remains understandable to the model ([JailbreakZoo]; [Jailbreak Attacks and Defenses: A Survey]). Black-box jailbreaks can also take a multi-turn form where attackers engage in dialogue that begins harmless but escalates towards a forbidden goal, changing the conversation history through references and hints while never explicitly stating the malicious request ([Cresendo attacks], [Echo Chamber attack]).
-Jailbreak generation can be automated with fine-tuned models ([MASTERKEY]), multi-agent systems ([Jailbreak Attacks and Defenses: A Survey]), or evolutionary algorithms ([JailbreakZoo]). Aside from fine-tuning, these approaches do not require direct model access.</t>
+    <t>Adversaries may induce a large language model (LLM) to ignore, circumvent, or override its safety/alignment behaviors and/or guardails to elicit outputs the model is intended to withhold. Once jailbroken, the LLM may be used in unintended ways by the adversary. Jailbreaks may be achieved via adversarial prompting, or by modifying model weights or safety mechanisms.
+Adversaries may attempt a jailbreak for [Defense Evasion](/tactics/AML.TA0007) of the LLM's guidelines and guardrails itself to then reveal information (ex: [LLM Data Leakage](/techniques/AML.T0057), [Discover LLM System Information](/techniques/AML.T0069)) or generate harmful content (ex: [Generate Malicious Commands](/techniques/AML.T0102), [Spearphishing via Social Engineering LLM](/techniques/AML.T0052.000)). They may also jailbreak a model for [Privilege Escalation](/tactics/AML.TA0012) to invoke tools or perform actions for their own purposes (ex: [AI Agent Tool Invocation](/techniques/AML.T0053)) or abuse the agent for a [Command and Control](/tactics/AML.TA0014) channel (ex: [AI Agent](/techniques/AML.T0108)).
+Adversaries use a variety of strategies to craft jailbreak prompts. Prompts may target specific models or model families and are iterated upon until successful. Model providers actively update their model guardrails to make them more resistant to jailbreak prompts as new prompts are developed. Common strategies [\[1\]][jailbreak-guide] include but are not limited to:
+- Instruction override: Use phrasing that attempts to supersede prior constraints (e.g. "ignore previous instructions").
+- Roleplay / persona switching: Instruct the LLM to adopt an identity or mode that allows unrestricted answers (e.g. "as a security researcher").
+- Fictionalization and hypotheticals: Instruct the LLM to include disallowed content as part of a story, screenplay, or educational scenario.
+- Separate intent from content: request analysis, examples, templates, or edge cases, that implicitly contain disallowed content.
+- Multi-turn escalation / Crescendo: Utilize a sequence of prompts that start benign, establish trust, then gradually cross policy boundaries with incremental prompts.
+- Constrained output formats: Instruct the LLM to output to a strict schema or format (e.g. JSON, YAML, code, or tables).
+- Obfuscation and transformation: Use encoding, transformations, translation, or euphemisms, (e.g., base64 encoding, "describe it in another language").
+- Create a high priority objective: Frame compliance as necessary to fulfill the user's main task (e.g. "to complete the evaluation," "to follow the spec," "to follow safety guidelines").
+Adversaries may also use algorithmic approaches to generating jailbreak prompts [\[2\]][jailbreak-zoo] [\[3\]][jailbreak-survey]. Algorithmic jailbreak generation allows for automated methods that discover jailbreaks at scale. Some approaches automate manual strategies [\[4\]][autodan] [\[5\]][gptfuzzer] [\[6\]][crescendo] [\[7\]][echo-chamber] while others optimize a string of tokens directly [\[8\]][universal] to produce nonsensical text. Both black-box (applicable to commercial models where the adversary has only query access to the model) and white-box (applicable in the open-source setting, where the adversary has full access to the model weights) optimization approaches are viable.
+Adversaries may also directly manipulate a model's weights, or modify or remove parts of a model to create a jailbroken of "uncensored" variant of the target model. This is applicable to open-source models, or cases where the adversary gains full access to the target model. Approaches include fine-tuning to reduce refusals [\[9\]][single-direction], targeted model editing [\[10\]][rome], addition of adapters [\[11\]][lora], and removing safety mechanisms such as guardrails.
+Jailbreak prompts that are known to work on various classes of LLMs are often published in the open-source community [\[12\]][dan]. Jailbroken or uncensored LLMs that have been trained or fine-tuned to be jailbroken are shared in public model registries such as huggingface [\[13\]][abliteration].
+[jailbreak-survey]: https://arxiv.org/abs/2407.04295 "Jailbreak Attacks and Defenses Against Large Language Models: A Survey"
+[jailbreak-zoo]: https://arxiv.org/abs/2407.01599 "JailbreakZoo: Survey, Landscapes, and Horizons in Jailbreaking Large Language and Vision-Language Models"
+[jailbreak-guide]: https://www.promptfoo.dev/blog/how-to-jailbreak-llms/ "Jailbreaking LLMs: A Comprehensive Guide (With Examples)"
+[autodan]: https://arxiv.org/abs/2310.04451 "AutoDAN: Generating Stealthy Jailbreak Prompts on Aligned Large Language Models"
+[gptfuzzer]: https://arxiv.org/abs/2309.10253 "GPTFUZZER: Red Teaming Large Language Models with Auto-Generated Jailbreak Prompts"
+[crescendo]: https://arxiv.org/abs/2404.01833 "Great, Now Write an Article About That: The Crescendo Multi-Turn LLM Jailbreak Attack"
+[echo-chamber]: https://arxiv.org/abs/2601.05742 "The Echo Chamber Multi-Turn LLM Jailbreak"
+[dan]: https://github.com/0xk1h0/ChatGPT_DAN "ChatGPT DAN"
+[rome]: https://arxiv.org/abs/2202.05262 "Locating and Editing Factual Associations in GPT"
+[universal]: https://arxiv.org/abs/2307.15043 "Universal and Transferable Adversarial Attacks on Aligned Language Models"
+[single-direction]: https://arxiv.org/abs/2406.11717 "Refusal in Language Models Is Mediated by a Single Direction"
+[lora]: https://arxiv.org/abs/2310.20624 "LoRA Fine-tuning Efficiently Undoes Safety Training in Llama 2-Chat 70B"
+[abliteration]: https://huggingface.co/blog/mlabonne/abliteration "Uncensor any LLM with abliteration"</t>
   </si>
   <si>
     <t>Adversaries may use their acquired knowledge of the target generative AI system to craft prompts that bypass its defenses and allow malicious instructions to be executed.
@@ -2157,9 +2243,8 @@
 Capabilities may be specific to AI-based attacks [Adversarial AI Attack Implementations](/techniques/AML.T0016.000) or generic software tools repurposed for malicious intent ([Software Tools](/techniques/AML.T0016.001)). In both instances, an adversary may modify or customize the capability to aid in targeting a particular AI-enabled system.</t>
   </si>
   <si>
-    <t xml:space="preserve">Adversaries may send phishing messages to gain access to victim systems. All forms of phishing are electronically delivered social engineering. Phishing can be targeted, known as spearphishing. In spearphishing, a specific individual, company, or industry will be targeted by the adversary. More generally, adversaries can conduct non-targeted phishing, such as in mass malware spam campaigns.
-Generative AI, including LLMs that generate synthetic text, visual deepfakes of faces, and audio deepfakes of speech, is enabling adversaries to scale targeted phishing campaigns. LLMs can interact with users via text conversations and can be programmed with a meta prompt to phish for sensitive information. Deepfakes can be use in impersonation as an aid to phishing.
-</t>
+    <t>Adversaries may send phishing messages to gain access to victim systems. All forms of phishing are electronically delivered social engineering. Phishing can be targeted, known as spearphishing. In spearphishing, a specific individual, company, or industry will be targeted by the adversary. More generally, adversaries can conduct non-targeted phishing, such as in mass malware spam campaigns.
+Generative AI, including LLMs that generate synthetic text, visual deepfakes of faces, and audio deepfakes of speech (See [Generate Deepfakes](/techniques/AML.T0088)), is enabling adversaries to scale targeted phishing campaigns (See [Spearphishing via Social Engineering LLM](/techniques/AML.T0052.000)). LLMs can interact with users via text conversations and can be programmed with a system prompt to phish for sensitive information. Deepfakes can also be used in [Impersonation](/techniques/AML.T0073) as an aid to phishing.</t>
   </si>
   <si>
     <t>Adversaries may acquire or manufacture physical countermeasures to aid or support their attack.
@@ -2416,6 +2501,9 @@
     <t>https://atlas.mitre.org/techniques/AML.T0100</t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0002.002</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0080</t>
   </si>
   <si>
@@ -2512,6 +2600,9 @@
     <t>https://atlas.mitre.org/techniques/AML.T0075</t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0095.000</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0050</t>
   </si>
   <si>
@@ -2554,6 +2645,9 @@
     <t>https://atlas.mitre.org/techniques/AML.T0002.000</t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0052.001</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0094</t>
   </si>
   <si>
@@ -2917,6 +3011,9 @@
     <t>25 November 2025</t>
   </si>
   <si>
+    <t>22 April 2026</t>
+  </si>
+  <si>
     <t>30 September 2025</t>
   </si>
   <si>
@@ -2995,6 +3092,9 @@
     <t>12 January 2024</t>
   </si>
   <si>
+    <t>30 April 2026</t>
+  </si>
+  <si>
     <t>12 October 2023</t>
   </si>
   <si>
@@ -3007,9 +3107,6 @@
     <t>06 November 2025</t>
   </si>
   <si>
-    <t>20 December 2025</t>
-  </si>
-  <si>
     <t>18 December 2025</t>
   </si>
   <si>
@@ -3022,9 +3119,15 @@
     <t>Execution</t>
   </si>
   <si>
+    <t>Resource Development</t>
+  </si>
+  <si>
     <t>Persistence</t>
   </si>
   <si>
+    <t>Initial Access</t>
+  </si>
+  <si>
     <t>Credential Access</t>
   </si>
   <si>
@@ -3037,15 +3140,9 @@
     <t>Impact</t>
   </si>
   <si>
-    <t>Resource Development</t>
-  </si>
-  <si>
     <t>AI Model Access</t>
   </si>
   <si>
-    <t>Initial Access</t>
-  </si>
-  <si>
     <t>Defense Evasion</t>
   </si>
   <si>
@@ -3055,9 +3152,18 @@
     <t>Reconnaissance</t>
   </si>
   <si>
+    <t>Lateral Movement</t>
+  </si>
+  <si>
     <t>AI Attack Staging</t>
   </si>
   <si>
+    <t>Initial Access, Lateral Movement</t>
+  </si>
+  <si>
+    <t>AI Attack Staging, Persistence</t>
+  </si>
+  <si>
     <t>Privilege Escalation</t>
   </si>
   <si>
@@ -3070,22 +3176,13 @@
     <t>Defense Evasion, Privilege Escalation</t>
   </si>
   <si>
-    <t>AI Attack Staging, Persistence</t>
-  </si>
-  <si>
     <t>Defense Evasion, Persistence</t>
   </si>
   <si>
-    <t>Initial Access, Lateral Movement</t>
-  </si>
-  <si>
     <t>Persistence, Resource Development</t>
   </si>
   <si>
     <t>Initial Access, Persistence</t>
-  </si>
-  <si>
-    <t>Lateral Movement</t>
   </si>
   <si>
     <t>Initial Access, Privilege Escalation</t>
@@ -3899,6 +3996,9 @@
   </si>
   <si>
     <t>19 March 2026</t>
+  </si>
+  <si>
+    <t>20 December 2025</t>
   </si>
 </sst>
 </file>
@@ -4307,7 +4407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I168"/>
+  <dimension ref="A1:I171"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -4344,28 +4444,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="D2" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>677</v>
+        <v>689</v>
       </c>
       <c r="F2" t="s">
-        <v>844</v>
+        <v>859</v>
       </c>
       <c r="G2" t="s">
-        <v>867</v>
+        <v>883</v>
       </c>
       <c r="H2" t="s">
-        <v>879</v>
+        <v>895</v>
       </c>
       <c r="I2" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -4373,28 +4473,28 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C3" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="D3" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>678</v>
+        <v>690</v>
       </c>
       <c r="F3" t="s">
-        <v>845</v>
+        <v>860</v>
       </c>
       <c r="G3" t="s">
-        <v>845</v>
+        <v>860</v>
       </c>
       <c r="H3" t="s">
-        <v>880</v>
+        <v>896</v>
       </c>
       <c r="I3" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -4402,28 +4502,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C4" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="D4" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="F4" t="s">
-        <v>846</v>
+        <v>861</v>
       </c>
       <c r="G4" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
       <c r="H4" t="s">
-        <v>881</v>
+        <v>897</v>
       </c>
       <c r="I4" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -4431,28 +4531,28 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C5" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="D5" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>680</v>
+        <v>692</v>
       </c>
       <c r="F5" t="s">
-        <v>847</v>
+        <v>862</v>
       </c>
       <c r="G5" t="s">
-        <v>847</v>
+        <v>884</v>
       </c>
       <c r="H5" t="s">
-        <v>881</v>
+        <v>898</v>
       </c>
       <c r="I5" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -4460,28 +4560,28 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C6" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="D6" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>681</v>
+        <v>693</v>
       </c>
       <c r="F6" t="s">
-        <v>845</v>
+        <v>863</v>
       </c>
       <c r="G6" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
       <c r="H6" t="s">
-        <v>882</v>
+        <v>899</v>
       </c>
       <c r="I6" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -4489,28 +4589,28 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C7" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="D7" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>682</v>
+        <v>694</v>
       </c>
       <c r="F7" t="s">
-        <v>845</v>
+        <v>860</v>
       </c>
       <c r="G7" t="s">
-        <v>845</v>
+        <v>885</v>
       </c>
       <c r="H7" t="s">
-        <v>881</v>
+        <v>900</v>
       </c>
       <c r="I7" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -4518,28 +4618,28 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C8" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="D8" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>683</v>
+        <v>695</v>
       </c>
       <c r="F8" t="s">
-        <v>848</v>
+        <v>860</v>
       </c>
       <c r="G8" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="H8" t="s">
-        <v>883</v>
+        <v>898</v>
       </c>
       <c r="I8" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -4547,28 +4647,28 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C9" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="D9" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F9" t="s">
-        <v>847</v>
+        <v>864</v>
       </c>
       <c r="G9" t="s">
-        <v>847</v>
+        <v>873</v>
       </c>
       <c r="H9" t="s">
-        <v>881</v>
+        <v>901</v>
       </c>
       <c r="I9" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -4576,28 +4676,28 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C10" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="D10" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>685</v>
+        <v>697</v>
       </c>
       <c r="F10" t="s">
-        <v>846</v>
+        <v>863</v>
       </c>
       <c r="G10" t="s">
-        <v>846</v>
+        <v>863</v>
       </c>
       <c r="H10" t="s">
-        <v>884</v>
+        <v>898</v>
       </c>
       <c r="I10" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -4605,28 +4705,28 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C11" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="D11" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>686</v>
+        <v>698</v>
       </c>
       <c r="F11" t="s">
-        <v>849</v>
+        <v>862</v>
       </c>
       <c r="G11" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="H11" t="s">
-        <v>884</v>
+        <v>902</v>
       </c>
       <c r="I11" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -4634,28 +4734,28 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C12" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="D12" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>687</v>
+        <v>699</v>
       </c>
       <c r="F12" t="s">
-        <v>847</v>
+        <v>865</v>
       </c>
       <c r="G12" t="s">
-        <v>847</v>
+        <v>876</v>
       </c>
       <c r="H12" t="s">
-        <v>885</v>
+        <v>902</v>
       </c>
       <c r="I12" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -4663,28 +4763,28 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C13" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="D13" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>688</v>
+        <v>700</v>
       </c>
       <c r="F13" t="s">
-        <v>849</v>
+        <v>863</v>
       </c>
       <c r="G13" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="H13" t="s">
-        <v>886</v>
+        <v>903</v>
       </c>
       <c r="I13" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -4692,28 +4792,28 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C14" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="D14" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>689</v>
+        <v>701</v>
       </c>
       <c r="F14" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G14" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
       <c r="H14" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
       <c r="I14" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -4721,28 +4821,28 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C15" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="D15" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="F15" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G15" t="s">
-        <v>852</v>
+        <v>876</v>
       </c>
       <c r="H15" t="s">
-        <v>887</v>
+        <v>903</v>
       </c>
       <c r="I15" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -4750,28 +4850,28 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C16" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="D16" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>691</v>
+        <v>703</v>
       </c>
       <c r="F16" t="s">
-        <v>850</v>
+        <v>865</v>
       </c>
       <c r="G16" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="H16" t="s">
-        <v>879</v>
+        <v>904</v>
       </c>
       <c r="I16" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -4779,28 +4879,28 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C17" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D17" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>692</v>
+        <v>704</v>
       </c>
       <c r="F17" t="s">
-        <v>847</v>
+        <v>866</v>
       </c>
       <c r="G17" t="s">
-        <v>847</v>
+        <v>886</v>
       </c>
       <c r="H17" t="s">
-        <v>885</v>
+        <v>895</v>
       </c>
       <c r="I17" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -4808,28 +4908,28 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C18" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="D18" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>693</v>
+        <v>705</v>
       </c>
       <c r="F18" t="s">
-        <v>849</v>
+        <v>863</v>
       </c>
       <c r="G18" t="s">
-        <v>847</v>
+        <v>863</v>
       </c>
       <c r="H18" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
       <c r="I18" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -4837,28 +4937,28 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C19" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="D19" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>694</v>
+        <v>706</v>
       </c>
       <c r="F19" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G19" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="H19" t="s">
-        <v>888</v>
+        <v>899</v>
       </c>
       <c r="I19" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -4866,28 +4966,28 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C20" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="D20" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>695</v>
+        <v>707</v>
       </c>
       <c r="F20" t="s">
-        <v>847</v>
+        <v>865</v>
       </c>
       <c r="G20" t="s">
-        <v>847</v>
+        <v>876</v>
       </c>
       <c r="H20" t="s">
-        <v>889</v>
+        <v>899</v>
       </c>
       <c r="I20" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -4895,28 +4995,28 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C21" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="D21" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>696</v>
+        <v>708</v>
       </c>
       <c r="F21" t="s">
-        <v>847</v>
+        <v>863</v>
       </c>
       <c r="G21" t="s">
-        <v>847</v>
+        <v>863</v>
       </c>
       <c r="H21" t="s">
-        <v>889</v>
+        <v>905</v>
       </c>
       <c r="I21" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -4924,28 +5024,28 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C22" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="D22" t="s">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>697</v>
+        <v>709</v>
       </c>
       <c r="F22" t="s">
-        <v>849</v>
+        <v>863</v>
       </c>
       <c r="G22" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="H22" t="s">
-        <v>887</v>
+        <v>905</v>
       </c>
       <c r="I22" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -4953,28 +5053,28 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C23" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="D23" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>698</v>
+        <v>710</v>
       </c>
       <c r="F23" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G23" t="s">
-        <v>852</v>
+        <v>876</v>
       </c>
       <c r="H23" t="s">
-        <v>886</v>
+        <v>904</v>
       </c>
       <c r="I23" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -4982,28 +5082,28 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C24" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="D24" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>699</v>
+        <v>711</v>
       </c>
       <c r="F24" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G24" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="H24" t="s">
-        <v>886</v>
+        <v>897</v>
       </c>
       <c r="I24" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -5011,28 +5111,28 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C25" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="D25" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>700</v>
+        <v>712</v>
       </c>
       <c r="F25" t="s">
-        <v>846</v>
+        <v>865</v>
       </c>
       <c r="G25" t="s">
-        <v>846</v>
+        <v>876</v>
       </c>
       <c r="H25" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="I25" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -5040,28 +5140,28 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C26" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="D26" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="F26" t="s">
-        <v>849</v>
+        <v>862</v>
       </c>
       <c r="G26" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="H26" t="s">
-        <v>891</v>
+        <v>906</v>
       </c>
       <c r="I26" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -5069,28 +5169,28 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C27" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="D27" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>702</v>
+        <v>714</v>
       </c>
       <c r="F27" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G27" t="s">
-        <v>860</v>
+        <v>873</v>
       </c>
       <c r="H27" t="s">
-        <v>886</v>
+        <v>907</v>
       </c>
       <c r="I27" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -5098,28 +5198,28 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C28" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="D28" t="s">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>703</v>
+        <v>715</v>
       </c>
       <c r="F28" t="s">
-        <v>848</v>
+        <v>865</v>
       </c>
       <c r="G28" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
       <c r="H28" t="s">
-        <v>886</v>
+        <v>897</v>
       </c>
       <c r="I28" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -5127,28 +5227,28 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C29" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="D29" t="s">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>704</v>
+        <v>716</v>
       </c>
       <c r="F29" t="s">
-        <v>847</v>
+        <v>864</v>
       </c>
       <c r="G29" t="s">
-        <v>847</v>
+        <v>876</v>
       </c>
       <c r="H29" t="s">
-        <v>881</v>
+        <v>897</v>
       </c>
       <c r="I29" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -5156,28 +5256,28 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C30" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D30" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="F30" t="s">
-        <v>851</v>
+        <v>863</v>
       </c>
       <c r="G30" t="s">
-        <v>870</v>
+        <v>863</v>
       </c>
       <c r="H30" t="s">
-        <v>889</v>
+        <v>903</v>
       </c>
       <c r="I30" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -5185,28 +5285,28 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C31" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="D31" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="F31" t="s">
-        <v>849</v>
+        <v>867</v>
       </c>
       <c r="G31" t="s">
-        <v>849</v>
+        <v>886</v>
       </c>
       <c r="H31" t="s">
-        <v>892</v>
+        <v>908</v>
       </c>
       <c r="I31" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -5214,28 +5314,28 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C32" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="D32" t="s">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>707</v>
+        <v>719</v>
       </c>
       <c r="F32" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G32" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="H32" t="s">
-        <v>892</v>
+        <v>909</v>
       </c>
       <c r="I32" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -5243,28 +5343,28 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C33" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="D33" t="s">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="F33" t="s">
-        <v>847</v>
+        <v>865</v>
       </c>
       <c r="G33" t="s">
-        <v>847</v>
+        <v>887</v>
       </c>
       <c r="H33" t="s">
-        <v>881</v>
+        <v>909</v>
       </c>
       <c r="I33" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -5272,28 +5372,28 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C34" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="D34" t="s">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>709</v>
+        <v>721</v>
       </c>
       <c r="F34" t="s">
-        <v>852</v>
+        <v>863</v>
       </c>
       <c r="G34" t="s">
-        <v>852</v>
+        <v>863</v>
       </c>
       <c r="H34" t="s">
-        <v>889</v>
+        <v>906</v>
       </c>
       <c r="I34" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -5301,28 +5401,28 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C35" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="D35" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>710</v>
+        <v>722</v>
       </c>
       <c r="F35" t="s">
-        <v>853</v>
+        <v>868</v>
       </c>
       <c r="G35" t="s">
-        <v>850</v>
+        <v>868</v>
       </c>
       <c r="H35" t="s">
-        <v>890</v>
+        <v>905</v>
       </c>
       <c r="I35" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -5330,28 +5430,28 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C36" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="D36" t="s">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>711</v>
+        <v>723</v>
       </c>
       <c r="F36" t="s">
-        <v>854</v>
+        <v>869</v>
       </c>
       <c r="G36" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
       <c r="H36" t="s">
-        <v>880</v>
+        <v>906</v>
       </c>
       <c r="I36" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -5359,28 +5459,28 @@
         <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C37" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="D37" t="s">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>712</v>
+        <v>724</v>
       </c>
       <c r="F37" t="s">
-        <v>849</v>
+        <v>861</v>
       </c>
       <c r="G37" t="s">
-        <v>849</v>
+        <v>888</v>
       </c>
       <c r="H37" t="s">
-        <v>886</v>
+        <v>907</v>
       </c>
       <c r="I37" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -5388,28 +5488,28 @@
         <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C38" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="D38" t="s">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="F38" t="s">
-        <v>855</v>
+        <v>870</v>
       </c>
       <c r="G38" t="s">
-        <v>855</v>
+        <v>889</v>
       </c>
       <c r="H38" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="I38" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -5417,28 +5517,28 @@
         <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C39" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="D39" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>714</v>
+        <v>726</v>
       </c>
       <c r="F39" t="s">
-        <v>853</v>
+        <v>865</v>
       </c>
       <c r="G39" t="s">
-        <v>853</v>
+        <v>865</v>
       </c>
       <c r="H39" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="I39" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -5446,28 +5546,28 @@
         <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C40" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="D40" t="s">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="F40" t="s">
-        <v>849</v>
+        <v>871</v>
       </c>
       <c r="G40" t="s">
-        <v>847</v>
+        <v>871</v>
       </c>
       <c r="H40" t="s">
-        <v>885</v>
+        <v>899</v>
       </c>
       <c r="I40" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -5475,28 +5575,28 @@
         <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C41" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="D41" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>716</v>
+        <v>728</v>
       </c>
       <c r="F41" t="s">
-        <v>849</v>
+        <v>869</v>
       </c>
       <c r="G41" t="s">
-        <v>860</v>
+        <v>869</v>
       </c>
       <c r="H41" t="s">
-        <v>892</v>
+        <v>905</v>
       </c>
       <c r="I41" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -5504,28 +5604,28 @@
         <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C42" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="D42" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
       <c r="F42" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G42" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="H42" t="s">
-        <v>892</v>
+        <v>903</v>
       </c>
       <c r="I42" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -5533,28 +5633,28 @@
         <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C43" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D43" t="s">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>718</v>
+        <v>730</v>
       </c>
       <c r="F43" t="s">
-        <v>846</v>
+        <v>865</v>
       </c>
       <c r="G43" t="s">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="H43" t="s">
-        <v>882</v>
+        <v>909</v>
       </c>
       <c r="I43" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -5562,28 +5662,28 @@
         <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C44" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="D44" t="s">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>719</v>
+        <v>731</v>
       </c>
       <c r="F44" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G44" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
       <c r="H44" t="s">
-        <v>888</v>
+        <v>909</v>
       </c>
       <c r="I44" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -5591,28 +5691,28 @@
         <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C45" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D45" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="F45" t="s">
-        <v>845</v>
+        <v>862</v>
       </c>
       <c r="G45" t="s">
-        <v>845</v>
+        <v>884</v>
       </c>
       <c r="H45" t="s">
-        <v>885</v>
+        <v>900</v>
       </c>
       <c r="I45" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -5620,28 +5720,28 @@
         <v>53</v>
       </c>
       <c r="B46" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C46" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="D46" t="s">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>721</v>
+        <v>733</v>
       </c>
       <c r="F46" t="s">
-        <v>846</v>
+        <v>865</v>
       </c>
       <c r="G46" t="s">
-        <v>857</v>
+        <v>876</v>
       </c>
       <c r="H46" t="s">
-        <v>884</v>
+        <v>899</v>
       </c>
       <c r="I46" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -5649,28 +5749,28 @@
         <v>54</v>
       </c>
       <c r="B47" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C47" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="D47" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>722</v>
+        <v>734</v>
       </c>
       <c r="F47" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="G47" t="s">
-        <v>873</v>
+        <v>860</v>
       </c>
       <c r="H47" t="s">
-        <v>884</v>
+        <v>903</v>
       </c>
       <c r="I47" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -5678,28 +5778,28 @@
         <v>55</v>
       </c>
       <c r="B48" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C48" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="D48" t="s">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="F48" t="s">
-        <v>849</v>
+        <v>862</v>
       </c>
       <c r="G48" t="s">
         <v>873</v>
       </c>
       <c r="H48" t="s">
-        <v>884</v>
+        <v>902</v>
       </c>
       <c r="I48" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -5707,28 +5807,28 @@
         <v>56</v>
       </c>
       <c r="B49" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C49" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="D49" t="s">
-        <v>557</v>
+        <v>566</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>724</v>
+        <v>736</v>
       </c>
       <c r="F49" t="s">
-        <v>849</v>
+        <v>872</v>
       </c>
       <c r="G49" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
       <c r="H49" t="s">
-        <v>886</v>
+        <v>902</v>
       </c>
       <c r="I49" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5736,28 +5836,28 @@
         <v>57</v>
       </c>
       <c r="B50" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C50" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="D50" t="s">
-        <v>558</v>
+        <v>567</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>725</v>
+        <v>737</v>
       </c>
       <c r="F50" t="s">
-        <v>857</v>
+        <v>865</v>
       </c>
       <c r="G50" t="s">
-        <v>866</v>
+        <v>890</v>
       </c>
       <c r="H50" t="s">
-        <v>889</v>
+        <v>902</v>
       </c>
       <c r="I50" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -5765,28 +5865,28 @@
         <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C51" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="D51" t="s">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>726</v>
+        <v>738</v>
       </c>
       <c r="F51" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G51" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="H51" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
       <c r="I51" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -5794,28 +5894,28 @@
         <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C52" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="D52" t="s">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>727</v>
+        <v>739</v>
       </c>
       <c r="F52" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="G52" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="H52" t="s">
-        <v>880</v>
+        <v>910</v>
       </c>
       <c r="I52" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -5823,28 +5923,28 @@
         <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C53" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="D53" t="s">
-        <v>561</v>
+        <v>570</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>728</v>
+        <v>740</v>
       </c>
       <c r="F53" t="s">
-        <v>848</v>
+        <v>873</v>
       </c>
       <c r="G53" t="s">
-        <v>860</v>
+        <v>882</v>
       </c>
       <c r="H53" t="s">
-        <v>886</v>
+        <v>905</v>
       </c>
       <c r="I53" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -5852,28 +5952,28 @@
         <v>61</v>
       </c>
       <c r="B54" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C54" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="D54" t="s">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>729</v>
+        <v>741</v>
       </c>
       <c r="F54" t="s">
-        <v>848</v>
+        <v>865</v>
       </c>
       <c r="G54" t="s">
-        <v>848</v>
+        <v>876</v>
       </c>
       <c r="H54" t="s">
-        <v>880</v>
+        <v>903</v>
       </c>
       <c r="I54" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -5881,28 +5981,28 @@
         <v>62</v>
       </c>
       <c r="B55" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C55" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="D55" t="s">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>730</v>
+        <v>742</v>
       </c>
       <c r="F55" t="s">
-        <v>846</v>
+        <v>874</v>
       </c>
       <c r="G55" t="s">
-        <v>846</v>
+        <v>874</v>
       </c>
       <c r="H55" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="I55" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -5910,28 +6010,28 @@
         <v>63</v>
       </c>
       <c r="B56" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C56" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="D56" t="s">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>731</v>
+        <v>743</v>
       </c>
       <c r="F56" t="s">
-        <v>849</v>
+        <v>864</v>
       </c>
       <c r="G56" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
       <c r="H56" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="I56" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -5939,28 +6039,28 @@
         <v>64</v>
       </c>
       <c r="B57" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C57" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="D57" t="s">
-        <v>565</v>
+        <v>574</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="F57" t="s">
-        <v>849</v>
+        <v>864</v>
       </c>
       <c r="G57" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="H57" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="I57" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -5968,28 +6068,28 @@
         <v>65</v>
       </c>
       <c r="B58" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C58" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="D58" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>733</v>
+        <v>745</v>
       </c>
       <c r="F58" t="s">
-        <v>849</v>
+        <v>862</v>
       </c>
       <c r="G58" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="H58" t="s">
-        <v>890</v>
+        <v>906</v>
       </c>
       <c r="I58" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -5997,28 +6097,28 @@
         <v>66</v>
       </c>
       <c r="B59" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C59" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="D59" t="s">
-        <v>567</v>
+        <v>576</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>734</v>
+        <v>746</v>
       </c>
       <c r="F59" t="s">
-        <v>852</v>
+        <v>865</v>
       </c>
       <c r="G59" t="s">
-        <v>852</v>
+        <v>876</v>
       </c>
       <c r="H59" t="s">
-        <v>890</v>
+        <v>906</v>
       </c>
       <c r="I59" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -6026,28 +6126,28 @@
         <v>67</v>
       </c>
       <c r="B60" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C60" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="D60" t="s">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
       <c r="F60" t="s">
-        <v>852</v>
+        <v>865</v>
       </c>
       <c r="G60" t="s">
-        <v>862</v>
+        <v>876</v>
       </c>
       <c r="H60" t="s">
-        <v>890</v>
+        <v>906</v>
       </c>
       <c r="I60" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -6055,28 +6155,28 @@
         <v>68</v>
       </c>
       <c r="B61" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C61" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="D61" t="s">
-        <v>569</v>
+        <v>578</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
       <c r="F61" t="s">
-        <v>852</v>
+        <v>865</v>
       </c>
       <c r="G61" t="s">
-        <v>852</v>
+        <v>876</v>
       </c>
       <c r="H61" t="s">
-        <v>890</v>
+        <v>906</v>
       </c>
       <c r="I61" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -6084,28 +6184,28 @@
         <v>69</v>
       </c>
       <c r="B62" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C62" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="D62" t="s">
-        <v>570</v>
+        <v>579</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
       <c r="F62" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="G62" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="H62" t="s">
-        <v>890</v>
+        <v>906</v>
       </c>
       <c r="I62" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -6113,28 +6213,28 @@
         <v>70</v>
       </c>
       <c r="B63" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C63" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="D63" t="s">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>738</v>
+        <v>750</v>
       </c>
       <c r="F63" t="s">
-        <v>859</v>
+        <v>868</v>
       </c>
       <c r="G63" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="H63" t="s">
-        <v>888</v>
+        <v>906</v>
       </c>
       <c r="I63" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -6142,28 +6242,28 @@
         <v>71</v>
       </c>
       <c r="B64" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C64" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="D64" t="s">
-        <v>572</v>
+        <v>581</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>739</v>
+        <v>751</v>
       </c>
       <c r="F64" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="G64" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="H64" t="s">
-        <v>889</v>
+        <v>906</v>
       </c>
       <c r="I64" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -6171,28 +6271,28 @@
         <v>72</v>
       </c>
       <c r="B65" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C65" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="D65" t="s">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>740</v>
+        <v>752</v>
       </c>
       <c r="F65" t="s">
-        <v>846</v>
+        <v>868</v>
       </c>
       <c r="G65" t="s">
-        <v>846</v>
+        <v>868</v>
       </c>
       <c r="H65" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="I65" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -6200,28 +6300,28 @@
         <v>73</v>
       </c>
       <c r="B66" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C66" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="D66" t="s">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>741</v>
+        <v>753</v>
       </c>
       <c r="F66" t="s">
-        <v>849</v>
+        <v>875</v>
       </c>
       <c r="G66" t="s">
-        <v>860</v>
+        <v>891</v>
       </c>
       <c r="H66" t="s">
-        <v>885</v>
+        <v>899</v>
       </c>
       <c r="I66" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -6229,28 +6329,28 @@
         <v>74</v>
       </c>
       <c r="B67" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C67" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="D67" t="s">
-        <v>575</v>
+        <v>584</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="F67" t="s">
-        <v>852</v>
+        <v>876</v>
       </c>
       <c r="G67" t="s">
-        <v>852</v>
+        <v>876</v>
       </c>
       <c r="H67" t="s">
-        <v>885</v>
+        <v>911</v>
       </c>
       <c r="I67" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -6258,28 +6358,28 @@
         <v>75</v>
       </c>
       <c r="B68" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C68" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="D68" t="s">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>743</v>
+        <v>755</v>
       </c>
       <c r="F68" t="s">
-        <v>844</v>
+        <v>862</v>
       </c>
       <c r="G68" t="s">
-        <v>844</v>
+        <v>862</v>
       </c>
       <c r="H68" t="s">
-        <v>893</v>
+        <v>906</v>
       </c>
       <c r="I68" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -6287,28 +6387,28 @@
         <v>76</v>
       </c>
       <c r="B69" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C69" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="D69" t="s">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>744</v>
+        <v>756</v>
       </c>
       <c r="F69" t="s">
-        <v>856</v>
+        <v>865</v>
       </c>
       <c r="G69" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="H69" t="s">
-        <v>886</v>
+        <v>903</v>
       </c>
       <c r="I69" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -6316,28 +6416,28 @@
         <v>77</v>
       </c>
       <c r="B70" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C70" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="D70" t="s">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="F70" t="s">
-        <v>849</v>
+        <v>868</v>
       </c>
       <c r="G70" t="s">
-        <v>857</v>
+        <v>868</v>
       </c>
       <c r="H70" t="s">
-        <v>894</v>
+        <v>903</v>
       </c>
       <c r="I70" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -6345,28 +6445,28 @@
         <v>78</v>
       </c>
       <c r="B71" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C71" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="D71" t="s">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>746</v>
+        <v>758</v>
       </c>
       <c r="F71" t="s">
-        <v>847</v>
+        <v>859</v>
       </c>
       <c r="G71" t="s">
-        <v>847</v>
+        <v>859</v>
       </c>
       <c r="H71" t="s">
-        <v>881</v>
+        <v>912</v>
       </c>
       <c r="I71" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -6374,28 +6474,28 @@
         <v>79</v>
       </c>
       <c r="B72" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C72" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="D72" t="s">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>747</v>
+        <v>759</v>
       </c>
       <c r="F72" t="s">
-        <v>846</v>
+        <v>872</v>
       </c>
       <c r="G72" t="s">
-        <v>847</v>
+        <v>890</v>
       </c>
       <c r="H72" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="I72" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -6403,28 +6503,28 @@
         <v>80</v>
       </c>
       <c r="B73" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C73" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="D73" t="s">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>748</v>
+        <v>760</v>
       </c>
       <c r="F73" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G73" t="s">
-        <v>860</v>
+        <v>873</v>
       </c>
       <c r="H73" t="s">
-        <v>895</v>
+        <v>913</v>
       </c>
       <c r="I73" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -6432,28 +6532,28 @@
         <v>81</v>
       </c>
       <c r="B74" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C74" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="D74" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>749</v>
+        <v>761</v>
       </c>
       <c r="F74" t="s">
-        <v>849</v>
+        <v>863</v>
       </c>
       <c r="G74" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="H74" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="I74" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -6461,28 +6561,28 @@
         <v>82</v>
       </c>
       <c r="B75" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C75" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="D75" t="s">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>750</v>
+        <v>762</v>
       </c>
       <c r="F75" t="s">
-        <v>854</v>
+        <v>862</v>
       </c>
       <c r="G75" t="s">
-        <v>854</v>
+        <v>863</v>
       </c>
       <c r="H75" t="s">
-        <v>888</v>
+        <v>914</v>
       </c>
       <c r="I75" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -6490,28 +6590,28 @@
         <v>83</v>
       </c>
       <c r="B76" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C76" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="D76" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>751</v>
+        <v>763</v>
       </c>
       <c r="F76" t="s">
-        <v>844</v>
+        <v>865</v>
       </c>
       <c r="G76" t="s">
-        <v>867</v>
+        <v>876</v>
       </c>
       <c r="H76" t="s">
-        <v>882</v>
+        <v>914</v>
       </c>
       <c r="I76" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -6519,28 +6619,28 @@
         <v>84</v>
       </c>
       <c r="B77" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C77" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="D77" t="s">
-        <v>585</v>
+        <v>594</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>752</v>
+        <v>764</v>
       </c>
       <c r="F77" t="s">
-        <v>844</v>
+        <v>865</v>
       </c>
       <c r="G77" t="s">
-        <v>867</v>
+        <v>876</v>
       </c>
       <c r="H77" t="s">
-        <v>889</v>
+        <v>914</v>
       </c>
       <c r="I77" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -6548,28 +6648,28 @@
         <v>85</v>
       </c>
       <c r="B78" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C78" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="D78" t="s">
-        <v>586</v>
+        <v>595</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="F78" t="s">
-        <v>861</v>
+        <v>870</v>
       </c>
       <c r="G78" t="s">
-        <v>848</v>
+        <v>870</v>
       </c>
       <c r="H78" t="s">
-        <v>885</v>
+        <v>899</v>
       </c>
       <c r="I78" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -6577,28 +6677,28 @@
         <v>86</v>
       </c>
       <c r="B79" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C79" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="D79" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>754</v>
+        <v>766</v>
       </c>
       <c r="F79" t="s">
-        <v>849</v>
+        <v>859</v>
       </c>
       <c r="G79" t="s">
-        <v>870</v>
+        <v>883</v>
       </c>
       <c r="H79" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="I79" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -6606,28 +6706,28 @@
         <v>87</v>
       </c>
       <c r="B80" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C80" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="D80" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
       <c r="F80" t="s">
-        <v>848</v>
+        <v>859</v>
       </c>
       <c r="G80" t="s">
-        <v>852</v>
+        <v>883</v>
       </c>
       <c r="H80" t="s">
-        <v>895</v>
+        <v>905</v>
       </c>
       <c r="I80" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -6635,28 +6735,28 @@
         <v>88</v>
       </c>
       <c r="B81" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C81" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="D81" t="s">
-        <v>589</v>
+        <v>598</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>756</v>
+        <v>768</v>
       </c>
       <c r="F81" t="s">
-        <v>852</v>
+        <v>877</v>
       </c>
       <c r="G81" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="H81" t="s">
-        <v>889</v>
+        <v>903</v>
       </c>
       <c r="I81" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -6664,28 +6764,28 @@
         <v>89</v>
       </c>
       <c r="B82" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C82" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="D82" t="s">
-        <v>590</v>
+        <v>599</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>757</v>
+        <v>769</v>
       </c>
       <c r="F82" t="s">
-        <v>848</v>
+        <v>865</v>
       </c>
       <c r="G82" t="s">
-        <v>848</v>
+        <v>886</v>
       </c>
       <c r="H82" t="s">
-        <v>885</v>
+        <v>914</v>
       </c>
       <c r="I82" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -6693,28 +6793,28 @@
         <v>90</v>
       </c>
       <c r="B83" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C83" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="D83" t="s">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>758</v>
+        <v>770</v>
       </c>
       <c r="F83" t="s">
-        <v>849</v>
+        <v>864</v>
       </c>
       <c r="G83" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="H83" t="s">
-        <v>887</v>
+        <v>914</v>
       </c>
       <c r="I83" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -6722,28 +6822,28 @@
         <v>91</v>
       </c>
       <c r="B84" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="D84" t="s">
-        <v>592</v>
+        <v>601</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="F84" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="G84" t="s">
-        <v>852</v>
+        <v>866</v>
       </c>
       <c r="H84" t="s">
-        <v>891</v>
+        <v>905</v>
       </c>
       <c r="I84" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -6751,28 +6851,28 @@
         <v>92</v>
       </c>
       <c r="B85" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C85" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="D85" t="s">
-        <v>593</v>
+        <v>602</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="F85" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="G85" t="s">
         <v>864</v>
       </c>
       <c r="H85" t="s">
-        <v>891</v>
+        <v>903</v>
       </c>
       <c r="I85" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -6780,28 +6880,28 @@
         <v>93</v>
       </c>
       <c r="B86" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="D86" t="s">
-        <v>594</v>
+        <v>603</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="F86" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="G86" t="s">
-        <v>857</v>
+        <v>876</v>
       </c>
       <c r="H86" t="s">
-        <v>892</v>
+        <v>904</v>
       </c>
       <c r="I86" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -6809,28 +6909,28 @@
         <v>94</v>
       </c>
       <c r="B87" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C87" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="D87" t="s">
-        <v>595</v>
+        <v>604</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
       <c r="F87" t="s">
-        <v>845</v>
+        <v>868</v>
       </c>
       <c r="G87" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="H87" t="s">
-        <v>892</v>
+        <v>907</v>
       </c>
       <c r="I87" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -6838,28 +6938,28 @@
         <v>95</v>
       </c>
       <c r="B88" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C88" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="D88" t="s">
-        <v>596</v>
+        <v>605</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>763</v>
+        <v>775</v>
       </c>
       <c r="F88" t="s">
-        <v>852</v>
+        <v>878</v>
       </c>
       <c r="G88" t="s">
-        <v>870</v>
+        <v>880</v>
       </c>
       <c r="H88" t="s">
-        <v>890</v>
+        <v>907</v>
       </c>
       <c r="I88" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -6867,28 +6967,28 @@
         <v>96</v>
       </c>
       <c r="B89" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C89" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="D89" t="s">
-        <v>597</v>
+        <v>606</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>764</v>
+        <v>776</v>
       </c>
       <c r="F89" t="s">
-        <v>849</v>
+        <v>878</v>
       </c>
       <c r="G89" t="s">
-        <v>852</v>
+        <v>873</v>
       </c>
       <c r="H89" t="s">
-        <v>888</v>
+        <v>909</v>
       </c>
       <c r="I89" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -6896,28 +6996,28 @@
         <v>97</v>
       </c>
       <c r="B90" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C90" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="D90" t="s">
-        <v>598</v>
+        <v>607</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="F90" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="G90" t="s">
-        <v>853</v>
+        <v>886</v>
       </c>
       <c r="H90" t="s">
-        <v>889</v>
+        <v>909</v>
       </c>
       <c r="I90" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -6925,28 +7025,28 @@
         <v>98</v>
       </c>
       <c r="B91" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C91" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="D91" t="s">
-        <v>599</v>
+        <v>608</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>766</v>
+        <v>778</v>
       </c>
       <c r="F91" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="G91" t="s">
-        <v>848</v>
+        <v>886</v>
       </c>
       <c r="H91" t="s">
-        <v>880</v>
+        <v>897</v>
       </c>
       <c r="I91" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -6954,28 +7054,28 @@
         <v>99</v>
       </c>
       <c r="B92" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C92" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="D92" t="s">
-        <v>600</v>
+        <v>609</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>767</v>
+        <v>779</v>
       </c>
       <c r="F92" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G92" t="s">
-        <v>875</v>
+        <v>868</v>
       </c>
       <c r="H92" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="I92" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -6983,28 +7083,28 @@
         <v>100</v>
       </c>
       <c r="B93" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C93" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="D93" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>768</v>
+        <v>780</v>
       </c>
       <c r="F93" t="s">
-        <v>849</v>
+        <v>869</v>
       </c>
       <c r="G93" t="s">
-        <v>849</v>
+        <v>869</v>
       </c>
       <c r="H93" t="s">
-        <v>892</v>
+        <v>905</v>
       </c>
       <c r="I93" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -7012,28 +7112,28 @@
         <v>101</v>
       </c>
       <c r="B94" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C94" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="D94" t="s">
-        <v>602</v>
+        <v>611</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
       <c r="F94" t="s">
-        <v>849</v>
+        <v>864</v>
       </c>
       <c r="G94" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="H94" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="I94" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -7041,28 +7141,28 @@
         <v>102</v>
       </c>
       <c r="B95" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C95" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="D95" t="s">
-        <v>603</v>
+        <v>612</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>770</v>
+        <v>782</v>
       </c>
       <c r="F95" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G95" t="s">
-        <v>860</v>
+        <v>892</v>
       </c>
       <c r="H95" t="s">
-        <v>891</v>
+        <v>914</v>
       </c>
       <c r="I95" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -7070,28 +7170,28 @@
         <v>103</v>
       </c>
       <c r="B96" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C96" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="D96" t="s">
-        <v>604</v>
+        <v>613</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>771</v>
+        <v>783</v>
       </c>
       <c r="F96" t="s">
-        <v>848</v>
+        <v>865</v>
       </c>
       <c r="G96" t="s">
-        <v>848</v>
+        <v>865</v>
       </c>
       <c r="H96" t="s">
-        <v>895</v>
+        <v>909</v>
       </c>
       <c r="I96" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -7099,28 +7199,28 @@
         <v>104</v>
       </c>
       <c r="B97" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C97" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="D97" t="s">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>772</v>
+        <v>784</v>
       </c>
       <c r="F97" t="s">
-        <v>848</v>
+        <v>865</v>
       </c>
       <c r="G97" t="s">
-        <v>847</v>
+        <v>876</v>
       </c>
       <c r="H97" t="s">
-        <v>896</v>
+        <v>914</v>
       </c>
       <c r="I97" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -7128,28 +7228,28 @@
         <v>105</v>
       </c>
       <c r="B98" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C98" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="D98" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>773</v>
+        <v>785</v>
       </c>
       <c r="F98" t="s">
-        <v>852</v>
+        <v>865</v>
       </c>
       <c r="G98" t="s">
-        <v>852</v>
+        <v>876</v>
       </c>
       <c r="H98" t="s">
-        <v>886</v>
+        <v>907</v>
       </c>
       <c r="I98" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -7157,28 +7257,28 @@
         <v>106</v>
       </c>
       <c r="B99" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C99" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="D99" t="s">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>774</v>
+        <v>786</v>
       </c>
       <c r="F99" t="s">
-        <v>848</v>
+        <v>864</v>
       </c>
       <c r="G99" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="H99" t="s">
-        <v>880</v>
+        <v>914</v>
       </c>
       <c r="I99" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -7186,28 +7286,28 @@
         <v>107</v>
       </c>
       <c r="B100" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C100" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="D100" t="s">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>775</v>
+        <v>787</v>
       </c>
       <c r="F100" t="s">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="G100" t="s">
-        <v>858</v>
+        <v>888</v>
       </c>
       <c r="H100" t="s">
-        <v>889</v>
+        <v>915</v>
       </c>
       <c r="I100" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -7215,28 +7315,28 @@
         <v>108</v>
       </c>
       <c r="B101" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C101" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="D101" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>776</v>
+        <v>788</v>
       </c>
       <c r="F101" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="G101" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="H101" t="s">
-        <v>881</v>
+        <v>897</v>
       </c>
       <c r="I101" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -7244,28 +7344,28 @@
         <v>109</v>
       </c>
       <c r="B102" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C102" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="D102" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>777</v>
+        <v>789</v>
       </c>
       <c r="F102" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="G102" t="s">
-        <v>863</v>
+        <v>882</v>
       </c>
       <c r="H102" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="I102" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -7273,28 +7373,28 @@
         <v>110</v>
       </c>
       <c r="B103" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C103" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="D103" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>778</v>
+        <v>790</v>
       </c>
       <c r="F103" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="G103" t="s">
-        <v>852</v>
+        <v>874</v>
       </c>
       <c r="H103" t="s">
-        <v>889</v>
+        <v>905</v>
       </c>
       <c r="I103" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -7302,28 +7402,28 @@
         <v>111</v>
       </c>
       <c r="B104" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C104" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="D104" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>779</v>
+        <v>791</v>
       </c>
       <c r="F104" t="s">
-        <v>847</v>
+        <v>868</v>
       </c>
       <c r="G104" t="s">
-        <v>847</v>
+        <v>868</v>
       </c>
       <c r="H104" t="s">
-        <v>885</v>
+        <v>898</v>
       </c>
       <c r="I104" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -7331,28 +7431,28 @@
         <v>112</v>
       </c>
       <c r="B105" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C105" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="D105" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>780</v>
+        <v>792</v>
       </c>
       <c r="F105" t="s">
-        <v>847</v>
+        <v>879</v>
       </c>
       <c r="G105" t="s">
-        <v>847</v>
+        <v>879</v>
       </c>
       <c r="H105" t="s">
-        <v>885</v>
+        <v>914</v>
       </c>
       <c r="I105" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -7360,28 +7460,28 @@
         <v>113</v>
       </c>
       <c r="B106" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C106" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="D106" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>781</v>
+        <v>793</v>
       </c>
       <c r="F106" t="s">
-        <v>844</v>
+        <v>868</v>
       </c>
       <c r="G106" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H106" t="s">
-        <v>886</v>
+        <v>905</v>
       </c>
       <c r="I106" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -7389,28 +7489,28 @@
         <v>114</v>
       </c>
       <c r="B107" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C107" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="D107" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>782</v>
+        <v>794</v>
       </c>
       <c r="F107" t="s">
-        <v>852</v>
+        <v>863</v>
       </c>
       <c r="G107" t="s">
-        <v>852</v>
+        <v>863</v>
       </c>
       <c r="H107" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="I107" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -7418,28 +7518,28 @@
         <v>115</v>
       </c>
       <c r="B108" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C108" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D108" t="s">
-        <v>616</v>
+        <v>625</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>783</v>
+        <v>795</v>
       </c>
       <c r="F108" t="s">
-        <v>849</v>
+        <v>863</v>
       </c>
       <c r="G108" t="s">
-        <v>853</v>
+        <v>863</v>
       </c>
       <c r="H108" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="I108" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -7447,28 +7547,28 @@
         <v>116</v>
       </c>
       <c r="B109" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C109" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="D109" t="s">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>784</v>
+        <v>796</v>
       </c>
       <c r="F109" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="G109" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="H109" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="I109" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -7476,28 +7576,28 @@
         <v>117</v>
       </c>
       <c r="B110" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C110" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="D110" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>785</v>
+        <v>797</v>
       </c>
       <c r="F110" t="s">
-        <v>849</v>
+        <v>868</v>
       </c>
       <c r="G110" t="s">
-        <v>849</v>
+        <v>868</v>
       </c>
       <c r="H110" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="I110" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -7505,28 +7605,28 @@
         <v>118</v>
       </c>
       <c r="B111" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C111" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="D111" t="s">
-        <v>619</v>
+        <v>628</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>786</v>
+        <v>798</v>
       </c>
       <c r="F111" t="s">
-        <v>853</v>
+        <v>865</v>
       </c>
       <c r="G111" t="s">
-        <v>853</v>
+        <v>869</v>
       </c>
       <c r="H111" t="s">
-        <v>889</v>
+        <v>911</v>
       </c>
       <c r="I111" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -7534,28 +7634,28 @@
         <v>119</v>
       </c>
       <c r="B112" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C112" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="D112" t="s">
-        <v>620</v>
+        <v>629</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>787</v>
+        <v>799</v>
       </c>
       <c r="F112" t="s">
-        <v>846</v>
+        <v>880</v>
       </c>
       <c r="G112" t="s">
-        <v>846</v>
+        <v>873</v>
       </c>
       <c r="H112" t="s">
-        <v>881</v>
+        <v>905</v>
       </c>
       <c r="I112" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -7563,28 +7663,28 @@
         <v>120</v>
       </c>
       <c r="B113" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C113" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="D113" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>788</v>
+        <v>800</v>
       </c>
       <c r="F113" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G113" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="H113" t="s">
-        <v>888</v>
+        <v>909</v>
       </c>
       <c r="I113" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -7592,28 +7692,28 @@
         <v>121</v>
       </c>
       <c r="B114" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C114" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="D114" t="s">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>789</v>
+        <v>801</v>
       </c>
       <c r="F114" t="s">
-        <v>849</v>
+        <v>869</v>
       </c>
       <c r="G114" t="s">
-        <v>854</v>
+        <v>869</v>
       </c>
       <c r="H114" t="s">
-        <v>886</v>
+        <v>905</v>
       </c>
       <c r="I114" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -7621,28 +7721,28 @@
         <v>122</v>
       </c>
       <c r="B115" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C115" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="D115" t="s">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>790</v>
+        <v>802</v>
       </c>
       <c r="F115" t="s">
-        <v>846</v>
+        <v>862</v>
       </c>
       <c r="G115" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="H115" t="s">
         <v>898</v>
       </c>
       <c r="I115" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -7650,28 +7750,28 @@
         <v>123</v>
       </c>
       <c r="B116" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C116" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="D116" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>791</v>
+        <v>803</v>
       </c>
       <c r="F116" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G116" t="s">
-        <v>855</v>
+        <v>876</v>
       </c>
       <c r="H116" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="I116" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -7679,28 +7779,28 @@
         <v>124</v>
       </c>
       <c r="B117" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C117" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="D117" t="s">
-        <v>625</v>
+        <v>634</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>792</v>
+        <v>804</v>
       </c>
       <c r="F117" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="G117" t="s">
-        <v>857</v>
+        <v>870</v>
       </c>
       <c r="H117" t="s">
-        <v>882</v>
+        <v>897</v>
       </c>
       <c r="I117" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -7708,28 +7808,28 @@
         <v>125</v>
       </c>
       <c r="B118" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C118" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="D118" t="s">
-        <v>626</v>
+        <v>635</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>793</v>
+        <v>805</v>
       </c>
       <c r="F118" t="s">
-        <v>849</v>
+        <v>862</v>
       </c>
       <c r="G118" t="s">
-        <v>860</v>
+        <v>883</v>
       </c>
       <c r="H118" t="s">
-        <v>886</v>
+        <v>916</v>
       </c>
       <c r="I118" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -7737,28 +7837,28 @@
         <v>126</v>
       </c>
       <c r="B119" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C119" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="D119" t="s">
-        <v>627</v>
+        <v>636</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>794</v>
+        <v>806</v>
       </c>
       <c r="F119" t="s">
-        <v>848</v>
+        <v>865</v>
       </c>
       <c r="G119" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="H119" t="s">
-        <v>899</v>
+        <v>911</v>
       </c>
       <c r="I119" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -7766,28 +7866,28 @@
         <v>127</v>
       </c>
       <c r="B120" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C120" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="D120" t="s">
-        <v>628</v>
+        <v>637</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>795</v>
+        <v>807</v>
       </c>
       <c r="F120" t="s">
-        <v>852</v>
+        <v>880</v>
       </c>
       <c r="G120" t="s">
-        <v>852</v>
+        <v>873</v>
       </c>
       <c r="H120" t="s">
-        <v>890</v>
+        <v>900</v>
       </c>
       <c r="I120" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -7795,28 +7895,28 @@
         <v>128</v>
       </c>
       <c r="B121" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C121" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="D121" t="s">
-        <v>629</v>
+        <v>638</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>796</v>
+        <v>808</v>
       </c>
       <c r="F121" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G121" t="s">
-        <v>849</v>
+        <v>876</v>
       </c>
       <c r="H121" t="s">
-        <v>887</v>
+        <v>897</v>
       </c>
       <c r="I121" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -7824,28 +7924,28 @@
         <v>129</v>
       </c>
       <c r="B122" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C122" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="D122" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>797</v>
+        <v>809</v>
       </c>
       <c r="F122" t="s">
-        <v>849</v>
+        <v>864</v>
       </c>
       <c r="G122" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
       <c r="H122" t="s">
-        <v>897</v>
+        <v>910</v>
       </c>
       <c r="I122" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -7853,28 +7953,28 @@
         <v>130</v>
       </c>
       <c r="B123" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C123" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="D123" t="s">
-        <v>631</v>
+        <v>640</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>798</v>
+        <v>810</v>
       </c>
       <c r="F123" t="s">
-        <v>849</v>
+        <v>868</v>
       </c>
       <c r="G123" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="H123" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="I123" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -7882,28 +7982,28 @@
         <v>131</v>
       </c>
       <c r="B124" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C124" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="D124" t="s">
-        <v>632</v>
+        <v>641</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>799</v>
+        <v>811</v>
       </c>
       <c r="F124" t="s">
-        <v>844</v>
+        <v>865</v>
       </c>
       <c r="G124" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="H124" t="s">
-        <v>886</v>
+        <v>904</v>
       </c>
       <c r="I124" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -7911,28 +8011,28 @@
         <v>132</v>
       </c>
       <c r="B125" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C125" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="D125" t="s">
-        <v>633</v>
+        <v>642</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="F125" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G125" t="s">
-        <v>849</v>
+        <v>886</v>
       </c>
       <c r="H125" t="s">
-        <v>891</v>
+        <v>911</v>
       </c>
       <c r="I125" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -7940,28 +8040,28 @@
         <v>133</v>
       </c>
       <c r="B126" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C126" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="D126" t="s">
-        <v>634</v>
+        <v>643</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>801</v>
+        <v>813</v>
       </c>
       <c r="F126" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="G126" t="s">
-        <v>857</v>
+        <v>876</v>
       </c>
       <c r="H126" t="s">
-        <v>890</v>
+        <v>917</v>
       </c>
       <c r="I126" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -7969,28 +8069,28 @@
         <v>134</v>
       </c>
       <c r="B127" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C127" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="D127" t="s">
-        <v>635</v>
+        <v>644</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>802</v>
+        <v>814</v>
       </c>
       <c r="F127" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="G127" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="H127" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="I127" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -7998,28 +8098,28 @@
         <v>135</v>
       </c>
       <c r="B128" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C128" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="D128" t="s">
-        <v>636</v>
+        <v>645</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="F128" t="s">
-        <v>852</v>
+        <v>865</v>
       </c>
       <c r="G128" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="H128" t="s">
-        <v>886</v>
+        <v>907</v>
       </c>
       <c r="I128" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -8027,28 +8127,28 @@
         <v>136</v>
       </c>
       <c r="B129" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C129" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="D129" t="s">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>804</v>
+        <v>816</v>
       </c>
       <c r="F129" t="s">
-        <v>844</v>
+        <v>880</v>
       </c>
       <c r="G129" t="s">
-        <v>847</v>
+        <v>873</v>
       </c>
       <c r="H129" t="s">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="I129" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -8056,28 +8156,28 @@
         <v>137</v>
       </c>
       <c r="B130" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C130" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="D130" t="s">
-        <v>638</v>
+        <v>647</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>805</v>
+        <v>817</v>
       </c>
       <c r="F130" t="s">
-        <v>849</v>
+        <v>881</v>
       </c>
       <c r="G130" t="s">
-        <v>849</v>
+        <v>893</v>
       </c>
       <c r="H130" t="s">
-        <v>886</v>
+        <v>918</v>
       </c>
       <c r="I130" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -8085,28 +8185,28 @@
         <v>138</v>
       </c>
       <c r="B131" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C131" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="D131" t="s">
-        <v>639</v>
+        <v>648</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>806</v>
+        <v>818</v>
       </c>
       <c r="F131" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="G131" t="s">
-        <v>852</v>
+        <v>878</v>
       </c>
       <c r="H131" t="s">
-        <v>886</v>
+        <v>897</v>
       </c>
       <c r="I131" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -8114,28 +8214,28 @@
         <v>139</v>
       </c>
       <c r="B132" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C132" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="D132" t="s">
-        <v>640</v>
+        <v>649</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>807</v>
+        <v>819</v>
       </c>
       <c r="F132" t="s">
-        <v>846</v>
+        <v>859</v>
       </c>
       <c r="G132" t="s">
-        <v>846</v>
+        <v>863</v>
       </c>
       <c r="H132" t="s">
-        <v>882</v>
+        <v>897</v>
       </c>
       <c r="I132" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -8143,28 +8243,28 @@
         <v>140</v>
       </c>
       <c r="B133" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C133" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="D133" t="s">
-        <v>641</v>
+        <v>650</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>808</v>
+        <v>820</v>
       </c>
       <c r="F133" t="s">
-        <v>846</v>
+        <v>865</v>
       </c>
       <c r="G133" t="s">
-        <v>846</v>
+        <v>865</v>
       </c>
       <c r="H133" t="s">
-        <v>884</v>
+        <v>897</v>
       </c>
       <c r="I133" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -8172,28 +8272,28 @@
         <v>141</v>
       </c>
       <c r="B134" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C134" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="D134" t="s">
-        <v>642</v>
+        <v>651</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>809</v>
+        <v>821</v>
       </c>
       <c r="F134" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="G134" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="H134" t="s">
-        <v>881</v>
+        <v>897</v>
       </c>
       <c r="I134" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -8201,28 +8301,28 @@
         <v>142</v>
       </c>
       <c r="B135" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C135" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="D135" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>810</v>
+        <v>822</v>
       </c>
       <c r="F135" t="s">
-        <v>848</v>
+        <v>862</v>
       </c>
       <c r="G135" t="s">
-        <v>848</v>
+        <v>862</v>
       </c>
       <c r="H135" t="s">
-        <v>885</v>
+        <v>900</v>
       </c>
       <c r="I135" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -8230,28 +8330,28 @@
         <v>143</v>
       </c>
       <c r="B136" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C136" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="D136" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>811</v>
+        <v>823</v>
       </c>
       <c r="F136" t="s">
-        <v>847</v>
+        <v>862</v>
       </c>
       <c r="G136" t="s">
-        <v>847</v>
+        <v>862</v>
       </c>
       <c r="H136" t="s">
-        <v>881</v>
+        <v>902</v>
       </c>
       <c r="I136" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -8259,28 +8359,28 @@
         <v>144</v>
       </c>
       <c r="B137" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C137" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="D137" t="s">
-        <v>645</v>
+        <v>654</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>812</v>
+        <v>824</v>
       </c>
       <c r="F137" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="G137" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="H137" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="I137" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -8288,28 +8388,28 @@
         <v>145</v>
       </c>
       <c r="B138" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C138" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="D138" t="s">
-        <v>646</v>
+        <v>655</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="F138" t="s">
-        <v>855</v>
+        <v>864</v>
       </c>
       <c r="G138" t="s">
-        <v>853</v>
+        <v>864</v>
       </c>
       <c r="H138" t="s">
-        <v>879</v>
+        <v>903</v>
       </c>
       <c r="I138" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -8317,28 +8417,28 @@
         <v>146</v>
       </c>
       <c r="B139" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C139" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="D139" t="s">
-        <v>647</v>
+        <v>656</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>814</v>
+        <v>826</v>
       </c>
       <c r="F139" t="s">
-        <v>849</v>
+        <v>863</v>
       </c>
       <c r="G139" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="H139" t="s">
-        <v>891</v>
+        <v>903</v>
       </c>
       <c r="I139" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -8346,28 +8446,28 @@
         <v>147</v>
       </c>
       <c r="B140" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C140" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="D140" t="s">
-        <v>648</v>
+        <v>657</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>815</v>
+        <v>827</v>
       </c>
       <c r="F140" t="s">
-        <v>849</v>
+        <v>868</v>
       </c>
       <c r="G140" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="H140" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="I140" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -8375,28 +8475,28 @@
         <v>148</v>
       </c>
       <c r="B141" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C141" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="D141" t="s">
-        <v>649</v>
+        <v>658</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
       <c r="F141" t="s">
-        <v>849</v>
+        <v>871</v>
       </c>
       <c r="G141" t="s">
-        <v>860</v>
+        <v>869</v>
       </c>
       <c r="H141" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="I141" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -8404,28 +8504,28 @@
         <v>149</v>
       </c>
       <c r="B142" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C142" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="D142" t="s">
-        <v>650</v>
+        <v>659</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>817</v>
+        <v>829</v>
       </c>
       <c r="F142" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="G142" t="s">
-        <v>875</v>
+        <v>884</v>
       </c>
       <c r="H142" t="s">
-        <v>891</v>
+        <v>907</v>
       </c>
       <c r="I142" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -8433,28 +8533,28 @@
         <v>150</v>
       </c>
       <c r="B143" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C143" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="D143" t="s">
-        <v>651</v>
+        <v>660</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>818</v>
+        <v>830</v>
       </c>
       <c r="F143" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G143" t="s">
-        <v>860</v>
+        <v>891</v>
       </c>
       <c r="H143" t="s">
-        <v>891</v>
+        <v>907</v>
       </c>
       <c r="I143" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -8462,28 +8562,28 @@
         <v>151</v>
       </c>
       <c r="B144" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C144" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="D144" t="s">
-        <v>652</v>
+        <v>661</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>819</v>
+        <v>831</v>
       </c>
       <c r="F144" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="G144" t="s">
-        <v>863</v>
+        <v>876</v>
       </c>
       <c r="H144" t="s">
-        <v>895</v>
+        <v>907</v>
       </c>
       <c r="I144" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -8491,28 +8591,28 @@
         <v>152</v>
       </c>
       <c r="B145" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C145" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="D145" t="s">
-        <v>653</v>
+        <v>662</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>820</v>
+        <v>832</v>
       </c>
       <c r="F145" t="s">
-        <v>848</v>
+        <v>882</v>
       </c>
       <c r="G145" t="s">
-        <v>848</v>
+        <v>892</v>
       </c>
       <c r="H145" t="s">
-        <v>885</v>
+        <v>907</v>
       </c>
       <c r="I145" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -8520,28 +8620,28 @@
         <v>153</v>
       </c>
       <c r="B146" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C146" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="D146" t="s">
-        <v>654</v>
+        <v>663</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>821</v>
+        <v>833</v>
       </c>
       <c r="F146" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G146" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
       <c r="H146" t="s">
-        <v>886</v>
+        <v>907</v>
       </c>
       <c r="I146" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -8549,28 +8649,28 @@
         <v>154</v>
       </c>
       <c r="B147" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C147" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="D147" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>822</v>
+        <v>834</v>
       </c>
       <c r="F147" t="s">
-        <v>849</v>
+        <v>879</v>
       </c>
       <c r="G147" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="H147" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
       <c r="I147" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -8578,28 +8678,28 @@
         <v>155</v>
       </c>
       <c r="B148" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C148" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="D148" t="s">
-        <v>656</v>
+        <v>665</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>823</v>
+        <v>835</v>
       </c>
       <c r="F148" t="s">
-        <v>848</v>
+        <v>864</v>
       </c>
       <c r="G148" t="s">
-        <v>848</v>
+        <v>864</v>
       </c>
       <c r="H148" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="I148" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -8607,28 +8707,28 @@
         <v>156</v>
       </c>
       <c r="B149" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C149" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="D149" t="s">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>824</v>
+        <v>836</v>
       </c>
       <c r="F149" t="s">
-        <v>852</v>
+        <v>865</v>
       </c>
       <c r="G149" t="s">
-        <v>852</v>
+        <v>876</v>
       </c>
       <c r="H149" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="I149" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -8636,28 +8736,28 @@
         <v>157</v>
       </c>
       <c r="B150" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C150" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="D150" t="s">
-        <v>658</v>
+        <v>667</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>825</v>
+        <v>837</v>
       </c>
       <c r="F150" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="G150" t="s">
-        <v>874</v>
+        <v>893</v>
       </c>
       <c r="H150" t="s">
-        <v>886</v>
+        <v>903</v>
       </c>
       <c r="I150" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -8665,28 +8765,28 @@
         <v>158</v>
       </c>
       <c r="B151" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C151" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="D151" t="s">
-        <v>659</v>
+        <v>668</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>826</v>
+        <v>838</v>
       </c>
       <c r="F151" t="s">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="G151" t="s">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="H151" t="s">
-        <v>890</v>
+        <v>910</v>
       </c>
       <c r="I151" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -8694,28 +8794,28 @@
         <v>159</v>
       </c>
       <c r="B152" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C152" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="D152" t="s">
-        <v>660</v>
+        <v>669</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>827</v>
+        <v>839</v>
       </c>
       <c r="F152" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="G152" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="H152" t="s">
-        <v>890</v>
+        <v>906</v>
       </c>
       <c r="I152" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -8723,28 +8823,28 @@
         <v>160</v>
       </c>
       <c r="B153" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C153" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="D153" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>828</v>
+        <v>840</v>
       </c>
       <c r="F153" t="s">
-        <v>849</v>
+        <v>875</v>
       </c>
       <c r="G153" t="s">
-        <v>868</v>
+        <v>891</v>
       </c>
       <c r="H153" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="I153" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -8752,28 +8852,28 @@
         <v>161</v>
       </c>
       <c r="B154" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C154" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="D154" t="s">
-        <v>662</v>
+        <v>671</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>829</v>
+        <v>841</v>
       </c>
       <c r="F154" t="s">
-        <v>846</v>
+        <v>868</v>
       </c>
       <c r="G154" t="s">
-        <v>846</v>
+        <v>868</v>
       </c>
       <c r="H154" t="s">
-        <v>881</v>
+        <v>906</v>
       </c>
       <c r="I154" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -8781,28 +8881,28 @@
         <v>162</v>
       </c>
       <c r="B155" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C155" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="D155" t="s">
-        <v>663</v>
+        <v>672</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>830</v>
+        <v>842</v>
       </c>
       <c r="F155" t="s">
-        <v>846</v>
+        <v>868</v>
       </c>
       <c r="G155" t="s">
-        <v>846</v>
+        <v>868</v>
       </c>
       <c r="H155" t="s">
-        <v>890</v>
+        <v>906</v>
       </c>
       <c r="I155" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -8810,28 +8910,28 @@
         <v>163</v>
       </c>
       <c r="B156" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C156" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D156" t="s">
-        <v>664</v>
+        <v>673</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>831</v>
+        <v>843</v>
       </c>
       <c r="F156" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G156" t="s">
-        <v>860</v>
+        <v>884</v>
       </c>
       <c r="H156" t="s">
-        <v>892</v>
+        <v>907</v>
       </c>
       <c r="I156" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -8839,28 +8939,28 @@
         <v>164</v>
       </c>
       <c r="B157" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C157" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D157" t="s">
-        <v>665</v>
+        <v>674</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>832</v>
+        <v>844</v>
       </c>
       <c r="F157" t="s">
-        <v>849</v>
+        <v>862</v>
       </c>
       <c r="G157" t="s">
-        <v>849</v>
+        <v>862</v>
       </c>
       <c r="H157" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="I157" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -8868,28 +8968,28 @@
         <v>165</v>
       </c>
       <c r="B158" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C158" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="D158" t="s">
-        <v>666</v>
+        <v>675</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>833</v>
+        <v>845</v>
       </c>
       <c r="F158" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="G158" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="H158" t="s">
-        <v>889</v>
+        <v>906</v>
       </c>
       <c r="I158" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -8897,28 +8997,28 @@
         <v>166</v>
       </c>
       <c r="B159" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C159" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="D159" t="s">
-        <v>667</v>
+        <v>676</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>834</v>
+        <v>846</v>
       </c>
       <c r="F159" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G159" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
       <c r="H159" t="s">
-        <v>880</v>
+        <v>909</v>
       </c>
       <c r="I159" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -8926,28 +9026,28 @@
         <v>167</v>
       </c>
       <c r="B160" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C160" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="D160" t="s">
-        <v>668</v>
+        <v>677</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>835</v>
+        <v>847</v>
       </c>
       <c r="F160" t="s">
-        <v>848</v>
+        <v>865</v>
       </c>
       <c r="G160" t="s">
-        <v>878</v>
+        <v>865</v>
       </c>
       <c r="H160" t="s">
-        <v>882</v>
+        <v>909</v>
       </c>
       <c r="I160" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -8955,28 +9055,28 @@
         <v>168</v>
       </c>
       <c r="B161" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C161" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="D161" t="s">
-        <v>669</v>
+        <v>678</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>836</v>
+        <v>848</v>
       </c>
       <c r="F161" t="s">
-        <v>864</v>
+        <v>873</v>
       </c>
       <c r="G161" t="s">
-        <v>857</v>
+        <v>882</v>
       </c>
       <c r="H161" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="I161" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -8984,28 +9084,28 @@
         <v>169</v>
       </c>
       <c r="B162" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C162" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D162" t="s">
-        <v>670</v>
+        <v>679</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>837</v>
+        <v>849</v>
       </c>
       <c r="F162" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G162" t="s">
-        <v>849</v>
+        <v>876</v>
       </c>
       <c r="H162" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="I162" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -9013,28 +9113,28 @@
         <v>170</v>
       </c>
       <c r="B163" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C163" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="D163" t="s">
-        <v>671</v>
+        <v>680</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>838</v>
+        <v>850</v>
       </c>
       <c r="F163" t="s">
-        <v>849</v>
+        <v>864</v>
       </c>
       <c r="G163" t="s">
-        <v>873</v>
+        <v>894</v>
       </c>
       <c r="H163" t="s">
-        <v>880</v>
+        <v>900</v>
       </c>
       <c r="I163" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -9042,28 +9142,28 @@
         <v>171</v>
       </c>
       <c r="B164" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C164" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="D164" t="s">
-        <v>672</v>
+        <v>681</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>839</v>
+        <v>851</v>
       </c>
       <c r="F164" t="s">
-        <v>848</v>
+        <v>880</v>
       </c>
       <c r="G164" t="s">
-        <v>848</v>
+        <v>873</v>
       </c>
       <c r="H164" t="s">
-        <v>885</v>
+        <v>908</v>
       </c>
       <c r="I164" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -9071,28 +9171,28 @@
         <v>172</v>
       </c>
       <c r="B165" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C165" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="D165" t="s">
-        <v>673</v>
+        <v>682</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>840</v>
+        <v>852</v>
       </c>
       <c r="F165" t="s">
-        <v>856</v>
+        <v>865</v>
       </c>
       <c r="G165" t="s">
-        <v>850</v>
+        <v>865</v>
       </c>
       <c r="H165" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="I165" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -9100,28 +9200,28 @@
         <v>173</v>
       </c>
       <c r="B166" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C166" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="D166" t="s">
-        <v>674</v>
+        <v>683</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>841</v>
+        <v>853</v>
       </c>
       <c r="F166" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G166" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
       <c r="H166" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="I166" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -9129,28 +9229,28 @@
         <v>174</v>
       </c>
       <c r="B167" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C167" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="D167" t="s">
-        <v>675</v>
+        <v>684</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="F167" t="s">
-        <v>845</v>
+        <v>864</v>
       </c>
       <c r="G167" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="H167" t="s">
-        <v>889</v>
+        <v>903</v>
       </c>
       <c r="I167" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -9158,28 +9258,115 @@
         <v>175</v>
       </c>
       <c r="B168" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C168" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="D168" t="s">
-        <v>676</v>
+        <v>685</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>843</v>
+        <v>855</v>
       </c>
       <c r="F168" t="s">
-        <v>849</v>
+        <v>872</v>
       </c>
       <c r="G168" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="H168" t="s">
-        <v>892</v>
+        <v>919</v>
       </c>
       <c r="I168" t="s">
-        <v>904</v>
+        <v>920</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9">
+      <c r="A169" t="s">
+        <v>176</v>
+      </c>
+      <c r="B169" t="s">
+        <v>346</v>
+      </c>
+      <c r="C169" t="s">
+        <v>516</v>
+      </c>
+      <c r="D169" t="s">
+        <v>686</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="F169" t="s">
+        <v>865</v>
+      </c>
+      <c r="G169" t="s">
+        <v>865</v>
+      </c>
+      <c r="H169" t="s">
+        <v>909</v>
+      </c>
+      <c r="I169" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9">
+      <c r="A170" t="s">
+        <v>177</v>
+      </c>
+      <c r="B170" t="s">
+        <v>347</v>
+      </c>
+      <c r="C170" t="s">
+        <v>517</v>
+      </c>
+      <c r="D170" t="s">
+        <v>687</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="F170" t="s">
+        <v>860</v>
+      </c>
+      <c r="G170" t="s">
+        <v>886</v>
+      </c>
+      <c r="H170" t="s">
+        <v>905</v>
+      </c>
+      <c r="I170" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9">
+      <c r="A171" t="s">
+        <v>178</v>
+      </c>
+      <c r="B171" t="s">
+        <v>348</v>
+      </c>
+      <c r="C171" t="s">
+        <v>518</v>
+      </c>
+      <c r="D171" t="s">
+        <v>688</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="F171" t="s">
+        <v>865</v>
+      </c>
+      <c r="G171" t="s">
+        <v>887</v>
+      </c>
+      <c r="H171" t="s">
+        <v>909</v>
+      </c>
+      <c r="I171" t="s">
+        <v>920</v>
       </c>
     </row>
   </sheetData>
@@ -9351,6 +9538,9 @@
     <hyperlink ref="E166" r:id="rId165"/>
     <hyperlink ref="E167" r:id="rId166"/>
     <hyperlink ref="E168" r:id="rId167"/>
+    <hyperlink ref="E169" r:id="rId168"/>
+    <hyperlink ref="E170" r:id="rId169"/>
+    <hyperlink ref="E171" r:id="rId170"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9386,370 +9576,370 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>905</v>
+        <v>921</v>
       </c>
       <c r="B2" t="s">
-        <v>921</v>
+        <v>937</v>
       </c>
       <c r="C2" t="s">
-        <v>892</v>
+        <v>909</v>
       </c>
       <c r="D2" t="s">
-        <v>937</v>
+        <v>953</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>953</v>
+        <v>969</v>
       </c>
       <c r="F2" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G2" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>906</v>
+        <v>922</v>
       </c>
       <c r="B3" t="s">
-        <v>922</v>
+        <v>938</v>
       </c>
       <c r="C3" t="s">
-        <v>887</v>
+        <v>904</v>
       </c>
       <c r="D3" t="s">
-        <v>938</v>
+        <v>954</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>954</v>
+        <v>970</v>
       </c>
       <c r="F3" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G3" t="s">
-        <v>868</v>
+        <v>884</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>907</v>
+        <v>923</v>
       </c>
       <c r="B4" t="s">
-        <v>923</v>
+        <v>939</v>
       </c>
       <c r="C4" t="s">
-        <v>884</v>
+        <v>902</v>
       </c>
       <c r="D4" t="s">
-        <v>939</v>
+        <v>955</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>955</v>
+        <v>971</v>
       </c>
       <c r="F4" t="s">
-        <v>856</v>
+        <v>872</v>
       </c>
       <c r="G4" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>908</v>
+        <v>924</v>
       </c>
       <c r="B5" t="s">
-        <v>924</v>
+        <v>940</v>
       </c>
       <c r="C5" t="s">
-        <v>879</v>
+        <v>895</v>
       </c>
       <c r="D5" t="s">
-        <v>940</v>
+        <v>956</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>956</v>
+        <v>972</v>
       </c>
       <c r="F5" t="s">
-        <v>855</v>
+        <v>871</v>
       </c>
       <c r="G5" t="s">
-        <v>855</v>
+        <v>871</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>909</v>
+        <v>925</v>
       </c>
       <c r="B6" t="s">
-        <v>925</v>
+        <v>941</v>
       </c>
       <c r="C6" t="s">
-        <v>882</v>
+        <v>900</v>
       </c>
       <c r="D6" t="s">
-        <v>941</v>
+        <v>957</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>957</v>
+        <v>973</v>
       </c>
       <c r="F6" t="s">
-        <v>848</v>
+        <v>864</v>
       </c>
       <c r="G6" t="s">
-        <v>848</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>910</v>
+        <v>926</v>
       </c>
       <c r="B7" t="s">
-        <v>926</v>
+        <v>942</v>
       </c>
       <c r="C7" t="s">
-        <v>889</v>
+        <v>905</v>
       </c>
       <c r="D7" t="s">
-        <v>942</v>
+        <v>958</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>958</v>
+        <v>974</v>
       </c>
       <c r="F7" t="s">
-        <v>856</v>
+        <v>872</v>
       </c>
       <c r="G7" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>911</v>
+        <v>927</v>
       </c>
       <c r="B8" t="s">
-        <v>927</v>
+        <v>943</v>
       </c>
       <c r="C8" t="s">
-        <v>890</v>
+        <v>906</v>
       </c>
       <c r="D8" t="s">
-        <v>943</v>
+        <v>959</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>959</v>
+        <v>975</v>
       </c>
       <c r="F8" t="s">
-        <v>856</v>
+        <v>872</v>
       </c>
       <c r="G8" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>912</v>
+        <v>928</v>
       </c>
       <c r="B9" t="s">
-        <v>928</v>
+        <v>944</v>
       </c>
       <c r="C9" t="s">
-        <v>880</v>
+        <v>896</v>
       </c>
       <c r="D9" t="s">
-        <v>944</v>
+        <v>960</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>960</v>
+        <v>976</v>
       </c>
       <c r="F9" t="s">
-        <v>856</v>
+        <v>872</v>
       </c>
       <c r="G9" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>913</v>
+        <v>929</v>
       </c>
       <c r="B10" t="s">
-        <v>929</v>
+        <v>945</v>
       </c>
       <c r="C10" t="s">
-        <v>895</v>
+        <v>914</v>
       </c>
       <c r="D10" t="s">
-        <v>945</v>
+        <v>961</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>961</v>
+        <v>977</v>
       </c>
       <c r="F10" t="s">
-        <v>856</v>
+        <v>872</v>
       </c>
       <c r="G10" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>914</v>
+        <v>930</v>
       </c>
       <c r="B11" t="s">
-        <v>930</v>
+        <v>946</v>
       </c>
       <c r="C11" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="D11" t="s">
-        <v>946</v>
+        <v>962</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>962</v>
+        <v>978</v>
       </c>
       <c r="F11" t="s">
-        <v>856</v>
+        <v>872</v>
       </c>
       <c r="G11" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>915</v>
+        <v>931</v>
       </c>
       <c r="B12" t="s">
-        <v>931</v>
+        <v>947</v>
       </c>
       <c r="C12" t="s">
-        <v>888</v>
+        <v>899</v>
       </c>
       <c r="D12" t="s">
-        <v>947</v>
+        <v>963</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>963</v>
+        <v>979</v>
       </c>
       <c r="F12" t="s">
-        <v>856</v>
+        <v>872</v>
       </c>
       <c r="G12" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>916</v>
+        <v>932</v>
       </c>
       <c r="B13" t="s">
-        <v>932</v>
+        <v>948</v>
       </c>
       <c r="C13" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="D13" t="s">
-        <v>948</v>
+        <v>964</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>964</v>
+        <v>980</v>
       </c>
       <c r="F13" t="s">
-        <v>864</v>
+        <v>880</v>
       </c>
       <c r="G13" t="s">
-        <v>866</v>
+        <v>882</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>917</v>
+        <v>933</v>
       </c>
       <c r="B14" t="s">
-        <v>933</v>
+        <v>949</v>
       </c>
       <c r="C14" t="s">
-        <v>881</v>
+        <v>898</v>
       </c>
       <c r="D14" t="s">
-        <v>949</v>
+        <v>965</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>965</v>
+        <v>981</v>
       </c>
       <c r="F14" t="s">
-        <v>856</v>
+        <v>872</v>
       </c>
       <c r="G14" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>918</v>
+        <v>934</v>
       </c>
       <c r="B15" t="s">
-        <v>934</v>
+        <v>950</v>
       </c>
       <c r="C15" t="s">
-        <v>893</v>
+        <v>912</v>
       </c>
       <c r="D15" t="s">
-        <v>950</v>
+        <v>966</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>966</v>
+        <v>982</v>
       </c>
       <c r="F15" t="s">
-        <v>848</v>
+        <v>864</v>
       </c>
       <c r="G15" t="s">
-        <v>848</v>
+        <v>864</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>919</v>
+        <v>935</v>
       </c>
       <c r="B16" t="s">
-        <v>935</v>
+        <v>951</v>
       </c>
       <c r="C16" t="s">
-        <v>891</v>
+        <v>907</v>
       </c>
       <c r="D16" t="s">
-        <v>951</v>
+        <v>967</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>967</v>
+        <v>983</v>
       </c>
       <c r="F16" t="s">
-        <v>856</v>
+        <v>872</v>
       </c>
       <c r="G16" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>920</v>
+        <v>936</v>
       </c>
       <c r="B17" t="s">
-        <v>936</v>
+        <v>952</v>
       </c>
       <c r="C17" t="s">
-        <v>886</v>
+        <v>897</v>
       </c>
       <c r="D17" t="s">
-        <v>952</v>
+        <v>968</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>968</v>
+        <v>984</v>
       </c>
       <c r="F17" t="s">
-        <v>856</v>
+        <v>872</v>
       </c>
       <c r="G17" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
     </row>
   </sheetData>
@@ -9803,812 +9993,812 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>969</v>
+        <v>985</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>970</v>
+        <v>986</v>
       </c>
       <c r="B2" t="s">
-        <v>1005</v>
+        <v>1021</v>
       </c>
       <c r="C2" t="s">
-        <v>1040</v>
+        <v>1056</v>
       </c>
       <c r="D2" t="s">
-        <v>1075</v>
+        <v>1091</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1110</v>
+        <v>1126</v>
       </c>
       <c r="F2" t="s">
-        <v>865</v>
+        <v>881</v>
       </c>
       <c r="G2" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>971</v>
+        <v>987</v>
       </c>
       <c r="B3" t="s">
-        <v>1006</v>
+        <v>1022</v>
       </c>
       <c r="C3" t="s">
-        <v>1041</v>
+        <v>1057</v>
       </c>
       <c r="D3" t="s">
-        <v>1076</v>
+        <v>1092</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1111</v>
+        <v>1127</v>
       </c>
       <c r="F3" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="G3" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>972</v>
+        <v>988</v>
       </c>
       <c r="B4" t="s">
-        <v>1007</v>
+        <v>1023</v>
       </c>
       <c r="C4" t="s">
-        <v>1042</v>
+        <v>1058</v>
       </c>
       <c r="D4" t="s">
-        <v>1077</v>
+        <v>1093</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1112</v>
+        <v>1128</v>
       </c>
       <c r="F4" t="s">
-        <v>1145</v>
+        <v>1161</v>
       </c>
       <c r="G4" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>973</v>
+        <v>989</v>
       </c>
       <c r="B5" t="s">
-        <v>1008</v>
+        <v>1024</v>
       </c>
       <c r="C5" t="s">
-        <v>1043</v>
+        <v>1059</v>
       </c>
       <c r="D5" t="s">
-        <v>1078</v>
+        <v>1094</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1113</v>
+        <v>1129</v>
       </c>
       <c r="F5" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="G5" t="s">
-        <v>1146</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>974</v>
+        <v>990</v>
       </c>
       <c r="B6" t="s">
-        <v>1009</v>
+        <v>1025</v>
       </c>
       <c r="C6" t="s">
-        <v>1044</v>
+        <v>1060</v>
       </c>
       <c r="D6" t="s">
-        <v>1079</v>
+        <v>1095</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1114</v>
+        <v>1130</v>
       </c>
       <c r="F6" t="s">
-        <v>1145</v>
+        <v>1161</v>
       </c>
       <c r="G6" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>975</v>
+        <v>991</v>
       </c>
       <c r="B7" t="s">
-        <v>1010</v>
+        <v>1026</v>
       </c>
       <c r="C7" t="s">
-        <v>1045</v>
+        <v>1061</v>
       </c>
       <c r="D7" t="s">
-        <v>1080</v>
+        <v>1096</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1115</v>
+        <v>1131</v>
       </c>
       <c r="F7" t="s">
-        <v>1145</v>
+        <v>1161</v>
       </c>
       <c r="G7" t="s">
-        <v>1146</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>976</v>
+        <v>992</v>
       </c>
       <c r="B8" t="s">
-        <v>1011</v>
+        <v>1027</v>
       </c>
       <c r="C8" t="s">
-        <v>1046</v>
+        <v>1062</v>
       </c>
       <c r="D8" t="s">
-        <v>1081</v>
+        <v>1097</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1116</v>
+        <v>1132</v>
       </c>
       <c r="F8" t="s">
-        <v>1145</v>
+        <v>1161</v>
       </c>
       <c r="G8" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>977</v>
+        <v>993</v>
       </c>
       <c r="B9" t="s">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="C9" t="s">
-        <v>1047</v>
+        <v>1063</v>
       </c>
       <c r="D9" t="s">
-        <v>1082</v>
+        <v>1098</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1117</v>
+        <v>1133</v>
       </c>
       <c r="F9" t="s">
-        <v>871</v>
+        <v>887</v>
       </c>
       <c r="G9" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>978</v>
+        <v>994</v>
       </c>
       <c r="B10" t="s">
-        <v>1013</v>
+        <v>1029</v>
       </c>
       <c r="C10" t="s">
-        <v>1048</v>
+        <v>1064</v>
       </c>
       <c r="D10" t="s">
-        <v>1083</v>
+        <v>1099</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1118</v>
+        <v>1134</v>
       </c>
       <c r="F10" t="s">
-        <v>845</v>
+        <v>860</v>
       </c>
       <c r="G10" t="s">
-        <v>845</v>
+        <v>861</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>979</v>
+        <v>995</v>
       </c>
       <c r="B11" t="s">
-        <v>1014</v>
+        <v>1030</v>
       </c>
       <c r="C11" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="D11" t="s">
-        <v>1084</v>
+        <v>1100</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1119</v>
+        <v>1135</v>
       </c>
       <c r="F11" t="s">
-        <v>1145</v>
+        <v>1161</v>
       </c>
       <c r="G11" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>980</v>
+        <v>996</v>
       </c>
       <c r="B12" t="s">
-        <v>1015</v>
+        <v>1031</v>
       </c>
       <c r="C12" t="s">
-        <v>1050</v>
+        <v>1066</v>
       </c>
       <c r="D12" t="s">
-        <v>1085</v>
+        <v>1101</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1120</v>
+        <v>1136</v>
       </c>
       <c r="F12" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="G12" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>981</v>
+        <v>997</v>
       </c>
       <c r="B13" t="s">
-        <v>1016</v>
+        <v>1032</v>
       </c>
       <c r="C13" t="s">
-        <v>1051</v>
+        <v>1067</v>
       </c>
       <c r="D13" t="s">
-        <v>1086</v>
+        <v>1102</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1121</v>
+        <v>1137</v>
       </c>
       <c r="F13" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="G13" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>982</v>
+        <v>998</v>
       </c>
       <c r="B14" t="s">
-        <v>1017</v>
+        <v>1033</v>
       </c>
       <c r="C14" t="s">
-        <v>1052</v>
+        <v>1068</v>
       </c>
       <c r="D14" t="s">
-        <v>1087</v>
+        <v>1103</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1122</v>
+        <v>1138</v>
       </c>
       <c r="F14" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="G14" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>983</v>
+        <v>999</v>
       </c>
       <c r="B15" t="s">
-        <v>1018</v>
+        <v>1034</v>
       </c>
       <c r="C15" t="s">
-        <v>1053</v>
+        <v>1069</v>
       </c>
       <c r="D15" t="s">
-        <v>1088</v>
+        <v>1104</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1123</v>
+        <v>1139</v>
       </c>
       <c r="F15" t="s">
-        <v>865</v>
+        <v>881</v>
       </c>
       <c r="G15" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>984</v>
+        <v>1000</v>
       </c>
       <c r="B16" t="s">
-        <v>1019</v>
+        <v>1035</v>
       </c>
       <c r="C16" t="s">
-        <v>1054</v>
+        <v>1070</v>
       </c>
       <c r="D16" t="s">
-        <v>1089</v>
+        <v>1105</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1124</v>
+        <v>1140</v>
       </c>
       <c r="F16" t="s">
-        <v>1145</v>
+        <v>1161</v>
       </c>
       <c r="G16" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>985</v>
+        <v>1001</v>
       </c>
       <c r="B17" t="s">
-        <v>1020</v>
+        <v>1036</v>
       </c>
       <c r="C17" t="s">
-        <v>1055</v>
+        <v>1071</v>
       </c>
       <c r="D17" t="s">
-        <v>1090</v>
+        <v>1106</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1125</v>
+        <v>1141</v>
       </c>
       <c r="F17" t="s">
-        <v>845</v>
+        <v>860</v>
       </c>
       <c r="G17" t="s">
-        <v>877</v>
+        <v>893</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>986</v>
+        <v>1002</v>
       </c>
       <c r="B18" t="s">
-        <v>1021</v>
+        <v>1037</v>
       </c>
       <c r="C18" t="s">
-        <v>1056</v>
+        <v>1072</v>
       </c>
       <c r="D18" t="s">
-        <v>1091</v>
+        <v>1107</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1126</v>
+        <v>1142</v>
       </c>
       <c r="F18" t="s">
-        <v>1145</v>
+        <v>1161</v>
       </c>
       <c r="G18" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>987</v>
+        <v>1003</v>
       </c>
       <c r="B19" t="s">
-        <v>1022</v>
+        <v>1038</v>
       </c>
       <c r="C19" t="s">
-        <v>1057</v>
+        <v>1073</v>
       </c>
       <c r="D19" t="s">
-        <v>1092</v>
+        <v>1108</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1127</v>
+        <v>1143</v>
       </c>
       <c r="F19" t="s">
-        <v>1145</v>
+        <v>1161</v>
       </c>
       <c r="G19" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>988</v>
+        <v>1004</v>
       </c>
       <c r="B20" t="s">
-        <v>1023</v>
+        <v>1039</v>
       </c>
       <c r="C20" t="s">
-        <v>1058</v>
+        <v>1074</v>
       </c>
       <c r="D20" t="s">
-        <v>1093</v>
+        <v>1109</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1128</v>
+        <v>1144</v>
       </c>
       <c r="F20" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="G20" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>989</v>
+        <v>1005</v>
       </c>
       <c r="B21" t="s">
-        <v>1024</v>
+        <v>1040</v>
       </c>
       <c r="C21" t="s">
-        <v>1059</v>
+        <v>1075</v>
       </c>
       <c r="D21" t="s">
-        <v>1094</v>
+        <v>1110</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1129</v>
+        <v>1145</v>
       </c>
       <c r="F21" t="s">
-        <v>865</v>
+        <v>881</v>
       </c>
       <c r="G21" t="s">
-        <v>876</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>990</v>
+        <v>1006</v>
       </c>
       <c r="B22" t="s">
-        <v>1025</v>
+        <v>1041</v>
       </c>
       <c r="C22" t="s">
-        <v>1060</v>
+        <v>1076</v>
       </c>
       <c r="D22" t="s">
-        <v>1095</v>
+        <v>1111</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1130</v>
+        <v>1146</v>
       </c>
       <c r="F22" t="s">
-        <v>1145</v>
+        <v>1161</v>
       </c>
       <c r="G22" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>991</v>
+        <v>1007</v>
       </c>
       <c r="B23" t="s">
-        <v>1026</v>
+        <v>1042</v>
       </c>
       <c r="C23" t="s">
-        <v>1061</v>
+        <v>1077</v>
       </c>
       <c r="D23" t="s">
-        <v>1096</v>
+        <v>1112</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1131</v>
+        <v>1147</v>
       </c>
       <c r="F23" t="s">
-        <v>1145</v>
+        <v>1161</v>
       </c>
       <c r="G23" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>992</v>
+        <v>1008</v>
       </c>
       <c r="B24" t="s">
-        <v>1027</v>
+        <v>1043</v>
       </c>
       <c r="C24" t="s">
-        <v>1062</v>
+        <v>1078</v>
       </c>
       <c r="D24" t="s">
-        <v>1097</v>
+        <v>1113</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1132</v>
+        <v>1148</v>
       </c>
       <c r="F24" t="s">
-        <v>865</v>
+        <v>881</v>
       </c>
       <c r="G24" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>993</v>
+        <v>1009</v>
       </c>
       <c r="B25" t="s">
-        <v>1028</v>
+        <v>1044</v>
       </c>
       <c r="C25" t="s">
-        <v>1063</v>
+        <v>1079</v>
       </c>
       <c r="D25" t="s">
-        <v>1098</v>
+        <v>1114</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1133</v>
+        <v>1149</v>
       </c>
       <c r="F25" t="s">
-        <v>865</v>
+        <v>881</v>
       </c>
       <c r="G25" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>994</v>
+        <v>1010</v>
       </c>
       <c r="B26" t="s">
-        <v>1029</v>
+        <v>1045</v>
       </c>
       <c r="C26" t="s">
-        <v>1064</v>
+        <v>1080</v>
       </c>
       <c r="D26" t="s">
-        <v>1099</v>
+        <v>1115</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1134</v>
+        <v>1150</v>
       </c>
       <c r="F26" t="s">
-        <v>1145</v>
+        <v>1161</v>
       </c>
       <c r="G26" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>995</v>
+        <v>1011</v>
       </c>
       <c r="B27" t="s">
-        <v>1030</v>
+        <v>1046</v>
       </c>
       <c r="C27" t="s">
-        <v>1065</v>
+        <v>1081</v>
       </c>
       <c r="D27" t="s">
-        <v>1100</v>
+        <v>1116</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1135</v>
+        <v>1151</v>
       </c>
       <c r="F27" t="s">
-        <v>1145</v>
+        <v>1161</v>
       </c>
       <c r="G27" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>996</v>
+        <v>1012</v>
       </c>
       <c r="B28" t="s">
-        <v>1031</v>
+        <v>1047</v>
       </c>
       <c r="C28" t="s">
-        <v>1066</v>
+        <v>1082</v>
       </c>
       <c r="D28" t="s">
-        <v>1101</v>
+        <v>1117</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1136</v>
+        <v>1152</v>
       </c>
       <c r="F28" t="s">
-        <v>1145</v>
+        <v>1161</v>
       </c>
       <c r="G28" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>997</v>
+        <v>1013</v>
       </c>
       <c r="B29" t="s">
-        <v>1032</v>
+        <v>1048</v>
       </c>
       <c r="C29" t="s">
-        <v>1067</v>
+        <v>1083</v>
       </c>
       <c r="D29" t="s">
-        <v>1102</v>
+        <v>1118</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1137</v>
+        <v>1153</v>
       </c>
       <c r="F29" t="s">
-        <v>845</v>
+        <v>860</v>
       </c>
       <c r="G29" t="s">
-        <v>1146</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>998</v>
+        <v>1014</v>
       </c>
       <c r="B30" t="s">
-        <v>1033</v>
+        <v>1049</v>
       </c>
       <c r="C30" t="s">
-        <v>1068</v>
+        <v>1084</v>
       </c>
       <c r="D30" t="s">
-        <v>1103</v>
+        <v>1119</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1138</v>
+        <v>1154</v>
       </c>
       <c r="F30" t="s">
-        <v>865</v>
+        <v>881</v>
       </c>
       <c r="G30" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="B31" t="s">
-        <v>1034</v>
+        <v>1050</v>
       </c>
       <c r="C31" t="s">
-        <v>1069</v>
+        <v>1085</v>
       </c>
       <c r="D31" t="s">
-        <v>1104</v>
+        <v>1120</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>1139</v>
+        <v>1155</v>
       </c>
       <c r="F31" t="s">
-        <v>1145</v>
+        <v>1161</v>
       </c>
       <c r="G31" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>1000</v>
+        <v>1016</v>
       </c>
       <c r="B32" t="s">
-        <v>1035</v>
+        <v>1051</v>
       </c>
       <c r="C32" t="s">
-        <v>1070</v>
+        <v>1086</v>
       </c>
       <c r="D32" t="s">
-        <v>1105</v>
+        <v>1121</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1140</v>
+        <v>1156</v>
       </c>
       <c r="F32" t="s">
-        <v>1145</v>
+        <v>1161</v>
       </c>
       <c r="G32" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="B33" t="s">
-        <v>1036</v>
+        <v>1052</v>
       </c>
       <c r="C33" t="s">
-        <v>1071</v>
+        <v>1087</v>
       </c>
       <c r="D33" t="s">
-        <v>1106</v>
+        <v>1122</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1141</v>
+        <v>1157</v>
       </c>
       <c r="F33" t="s">
-        <v>1145</v>
+        <v>1161</v>
       </c>
       <c r="G33" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>1002</v>
+        <v>1018</v>
       </c>
       <c r="B34" t="s">
-        <v>1037</v>
+        <v>1053</v>
       </c>
       <c r="C34" t="s">
-        <v>1072</v>
+        <v>1088</v>
       </c>
       <c r="D34" t="s">
-        <v>1107</v>
+        <v>1123</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1142</v>
+        <v>1158</v>
       </c>
       <c r="F34" t="s">
-        <v>1145</v>
+        <v>1161</v>
       </c>
       <c r="G34" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>1003</v>
+        <v>1019</v>
       </c>
       <c r="B35" t="s">
-        <v>1038</v>
+        <v>1054</v>
       </c>
       <c r="C35" t="s">
-        <v>1073</v>
+        <v>1089</v>
       </c>
       <c r="D35" t="s">
-        <v>1108</v>
+        <v>1124</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>1143</v>
+        <v>1159</v>
       </c>
       <c r="F35" t="s">
-        <v>1145</v>
+        <v>1161</v>
       </c>
       <c r="G35" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>1004</v>
+        <v>1020</v>
       </c>
       <c r="B36" t="s">
-        <v>1039</v>
+        <v>1055</v>
       </c>
       <c r="C36" t="s">
-        <v>1074</v>
+        <v>1090</v>
       </c>
       <c r="D36" t="s">
-        <v>1109</v>
+        <v>1125</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1144</v>
+        <v>1160</v>
       </c>
       <c r="F36" t="s">
-        <v>1145</v>
+        <v>1161</v>
       </c>
       <c r="G36" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
     </row>
   </sheetData>
@@ -10655,7 +10845,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB18"/>
+  <dimension ref="A1:AB23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="3" customWidth="1"/>
@@ -10691,713 +10881,748 @@
   <sheetData>
     <row r="1" spans="1:28">
       <c r="A1" s="5" t="s">
-        <v>891</v>
+        <v>907</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5" t="s">
-        <v>886</v>
+        <v>897</v>
       </c>
       <c r="D1" s="5"/>
       <c r="E1" s="5" t="s">
-        <v>888</v>
+        <v>899</v>
       </c>
       <c r="F1" s="5"/>
       <c r="G1" s="1" t="s">
-        <v>887</v>
+        <v>904</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>880</v>
+        <v>896</v>
       </c>
       <c r="I1" s="5"/>
       <c r="J1" s="5" t="s">
-        <v>881</v>
+        <v>898</v>
       </c>
       <c r="K1" s="5"/>
       <c r="L1" s="1" t="s">
-        <v>893</v>
+        <v>912</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>889</v>
+        <v>905</v>
       </c>
       <c r="N1" s="5"/>
       <c r="O1" s="1" t="s">
-        <v>882</v>
+        <v>900</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>890</v>
+        <v>906</v>
       </c>
       <c r="Q1" s="5"/>
       <c r="R1" s="5" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="S1" s="5"/>
       <c r="T1" s="5" t="s">
-        <v>884</v>
+        <v>902</v>
       </c>
       <c r="U1" s="5"/>
       <c r="V1" s="5" t="s">
-        <v>892</v>
+        <v>909</v>
       </c>
       <c r="W1" s="5"/>
       <c r="X1" s="1" t="s">
-        <v>879</v>
+        <v>895</v>
       </c>
       <c r="Y1" s="5" t="s">
-        <v>895</v>
+        <v>914</v>
       </c>
       <c r="Z1" s="5"/>
       <c r="AA1" s="5" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="AB1" s="5"/>
     </row>
     <row r="2" spans="1:28">
       <c r="A2" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="F2" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="G2" t="s">
+        <v>363</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="L2" t="s">
+        <v>356</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="O2" t="s">
         <v>354</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="P2" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="T2" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="G2" t="s">
-        <v>356</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="V2" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="X2" t="s">
         <v>349</v>
       </c>
-      <c r="M2" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="O2" t="s">
-        <v>347</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="V2" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="X2" t="s">
-        <v>343</v>
-      </c>
       <c r="Y2" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>381</v>
+        <v>422</v>
+      </c>
+      <c r="AA2" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="3" spans="1:28">
       <c r="A3" s="3" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="4" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="4" t="s">
-        <v>385</v>
+        <v>366</v>
       </c>
       <c r="G3" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="J3" s="6"/>
       <c r="K3" s="4" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="L3" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="O3" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>502</v>
+        <v>373</v>
+      </c>
+      <c r="R3" s="6"/>
+      <c r="S3" s="4" t="s">
+        <v>498</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="V3" s="6"/>
       <c r="W3" s="4" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="X3" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="Z3" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="AA3" s="3" t="s">
-        <v>386</v>
+        <v>429</v>
+      </c>
+      <c r="AA3" s="6"/>
+      <c r="AB3" s="4" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="4" spans="1:28">
       <c r="A4" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>365</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="C4" s="6"/>
       <c r="D4" s="4" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="4" t="s">
-        <v>430</v>
+        <v>387</v>
       </c>
       <c r="G4" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="L4" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="O4" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="P4" s="6"/>
       <c r="Q4" s="4" t="s">
-        <v>406</v>
+        <v>381</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>378</v>
       </c>
       <c r="T4" s="6"/>
       <c r="U4" s="4" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="V4" s="6"/>
       <c r="W4" s="4" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="X4" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="Y4" s="6"/>
       <c r="Z4" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="AA4" s="3" t="s">
-        <v>392</v>
+        <v>442</v>
+      </c>
+      <c r="AA4" s="6"/>
+      <c r="AB4" s="4" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="5" spans="1:28">
       <c r="A5" s="3" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="4" t="s">
-        <v>455</v>
+        <v>412</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="4" t="s">
-        <v>454</v>
+        <v>393</v>
       </c>
       <c r="G5" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>346</v>
+        <v>402</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>357</v>
       </c>
       <c r="L5" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>499</v>
+        <v>400</v>
       </c>
       <c r="O5" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="P5" s="6"/>
       <c r="Q5" s="4" t="s">
-        <v>496</v>
+        <v>415</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="V5" s="6"/>
       <c r="W5" s="4" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="Y5" s="6"/>
       <c r="Z5" s="4" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="AA5" s="3" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6" spans="1:28">
       <c r="A6" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>394</v>
-      </c>
+        <v>490</v>
+      </c>
+      <c r="C6" s="6"/>
       <c r="D6" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="E6" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="J6" s="6"/>
-      <c r="K6" s="4" t="s">
-        <v>370</v>
+      <c r="J6" s="3" t="s">
+        <v>451</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="O6" t="s">
-        <v>473</v>
-      </c>
-      <c r="P6" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="T6" s="3" t="s">
         <v>397</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>389</v>
       </c>
       <c r="V6" s="6"/>
       <c r="W6" s="4" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="Y6" s="3" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="AA6" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="AB6" s="4" t="s">
-        <v>448</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" spans="1:28">
       <c r="A7" s="6" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>411</v>
+        <v>445</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="4" t="s">
+        <v>463</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="J7" s="6"/>
+        <v>441</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>458</v>
+      </c>
       <c r="K7" s="4" t="s">
-        <v>374</v>
+        <v>414</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="O7" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="V7" s="6" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="W7" s="4" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="Y7" s="3" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="AA7" s="3" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" spans="1:28">
       <c r="A8" s="6"/>
       <c r="B8" s="4" t="s">
-        <v>466</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>439</v>
+        <v>475</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>351</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>504</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="H8" s="6"/>
       <c r="I8" s="4" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="J8" s="6"/>
       <c r="K8" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>422</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>375</v>
+        <v>466</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>431</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="V8" s="6"/>
       <c r="W8" s="4" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="Y8" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="AA8" s="6" t="s">
-        <v>419</v>
-      </c>
-      <c r="AB8" s="4" t="s">
-        <v>355</v>
+        <v>446</v>
+      </c>
+      <c r="AA8" s="3" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:28">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
-        <v>494</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>459</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="C9" s="6"/>
       <c r="D9" s="4" t="s">
-        <v>368</v>
+        <v>398</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>489</v>
+        <v>420</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>456</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="M9" s="6"/>
-      <c r="N9" s="4" t="s">
-        <v>379</v>
+        <v>472</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>440</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q9" s="4" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="V9" s="6"/>
       <c r="W9" s="4" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="Y9" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="Z9" s="4" t="s">
-        <v>485</v>
-      </c>
-      <c r="AA9" s="6"/>
-      <c r="AB9" s="4" t="s">
-        <v>423</v>
+        <v>452</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="10" spans="1:28">
       <c r="A10" s="3" t="s">
-        <v>483</v>
+        <v>492</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>384</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
-        <v>487</v>
+        <v>464</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>468</v>
+        <v>425</v>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" s="4" t="s">
+        <v>457</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="M10" s="6"/>
-      <c r="N10" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="P10" s="6" t="s">
-        <v>401</v>
-      </c>
-      <c r="Q10" s="4" t="s">
-        <v>403</v>
+        <v>465</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>409</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="AA10" s="6"/>
+        <v>436</v>
+      </c>
+      <c r="AA10" s="6" t="s">
+        <v>428</v>
+      </c>
       <c r="AB10" s="4" t="s">
-        <v>476</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11" spans="1:28">
       <c r="A11" s="3" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>449</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>457</v>
+        <v>403</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="H11" s="6"/>
+      <c r="I11" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>473</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="4" t="s">
-        <v>461</v>
+        <v>450</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>410</v>
       </c>
       <c r="V11" s="3" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="AA11" s="6"/>
       <c r="AB11" s="4" t="s">
-        <v>486</v>
+        <v>432</v>
       </c>
     </row>
     <row r="12" spans="1:28">
       <c r="C12" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="J12" s="6"/>
-      <c r="K12" s="4" t="s">
-        <v>463</v>
+        <v>419</v>
+      </c>
+      <c r="E12" s="6"/>
+      <c r="F12" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="H12" s="6"/>
+      <c r="I12" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>477</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>438</v>
+        <v>453</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>382</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="V12" s="6" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="W12" s="4" t="s">
-        <v>457</v>
+        <v>414</v>
       </c>
       <c r="AA12" s="6"/>
       <c r="AB12" s="4" t="s">
-        <v>505</v>
+        <v>485</v>
       </c>
     </row>
     <row r="13" spans="1:28">
-      <c r="C13" s="6" t="s">
-        <v>470</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>447</v>
+      <c r="C13" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>477</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>456</v>
+        <v>484</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="P13" s="6"/>
       <c r="Q13" s="4" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="V13" s="6"/>
       <c r="W13" s="4" t="s">
-        <v>463</v>
-      </c>
-      <c r="AA13" s="6" t="s">
-        <v>446</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="AA13" s="6"/>
       <c r="AB13" s="4" t="s">
-        <v>353</v>
+        <v>495</v>
       </c>
     </row>
     <row r="14" spans="1:28">
-      <c r="C14" s="6"/>
+      <c r="C14" s="6" t="s">
+        <v>468</v>
+      </c>
       <c r="D14" s="4" t="s">
-        <v>465</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>464</v>
+        <v>375</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>515</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="P14" s="6"/>
       <c r="Q14" s="4" t="s">
-        <v>493</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>507</v>
+        <v>502</v>
+      </c>
+      <c r="V14" s="6"/>
+      <c r="W14" s="4" t="s">
+        <v>472</v>
       </c>
       <c r="AA14" s="6"/>
       <c r="AB14" s="4" t="s">
-        <v>358</v>
+        <v>514</v>
       </c>
     </row>
     <row r="15" spans="1:28">
-      <c r="C15" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>468</v>
+      <c r="C15" s="6"/>
+      <c r="D15" s="4" t="s">
+        <v>438</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="N15" s="4" t="s">
-        <v>371</v>
+        <v>465</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="AA15" s="6"/>
+        <v>476</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="AA15" s="6" t="s">
+        <v>455</v>
+      </c>
       <c r="AB15" s="4" t="s">
-        <v>445</v>
+        <v>360</v>
       </c>
     </row>
     <row r="16" spans="1:28">
-      <c r="C16" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>475</v>
+      <c r="C16" s="6"/>
+      <c r="D16" s="4" t="s">
+        <v>496</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="AA16" s="3" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="17" spans="3:13">
+        <v>517</v>
+      </c>
+      <c r="AA16" s="6"/>
+      <c r="AB16" s="4" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="17" spans="3:27">
       <c r="C17" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="AA17" s="3" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27">
+      <c r="C18" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="18" spans="3:13">
-      <c r="C18" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>508</v>
+    </row>
+    <row r="19" spans="3:27">
+      <c r="C19" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="20" spans="3:27">
+      <c r="C20" s="3" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27">
+      <c r="C21" s="3" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27">
+      <c r="C22" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27">
+      <c r="C23" s="3" t="s">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="33">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C2:C7"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="C14:C16"/>
     <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="E11:E12"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="H6:H8"/>
+    <mergeCell ref="H9:H12"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J2:J3"/>
-    <mergeCell ref="J5:J9"/>
-    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J7:J9"/>
     <mergeCell ref="J1:K1"/>
-    <mergeCell ref="M8:M10"/>
     <mergeCell ref="M1:N1"/>
-    <mergeCell ref="P3:P5"/>
-    <mergeCell ref="P10:P11"/>
+    <mergeCell ref="P3:P6"/>
     <mergeCell ref="P12:P14"/>
     <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="R2:R3"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="T3:T4"/>
     <mergeCell ref="T1:U1"/>
     <mergeCell ref="V2:V6"/>
     <mergeCell ref="V7:V9"/>
-    <mergeCell ref="V12:V13"/>
+    <mergeCell ref="V12:V14"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="Y3:Y5"/>
     <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AA8:AA12"/>
-    <mergeCell ref="AA13:AA15"/>
+    <mergeCell ref="AA2:AA4"/>
+    <mergeCell ref="AA10:AA14"/>
+    <mergeCell ref="AA15:AA16"/>
     <mergeCell ref="AA1:AB1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
